--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -10759,7 +10759,7 @@
         <v>2.7000000000000006e-004</v>
       </c>
       <c r="E12" s="10">
-        <f t="shared" ref="E12:E21" si="0">2*PI()/C12</f>
+        <f t="shared" ref="E12:E15" si="0">2*PI()/C12</f>
         <v>4.9473900056532178</v>
       </c>
       <c r="F12" s="26">
@@ -10772,11 +10772,11 @@
         <v>4.9500000000000002</v>
       </c>
       <c r="I12" s="10">
-        <f t="shared" ref="I12:I21" si="1">AVERAGE(F12:H12)</f>
+        <f t="shared" ref="I12:I15" si="1">AVERAGE(F12:H12)</f>
         <v>5.0100000000000007</v>
       </c>
       <c r="J12" s="27">
-        <f t="shared" ref="J12:J21" si="2">2*PI()/I12</f>
+        <f t="shared" ref="J12:J15" si="2">2*PI()/I12</f>
         <v>1.2541288038282605</v>
       </c>
       <c r="K12" s="28">
@@ -10903,201 +10903,202 @@
         <v>5.4000000000000003e-003</v>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" s="10">
+        <v>3.2000000000000002</v>
+      </c>
+      <c r="C16">
+        <v>3.1400000000000001</v>
+      </c>
+      <c r="D16" s="25">
+        <f>1.9*10^-4</f>
+        <v>1.8999999999999998e-004</v>
+      </c>
+      <c r="E16" s="10">
+        <f>2*PI()/C16</f>
+        <v>2.0010144290380847</v>
+      </c>
+      <c r="F16" s="26">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>1.99</v>
+      </c>
+      <c r="H16" s="27">
+        <v>2</v>
+      </c>
+      <c r="I16" s="10">
+        <f>AVERAGE(F16:H16)</f>
+        <v>1.9966666666666668</v>
+      </c>
+      <c r="J16" s="27">
+        <f>2*PI()/I16</f>
+        <v>3.1468373825607276</v>
+      </c>
+      <c r="K16" s="26">
+        <v>2.9900000000000002</v>
+      </c>
+      <c r="L16" s="27">
+        <v>2.e-003</v>
+      </c>
+    </row>
     <row r="17">
       <c r="B17" s="10">
-        <v>3.2000000000000002</v>
+        <v>3.6000000000000001</v>
       </c>
       <c r="C17">
-        <v>3.1400000000000001</v>
+        <v>3.6800000000000002</v>
       </c>
       <c r="D17" s="25">
-        <f>1.9*10^-4</f>
-        <v>1.9000000000000001e-004</v>
+        <f>3*10^-4</f>
+        <v>2.9999999999999997e-004</v>
       </c>
       <c r="E17" s="10">
-        <f t="shared" si="0"/>
-        <v>2.0010144290380847</v>
+        <f>2*PI()/C17</f>
+        <v>1.7073873117335832</v>
       </c>
       <c r="F17" s="26">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G17">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="H17" s="27">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="I17" s="10">
-        <f t="shared" si="1"/>
-        <v>1.9966666666666668</v>
+        <f>AVERAGE(F17:H17)</f>
+        <v>1.7066666666666668</v>
       </c>
       <c r="J17" s="27">
-        <f t="shared" si="2"/>
-        <v>3.1468373825607276</v>
+        <f>2*PI()/I17</f>
+        <v>3.6815538909255388</v>
       </c>
       <c r="K17" s="26">
-        <v>2.9900000000000002</v>
+        <v>1.5800000000000001</v>
       </c>
       <c r="L17" s="27">
-        <v>2.e-003</v>
+        <v>1.5e-003</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="10">
-        <v>3.6000000000000001</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="C18">
-        <v>3.6800000000000002</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="D18" s="25">
-        <f>3*10^-4</f>
-        <v>3.0000000000000003e-004</v>
+        <f>3.7*10^-4</f>
+        <v>3.6999999999999999e-004</v>
       </c>
       <c r="E18" s="10">
-        <f t="shared" si="0"/>
-        <v>1.7073873117335832</v>
+        <f>2*PI()/C18</f>
+        <v>1.4312495004964889</v>
       </c>
       <c r="F18" s="26">
-        <v>1.7</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G18">
-        <v>1.71</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H18" s="27">
-        <v>1.71</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" si="1"/>
-        <v>1.7066666666666668</v>
+        <f>AVERAGE(F18:H18)</f>
+        <v>1.4333333333333333</v>
       </c>
       <c r="J18" s="27">
-        <f t="shared" si="2"/>
-        <v>3.6815538909255388</v>
+        <f>2*PI()/I18</f>
+        <v>4.3836176561718041</v>
       </c>
       <c r="K18" s="26">
-        <v>1.5800000000000001</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="L18" s="27">
-        <v>1.5e-003</v>
+        <v>7.7999999999999999e-004</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="10">
-        <v>4.2000000000000002</v>
+        <v>4.5</v>
       </c>
       <c r="C19">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="D19" s="25">
-        <f>3.7*10^-4</f>
-        <v>3.7000000000000005e-004</v>
+        <v>4.75</v>
+      </c>
+      <c r="D19" s="10">
+        <f>4.5*10^-4</f>
+        <v>4.4999999999999999e-004</v>
       </c>
       <c r="E19" s="10">
-        <f t="shared" si="0"/>
-        <v>1.4312495004964889</v>
+        <f>2*PI()/C19</f>
+        <v>1.3227758541430708</v>
       </c>
       <c r="F19" s="26">
-        <v>1.4399999999999999</v>
+        <v>1.3300000000000001</v>
       </c>
       <c r="G19">
-        <v>1.4299999999999999</v>
+        <v>1.3300000000000001</v>
       </c>
       <c r="H19" s="27">
-        <v>1.4299999999999999</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" si="1"/>
-        <v>1.4333333333333333</v>
+        <f>AVERAGE(F19:H19)</f>
+        <v>1.3266666666666669</v>
       </c>
       <c r="J19" s="27">
-        <f t="shared" si="2"/>
-        <v>4.3836176561718041</v>
+        <f>2*PI()/I19</f>
+        <v>4.7360693270197878</v>
       </c>
       <c r="K19" s="26">
-        <v>0.89300000000000002</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="L19" s="27">
-        <v>7.7999999999999999e-004</v>
+        <v>1.5e-003</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="C20">
-        <v>4.75</v>
-      </c>
-      <c r="D20" s="10">
-        <f>4.5*10^-4</f>
-        <v>4.5000000000000004e-004</v>
-      </c>
-      <c r="E20" s="10">
-        <f t="shared" si="0"/>
-        <v>1.3227758541430708</v>
-      </c>
-      <c r="F20" s="26">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="G20">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="H20" s="27">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="I20" s="10">
-        <f t="shared" si="1"/>
-        <v>1.3266666666666669</v>
-      </c>
-      <c r="J20" s="27">
-        <f t="shared" si="2"/>
-        <v>4.7360693270197878</v>
-      </c>
-      <c r="K20" s="26">
-        <v>0.71399999999999997</v>
-      </c>
-      <c r="L20" s="27">
-        <v>1.5e-003</v>
-      </c>
-    </row>
-    <row r="21" ht="13.15">
-      <c r="B21" s="30">
+      <c r="B20" s="30">
         <v>4.7000000000000002</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C20" s="31">
         <v>4.9500000000000002</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D20" s="30">
         <f>6.6*10^-4</f>
-        <v>6.6e-004</v>
-      </c>
-      <c r="E21" s="30">
-        <f t="shared" si="0"/>
+        <v>6.5999999999999989e-004</v>
+      </c>
+      <c r="E20" s="30">
+        <f>2*PI()/C20</f>
         <v>1.2693303650867851</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F20" s="32">
         <v>1.26</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G20" s="31">
         <v>1.28</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H20" s="33">
         <v>1.2669999999999999</v>
       </c>
-      <c r="I21" s="30">
-        <f t="shared" si="1"/>
+      <c r="I20" s="30">
+        <f>AVERAGE(F20:H20)</f>
         <v>1.2689999999999999</v>
       </c>
-      <c r="J21" s="33">
-        <f t="shared" si="2"/>
+      <c r="J20" s="33">
+        <f>2*PI()/I20</f>
         <v>4.9512886581399425</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K20" s="32">
         <v>0.63400000000000001</v>
       </c>
-      <c r="L21" s="33">
+      <c r="L20" s="33">
         <v>8.5999999999999998e-004</v>
       </c>
     </row>
+    <row r="21" ht="13.15"/>
     <row r="22" ht="13.5">
       <c r="B22" s="34"/>
     </row>

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Smorzate (4mm)" sheetId="1" state="visible" r:id="rId4"/>
@@ -221,7 +221,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,12 +245,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0"/>
+        <bgColor theme="4" tint="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0"/>
         <bgColor theme="6" tint="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -645,11 +651,20 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -664,12 +679,12 @@
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -727,6 +742,7 @@
     <xf fontId="0" fillId="2" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -17948,7 +17964,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.86328125"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="11.57421875"/>
     <col customWidth="1" min="2" max="2" width="13.265625"/>
     <col customWidth="1" min="3" max="3" width="13.1328125"/>
     <col customWidth="1" min="4" max="4" width="11.59765625"/>
@@ -17957,588 +17973,627 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="s">
+      <c r="B1" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="C1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="D1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="E1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="F1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="G1" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="H1" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="46" t="s">
+      <c r="I1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="J1" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="47" t="s">
+      <c r="K1" s="47" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="48">
+      <c r="B2" s="48">
         <v>0.25600000000000001</v>
       </c>
-      <c r="B2" s="48">
+      <c r="C2" s="48">
         <v>4.5999999999999999e-003</v>
       </c>
-      <c r="C2" s="48">
+      <c r="D2" s="48">
         <v>2.5699999999999998</v>
       </c>
-      <c r="D2" s="48">
+      <c r="E2" s="48">
         <v>4.4000000000000003e-003</v>
       </c>
-      <c r="E2" s="48">
-        <f>SQRT(A5^2+C5^2)</f>
+      <c r="F2" s="48">
+        <f>SQRT(B5^2+D5^2)</f>
         <v>2.6209779086798761</v>
       </c>
-      <c r="F2" s="48">
-        <f>E2*SQRT((D5/C5)^2+(B5/A5)^2)</f>
-        <v>5.861388954933708e-003</v>
-      </c>
       <c r="G2" s="48">
-        <f>E2/2</f>
-        <v>1.3104889543399381</v>
+        <f>F2*SQRT((E5/D5)^2+(C5/B5)^2)</f>
+        <v>5.8613889549337071e-003</v>
       </c>
       <c r="H2" s="48">
         <f>F2/2</f>
-        <v>2.930694477466854e-003</v>
+        <v>1.3104889543399381</v>
       </c>
       <c r="I2" s="48">
-        <f>E2*2</f>
-        <v>5.2419558173597522</v>
+        <f>G2/2</f>
+        <v>2.9306944774668536e-003</v>
       </c>
       <c r="J2" s="48">
         <f>F2*2</f>
-        <v>1.1722777909867416e-002</v>
+        <v>5.2419558173597522</v>
+      </c>
+      <c r="K2" s="48">
+        <f>G2*2</f>
+        <v>1.1722777909867414e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10">
+      <c r="B3" s="10">
         <v>0.26700000000000002</v>
       </c>
-      <c r="B3" s="10">
+      <c r="C3" s="10">
         <v>2.0999999999999999e-003</v>
       </c>
-      <c r="C3" s="10">
+      <c r="D3" s="10">
         <v>2.5899999999999999</v>
       </c>
-      <c r="D3" s="10">
+      <c r="E3" s="10">
         <v>1.9e-003</v>
       </c>
-      <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
     </row>
     <row r="4">
-      <c r="A4" s="10">
+      <c r="B4" s="10">
         <v>0.27400000000000002</v>
       </c>
-      <c r="B4" s="10">
+      <c r="C4" s="10">
         <f>6.4*10^-4</f>
-        <v>6.4000000000000005e-004</v>
-      </c>
-      <c r="C4" s="10">
+        <v>6.3999999999999994e-004</v>
+      </c>
+      <c r="D4" s="10">
         <v>2.6099999999999999</v>
       </c>
-      <c r="D4" s="10">
+      <c r="E4" s="10">
         <f>7.1*10^-4</f>
-        <v>7.1000000000000002e-004</v>
-      </c>
-      <c r="E4" s="10"/>
+        <v>7.0999999999999991e-004</v>
+      </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" ht="13.15">
-      <c r="A5" s="30">
-        <f>((A2/B2^2)+(A3/B3^2)+(A4/B4^2))/((1/B2^2)+(1/B3^2)+(1/B4^2))</f>
+      <c r="B5" s="30">
+        <f>((B2/C2^2)+(B3/C3^2)+(B4/C4^2))/((1/C2^2)+(1/C3^2)+(1/C4^2))</f>
         <v>0.27310217908105011</v>
       </c>
-      <c r="B5" s="30">
-        <f>SQRT(1/((1/B2^2)+(1/B3^2)+(1/B4^2)))</f>
-        <v>6.0684990176478428e-004</v>
-      </c>
       <c r="C5" s="30">
-        <f>((C2/D2^2)+(C3/D3^2)+(C4/D4^2))/((1/D2^2)+(1/D3^2)+(1/D4^2))</f>
+        <f>SQRT(1/((1/C2^2)+(1/C3^2)+(1/C4^2)))</f>
+        <v>6.0684990176478417e-004</v>
+      </c>
+      <c r="D5" s="30">
+        <f>((D2/E2^2)+(D3/E3^2)+(D4/E4^2))/((1/E2^2)+(1/E3^2)+(1/E4^2))</f>
         <v>2.6067106470740322</v>
       </c>
-      <c r="D5" s="30">
-        <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)))</f>
-        <v>6.5761093737006307e-004</v>
-      </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="30">
+        <f>SQRT(1/((1/E2^2)+(1/E3^2)+(1/E4^2)))</f>
+        <v>6.5761093737006296e-004</v>
+      </c>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
       <c r="H5" s="30"/>
       <c r="I5" s="30"/>
       <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
     </row>
     <row r="6" ht="13.15">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6">
+        <f>AVERAGE(B2:B5)</f>
+        <v>0.26752554477026252</v>
+      </c>
+      <c r="D6">
+        <f>AVERAGE(D2:D5)</f>
+        <v>2.5941776617685077</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <f>_xlfn.STDEV.S(B2:B5)</f>
+        <v>8.289185732326277e-003</v>
+      </c>
+      <c r="D7">
+        <f>_xlfn.STDEV.S(D2:D5)</f>
+        <v>1.8343339338159879e-002</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <f>B7/SQRT(4)</f>
+        <v>4.1445928661631385e-003</v>
+      </c>
+      <c r="D8">
+        <f>D7/SQRT(4)</f>
+        <v>9.1716696690799394e-003</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C10" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D10" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E10" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="20" t="s">
+      <c r="F10" s="22"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K10" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L10" s="6" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10">
-        <v>1.8</v>
-      </c>
-      <c r="B7" s="8">
-        <v>1.3100000000000001</v>
-      </c>
-      <c r="C7" s="8">
-        <v>9.1e-004</v>
-      </c>
-      <c r="D7" s="27">
-        <f t="shared" ref="D7:D16" si="3">2*PI()/B7</f>
-        <v>4.79632466196915</v>
-      </c>
-      <c r="E7" s="10">
-        <f t="shared" ref="E7:E16" si="4">2*PI()/B7</f>
-        <v>4.79632466196915</v>
-      </c>
-      <c r="F7" s="10">
-        <v>4.8399999999999999</v>
-      </c>
-      <c r="G7" s="10">
-        <v>4.7400000000000002</v>
-      </c>
-      <c r="H7" s="10">
-        <v>4.8200000000000003</v>
-      </c>
-      <c r="I7" s="10">
-        <f t="shared" ref="I7:I9" si="5">AVERAGE(F7:H7)</f>
-        <v>4.7999999999999998</v>
-      </c>
-      <c r="J7" s="10">
-        <f t="shared" ref="J7:J9" si="6">2*PI()/I7</f>
-        <v>1.3089969389957472</v>
-      </c>
-      <c r="K7" s="28">
-        <v>2.21</v>
-      </c>
-      <c r="L7" s="29">
-        <v>1.7000000000000001e-002</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10">
-        <v>1.8200000000000001</v>
-      </c>
-      <c r="B8" s="10">
-        <v>1.3600000000000001</v>
-      </c>
-      <c r="C8" s="10">
-        <f>8.9*10^-4</f>
-        <v>8.9000000000000006e-004</v>
-      </c>
-      <c r="D8" s="27">
-        <f t="shared" si="3"/>
-        <v>4.6199891964555775</v>
-      </c>
-      <c r="E8" s="10">
-        <f t="shared" si="4"/>
-        <v>4.6199891964555775</v>
-      </c>
-      <c r="F8" s="10">
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="G8" s="10">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="H8" s="10">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="I8" s="10">
-        <f t="shared" si="5"/>
-        <v>4.6200000000000001</v>
-      </c>
-      <c r="J8" s="10">
-        <f t="shared" si="6"/>
-        <v>1.3599968197358412</v>
-      </c>
-      <c r="K8" s="26">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="L8" s="27">
-        <v>1.4999999999999999e-002</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B9" s="10">
-        <v>1.9099999999999999</v>
-      </c>
-      <c r="C9" s="10">
-        <v>1.3999999999999999e-004</v>
-      </c>
-      <c r="D9" s="27">
-        <f t="shared" si="3"/>
-        <v>3.2896258152772706</v>
-      </c>
-      <c r="E9" s="10">
-        <f t="shared" si="4"/>
-        <v>3.2896258152772706</v>
-      </c>
-      <c r="F9" s="10">
-        <v>3.2999999999999998</v>
-      </c>
-      <c r="G9" s="10">
-        <v>3.29</v>
-      </c>
-      <c r="H9" s="10">
-        <v>3.29</v>
-      </c>
-      <c r="I9" s="10">
-        <f t="shared" si="5"/>
-        <v>3.293333333333333</v>
-      </c>
-      <c r="J9" s="10">
-        <f t="shared" si="6"/>
-        <v>1.9078497896294293</v>
-      </c>
-      <c r="K9" s="26">
-        <v>3.3799999999999999</v>
-      </c>
-      <c r="L9" s="27">
-        <v>3.7000000000000002e-003</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10">
-        <v>3.3999999999999999</v>
-      </c>
-      <c r="B10" s="10">
-        <v>3.3799999999999999</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="27">
-        <f t="shared" si="3"/>
-        <v>1.8589305642543155</v>
-      </c>
-      <c r="E10" s="10">
-        <f t="shared" si="4"/>
-        <v>1.8589305642543155</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1.8600000000000001</v>
-      </c>
-      <c r="G10" s="10">
-        <v>1.8600000000000001</v>
-      </c>
-      <c r="H10" s="10">
-        <v>1.8500000000000001</v>
-      </c>
-      <c r="I10" s="10">
-        <f t="shared" ref="I10:I12" si="7">AVERAGE(F10:H10)</f>
-        <v>1.8566666666666667</v>
-      </c>
-      <c r="J10" s="10">
-        <f t="shared" ref="J10:J16" si="8">2*PI()/I10</f>
-        <v>3.384121350366025</v>
-      </c>
-      <c r="K10" s="26">
-        <v>2.3599999999999999</v>
-      </c>
-      <c r="L10" s="27">
-        <v>2.e-003</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10">
-        <v>3.7999999999999998</v>
-      </c>
-      <c r="B11" s="10">
-        <v>3.8900000000000001</v>
-      </c>
-      <c r="C11" s="10"/>
+        <v>1.8</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1.3100000000000001</v>
+      </c>
+      <c r="C11" s="8">
+        <v>9.1e-004</v>
+      </c>
       <c r="D11" s="27">
-        <f t="shared" si="3"/>
-        <v>1.6152147319227728</v>
+        <f>2*PI()/B11</f>
+        <v>4.79632466196915</v>
       </c>
       <c r="E11" s="10">
-        <f t="shared" si="4"/>
-        <v>1.6152147319227728</v>
+        <f>2*PI()/B11</f>
+        <v>4.79632466196915</v>
       </c>
       <c r="F11" s="10">
-        <v>1.6200000000000001</v>
+        <v>4.8399999999999999</v>
       </c>
       <c r="G11" s="10">
-        <v>1.6200000000000001</v>
+        <v>4.7400000000000002</v>
       </c>
       <c r="H11" s="10">
-        <v>1.6100000000000001</v>
+        <v>4.8200000000000003</v>
       </c>
       <c r="I11" s="10">
-        <f t="shared" si="7"/>
-        <v>1.6166666666666669</v>
+        <f>AVERAGE(F11:H11)</f>
+        <v>4.7999999999999998</v>
       </c>
       <c r="J11" s="10">
-        <f t="shared" si="8"/>
-        <v>3.8865063755750011</v>
-      </c>
-      <c r="K11" s="26">
-        <v>1.3600000000000001</v>
-      </c>
-      <c r="L11" s="27">
-        <v>2.3e-003</v>
+        <f>2*PI()/I11</f>
+        <v>1.3089969389957472</v>
+      </c>
+      <c r="K11" s="28">
+        <v>2.21</v>
+      </c>
+      <c r="L11" s="29">
+        <v>1.7000000000000001e-002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10">
-        <v>4</v>
+        <v>1.8200000000000001</v>
       </c>
       <c r="B12" s="10">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="C12" s="10"/>
+        <v>1.3600000000000001</v>
+      </c>
+      <c r="C12" s="10">
+        <f>8.9*10^-4</f>
+        <v>8.8999999999999995e-004</v>
+      </c>
       <c r="D12" s="27">
-        <f t="shared" si="3"/>
-        <v>1.5475825879752676</v>
+        <f>2*PI()/B12</f>
+        <v>4.6199891964555775</v>
       </c>
       <c r="E12" s="10">
-        <f t="shared" si="4"/>
-        <v>1.5475825879752676</v>
+        <f>2*PI()/B12</f>
+        <v>4.6199891964555775</v>
       </c>
       <c r="F12" s="10">
-        <v>1.54</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="G12" s="10">
-        <v>1.55</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H12" s="10">
-        <v>1.55</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="I12" s="10">
-        <f t="shared" si="7"/>
-        <v>1.5466666666666666</v>
+        <f>AVERAGE(F12:H12)</f>
+        <v>4.6200000000000001</v>
       </c>
       <c r="J12" s="10">
-        <f t="shared" si="8"/>
-        <v>4.062404293435077</v>
+        <f>2*PI()/I12</f>
+        <v>1.3599968197358412</v>
       </c>
       <c r="K12" s="26">
-        <v>1.1699999999999999</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="L12" s="27">
-        <v>2.2000000000000001e-003</v>
+        <v>1.4999999999999999e-002</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10">
-        <v>4.2999999999999998</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="B13" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="C13" s="10"/>
+        <v>1.9099999999999999</v>
+      </c>
+      <c r="C13" s="10">
+        <v>1.3999999999999999e-004</v>
+      </c>
       <c r="D13" s="27">
-        <f t="shared" si="3"/>
-        <v>1.3962634015954636</v>
+        <f>2*PI()/B13</f>
+        <v>3.2896258152772706</v>
       </c>
       <c r="E13" s="10">
-        <f t="shared" si="4"/>
-        <v>1.3962634015954636</v>
+        <f>2*PI()/B13</f>
+        <v>3.2896258152772706</v>
       </c>
       <c r="F13" s="10">
-        <v>1.3999999999999999</v>
+        <v>3.2999999999999998</v>
       </c>
       <c r="G13" s="10">
-        <v>1.3999999999999999</v>
+        <v>3.29</v>
       </c>
       <c r="H13" s="10">
-        <v>1.3999999999999999</v>
+        <v>3.29</v>
       </c>
       <c r="I13" s="10">
-        <f>AVERAGE(G13:H13)</f>
-        <v>1.3999999999999999</v>
+        <f>AVERAGE(F13:H13)</f>
+        <v>3.293333333333333</v>
       </c>
       <c r="J13" s="10">
-        <f t="shared" si="8"/>
-        <v>4.4879895051282759</v>
+        <f>2*PI()/I13</f>
+        <v>1.9078497896294293</v>
       </c>
       <c r="K13" s="26">
-        <v>0.84499999999999997</v>
+        <v>3.3799999999999999</v>
       </c>
       <c r="L13" s="27">
-        <v>1.2999999999999999e-003</v>
+        <v>3.7000000000000002e-003</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10">
-        <v>4.5999999999999996</v>
+        <v>3.3999999999999999</v>
       </c>
       <c r="B14" s="10">
-        <v>4.8799999999999999</v>
+        <v>3.3799999999999999</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="27">
-        <f t="shared" si="3"/>
-        <v>1.2875379727827021</v>
+        <f>2*PI()/B14</f>
+        <v>1.8589305642543155</v>
       </c>
       <c r="E14" s="10">
-        <f t="shared" si="4"/>
-        <v>1.2875379727827021</v>
+        <f>2*PI()/B14</f>
+        <v>1.8589305642543155</v>
       </c>
       <c r="F14" s="10">
-        <v>1.3</v>
+        <v>1.8600000000000001</v>
       </c>
       <c r="G14" s="10">
-        <v>1.29</v>
+        <v>1.8600000000000001</v>
       </c>
       <c r="H14" s="10">
-        <v>1.28</v>
+        <v>1.8500000000000001</v>
       </c>
       <c r="I14" s="10">
-        <f t="shared" ref="I14:I16" si="9">AVERAGE(F14:H14)</f>
-        <v>1.29</v>
+        <f>AVERAGE(F14:H14)</f>
+        <v>1.8566666666666667</v>
       </c>
       <c r="J14" s="10">
-        <f t="shared" si="8"/>
-        <v>4.8706862846353376</v>
+        <f>2*PI()/I14</f>
+        <v>3.384121350366025</v>
       </c>
       <c r="K14" s="26">
-        <v>0.67300000000000004</v>
+        <v>2.3599999999999999</v>
       </c>
       <c r="L14" s="27">
-        <v>1.e-003</v>
+        <v>2.e-003</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10">
-        <v>4.7999999999999998</v>
+        <v>3.7999999999999998</v>
       </c>
       <c r="B15" s="10">
-        <v>5.1100000000000003</v>
+        <v>3.8900000000000001</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="27">
-        <f t="shared" si="3"/>
+        <f>2*PI()/B15</f>
+        <v>1.6152147319227728</v>
+      </c>
+      <c r="E15" s="10">
+        <f>2*PI()/B15</f>
+        <v>1.6152147319227728</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1.6200000000000001</v>
+      </c>
+      <c r="G15" s="10">
+        <v>1.6200000000000001</v>
+      </c>
+      <c r="H15" s="10">
+        <v>1.6100000000000001</v>
+      </c>
+      <c r="I15" s="10">
+        <f>AVERAGE(F15:H15)</f>
+        <v>1.6166666666666669</v>
+      </c>
+      <c r="J15" s="10">
+        <f>2*PI()/I15</f>
+        <v>3.8865063755750011</v>
+      </c>
+      <c r="K15" s="26">
+        <v>1.3600000000000001</v>
+      </c>
+      <c r="L15" s="27">
+        <v>2.3e-003</v>
+      </c>
+    </row>
+    <row r="16" ht="13.15">
+      <c r="A16" s="10">
+        <v>4</v>
+      </c>
+      <c r="B16" s="10">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="27">
+        <f>2*PI()/B16</f>
+        <v>1.5475825879752676</v>
+      </c>
+      <c r="E16" s="10">
+        <f>2*PI()/B16</f>
+        <v>1.5475825879752676</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1.54</v>
+      </c>
+      <c r="G16" s="10">
+        <v>1.55</v>
+      </c>
+      <c r="H16" s="10">
+        <v>1.55</v>
+      </c>
+      <c r="I16" s="10">
+        <f>AVERAGE(F16:H16)</f>
+        <v>1.5466666666666666</v>
+      </c>
+      <c r="J16" s="10">
+        <f>2*PI()/I16</f>
+        <v>4.062404293435077</v>
+      </c>
+      <c r="K16" s="26">
+        <v>1.1699999999999999</v>
+      </c>
+      <c r="L16" s="27">
+        <v>2.2000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="17" ht="12.75">
+      <c r="A17" s="10">
+        <v>4.2999999999999998</v>
+      </c>
+      <c r="B17" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="27">
+        <f>2*PI()/B17</f>
+        <v>1.3962634015954636</v>
+      </c>
+      <c r="E17" s="10">
+        <f>2*PI()/B17</f>
+        <v>1.3962634015954636</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="G17" s="10">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="H17" s="10">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="I17" s="10">
+        <f>AVERAGE(G17:H17)</f>
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="J17" s="10">
+        <f>2*PI()/I17</f>
+        <v>4.4879895051282759</v>
+      </c>
+      <c r="K17" s="26">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="L17" s="27">
+        <v>1.2999999999999999e-003</v>
+      </c>
+    </row>
+    <row r="18" ht="12.75">
+      <c r="A18" s="10">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="B18" s="10">
+        <v>4.8799999999999999</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="27">
+        <f>2*PI()/B18</f>
+        <v>1.2875379727827021</v>
+      </c>
+      <c r="E18" s="10">
+        <f>2*PI()/B18</f>
+        <v>1.2875379727827021</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1.29</v>
+      </c>
+      <c r="H18" s="10">
+        <v>1.28</v>
+      </c>
+      <c r="I18" s="10">
+        <f>AVERAGE(F18:H18)</f>
+        <v>1.29</v>
+      </c>
+      <c r="J18" s="10">
+        <f>2*PI()/I18</f>
+        <v>4.8706862846353376</v>
+      </c>
+      <c r="K18" s="26">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="L18" s="27">
+        <v>1.e-003</v>
+      </c>
+    </row>
+    <row r="19" ht="12.75">
+      <c r="A19" s="10">
+        <v>4.7999999999999998</v>
+      </c>
+      <c r="B19" s="10">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="27">
+        <f>2*PI()/B19</f>
         <v>1.2295861657885687</v>
       </c>
-      <c r="E15" s="10">
-        <f t="shared" si="4"/>
+      <c r="E19" s="10">
+        <f>2*PI()/B19</f>
         <v>1.2295861657885687</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F19" s="10">
         <v>1.22</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G19" s="10">
         <v>1.23</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H19" s="10">
         <v>1.23</v>
       </c>
-      <c r="I15" s="10">
-        <f t="shared" si="9"/>
+      <c r="I19" s="10">
+        <f>AVERAGE(F19:H19)</f>
         <v>1.2266666666666668</v>
       </c>
-      <c r="J15" s="10">
-        <f t="shared" si="8"/>
+      <c r="J19" s="10">
+        <f>2*PI()/I19</f>
         <v>5.122161935200749</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K19" s="26">
         <v>0.59299999999999997</v>
       </c>
-      <c r="L15" s="27">
+      <c r="L19" s="27">
         <v>7.4999999999999993e-005</v>
       </c>
     </row>
-    <row r="16" ht="13.15">
-      <c r="A16" s="30">
+    <row r="20" ht="12.75">
+      <c r="A20" s="30">
         <v>4.9000000000000004</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B20" s="30">
         <v>5.2300000000000004</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="33">
-        <f t="shared" si="3"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="33">
+        <f>2*PI()/B20</f>
         <v>1.2013738637054656</v>
       </c>
-      <c r="E16" s="30">
-        <f t="shared" si="4"/>
+      <c r="E20" s="30">
+        <f>2*PI()/B20</f>
         <v>1.2013738637054656</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F20" s="30">
         <v>1.2</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G20" s="30">
         <v>1.2</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H20" s="30">
         <v>1.2</v>
       </c>
-      <c r="I16" s="30">
-        <f t="shared" si="9"/>
+      <c r="I20" s="30">
+        <f>AVERAGE(F20:H20)</f>
         <v>1.2</v>
       </c>
-      <c r="J16" s="30">
-        <f t="shared" si="8"/>
+      <c r="J20" s="30">
+        <f>2*PI()/I20</f>
         <v>5.2359877559829888</v>
       </c>
-      <c r="K16" s="32">
+      <c r="K20" s="32">
         <v>0.55700000000000005</v>
       </c>
-      <c r="L16" s="33">
+      <c r="L20" s="33">
         <v>6.0000000000000002e-005</v>
       </c>
     </row>
     <row r="23">
-      <c r="N23" s="49"/>
+      <c r="N23" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="E10:G10"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Smorzate forzate (4mm)" sheetId="1" state="visible" r:id="rId4"/>

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -160,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="53">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -542,6 +542,21 @@
       <left style="medium">
         <color theme="1"/>
       </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
       <right/>
       <top style="medium">
         <color theme="1"/>
@@ -788,17 +803,8 @@
         <color theme="1"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
+        <color theme="1"/>
+      </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -817,17 +823,6 @@
       <left style="none"/>
       <right style="medium">
         <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
       </right>
       <top style="none"/>
       <bottom style="medium">
@@ -839,7 +834,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -914,38 +909,38 @@
     <xf fontId="0" fillId="0" borderId="30" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="27" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="28" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="4" borderId="33" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="42" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="43" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="44" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="45" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="46" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="47" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -954,19 +949,18 @@
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="47" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="49" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="50" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="51" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="52" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="53" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1716,7 +1710,7 @@
         <v>2.1600000000000001</v>
       </c>
       <c r="K13" s="39">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="14">
@@ -1754,7 +1748,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="K14" s="43">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="15">
@@ -1792,7 +1786,7 @@
         <v>2.6000000000000001</v>
       </c>
       <c r="K15" s="43">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="16">
@@ -1830,7 +1824,7 @@
         <v>3.6699999999999999</v>
       </c>
       <c r="K16" s="43">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="17">
@@ -1868,7 +1862,7 @@
         <v>2.9900000000000002</v>
       </c>
       <c r="K17" s="43">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="18">
@@ -1906,7 +1900,7 @@
         <v>1.5800000000000001</v>
       </c>
       <c r="K18" s="43">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="19">
@@ -1944,7 +1938,7 @@
         <v>0.89300000000000002</v>
       </c>
       <c r="K19" s="43">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="20">
@@ -1982,7 +1976,7 @@
         <v>0.71399999999999997</v>
       </c>
       <c r="K20" s="43">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="21" ht="13.15">
@@ -2020,7 +2014,7 @@
         <v>0.63400000000000001</v>
       </c>
       <c r="K21" s="54">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="22" ht="13.5">
@@ -2316,15 +2310,15 @@
       <c r="J10" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="84" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="84">
+      <c r="A11" s="85">
         <v>1.8</v>
       </c>
-      <c r="B11" s="85">
+      <c r="B11" s="86">
         <v>1.3100000000000001</v>
       </c>
       <c r="C11" s="39">
@@ -2347,19 +2341,19 @@
         <f>AVERAGE(E11:G11)</f>
         <v>4.7999999999999998</v>
       </c>
-      <c r="I11" s="86">
+      <c r="I11" s="87">
         <f>2*PI()/H11</f>
         <v>1.3089969389957472</v>
       </c>
-      <c r="J11" s="85">
+      <c r="J11" s="86">
         <v>2.21</v>
       </c>
-      <c r="K11" s="87">
-        <v>1.7000000000000001e-002</v>
+      <c r="K11" s="39">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="84">
+      <c r="A12" s="85">
         <v>1.8200000000000001</v>
       </c>
       <c r="B12" s="71">
@@ -2385,19 +2379,19 @@
         <f>AVERAGE(E12:G12)</f>
         <v>4.6200000000000001</v>
       </c>
-      <c r="I12" s="86">
+      <c r="I12" s="87">
         <f>2*PI()/H12</f>
         <v>1.3599968197358412</v>
       </c>
       <c r="J12" s="71">
         <v>2.2400000000000002</v>
       </c>
-      <c r="K12" s="88">
-        <v>1.4999999999999999e-002</v>
+      <c r="K12" s="43">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="84">
+      <c r="A13" s="85">
         <v>2.2999999999999998</v>
       </c>
       <c r="B13" s="71">
@@ -2423,19 +2417,19 @@
         <f>AVERAGE(E13:G13)</f>
         <v>3.293333333333333</v>
       </c>
-      <c r="I13" s="86">
+      <c r="I13" s="87">
         <f>2*PI()/H13</f>
         <v>1.9078497896294293</v>
       </c>
       <c r="J13" s="71">
         <v>3.3799999999999999</v>
       </c>
-      <c r="K13" s="88">
-        <v>3.7000000000000002e-003</v>
+      <c r="K13" s="43">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="84">
+      <c r="A14" s="85">
         <v>3.3999999999999999</v>
       </c>
       <c r="B14" s="71">
@@ -2461,19 +2455,19 @@
         <f>AVERAGE(E14:G14)</f>
         <v>1.8566666666666667</v>
       </c>
-      <c r="I14" s="86">
+      <c r="I14" s="87">
         <f>2*PI()/H14</f>
         <v>3.384121350366025</v>
       </c>
       <c r="J14" s="71">
         <v>2.3599999999999999</v>
       </c>
-      <c r="K14" s="88">
-        <v>2.e-003</v>
+      <c r="K14" s="43">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="84">
+      <c r="A15" s="85">
         <v>3.7999999999999998</v>
       </c>
       <c r="B15" s="71">
@@ -2499,19 +2493,19 @@
         <f>AVERAGE(E15:G15)</f>
         <v>1.6166666666666669</v>
       </c>
-      <c r="I15" s="86">
+      <c r="I15" s="87">
         <f>2*PI()/H15</f>
         <v>3.8865063755750011</v>
       </c>
       <c r="J15" s="71">
         <v>1.3600000000000001</v>
       </c>
-      <c r="K15" s="88">
-        <v>2.3e-003</v>
+      <c r="K15" s="43">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="16" ht="13.15">
-      <c r="A16" s="84">
+      <c r="A16" s="85">
         <v>4</v>
       </c>
       <c r="B16" s="71">
@@ -2537,19 +2531,19 @@
         <f>AVERAGE(E16:G16)</f>
         <v>1.5466666666666666</v>
       </c>
-      <c r="I16" s="86">
+      <c r="I16" s="87">
         <f>2*PI()/H16</f>
         <v>4.062404293435077</v>
       </c>
       <c r="J16" s="71">
         <v>1.1699999999999999</v>
       </c>
-      <c r="K16" s="88">
-        <v>2.2000000000000001e-003</v>
+      <c r="K16" s="43">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" s="84">
+      <c r="A17" s="85">
         <v>4.2999999999999998</v>
       </c>
       <c r="B17" s="42">
@@ -2575,19 +2569,19 @@
         <f>AVERAGE(F17:G17)</f>
         <v>1.3999999999999999</v>
       </c>
-      <c r="I17" s="86">
+      <c r="I17" s="87">
         <f>2*PI()/H17</f>
         <v>4.4879895051282759</v>
       </c>
       <c r="J17" s="71">
         <v>0.84499999999999997</v>
       </c>
-      <c r="K17" s="88">
-        <v>1.2999999999999999e-003</v>
+      <c r="K17" s="43">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="18" ht="12.75">
-      <c r="A18" s="84">
+      <c r="A18" s="85">
         <v>4.5999999999999996</v>
       </c>
       <c r="B18" s="71">
@@ -2613,19 +2607,19 @@
         <f>AVERAGE(E18:G18)</f>
         <v>1.29</v>
       </c>
-      <c r="I18" s="86">
+      <c r="I18" s="87">
         <f>2*PI()/H18</f>
         <v>4.8706862846353376</v>
       </c>
       <c r="J18" s="71">
         <v>0.67300000000000004</v>
       </c>
-      <c r="K18" s="88">
-        <v>1.e-003</v>
+      <c r="K18" s="43">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="19" ht="12.75">
-      <c r="A19" s="84">
+      <c r="A19" s="85">
         <v>4.7999999999999998</v>
       </c>
       <c r="B19" s="71">
@@ -2651,25 +2645,25 @@
         <f>AVERAGE(E19:G19)</f>
         <v>1.2266666666666668</v>
       </c>
-      <c r="I19" s="86">
+      <c r="I19" s="87">
         <f>2*PI()/H19</f>
         <v>5.122161935200749</v>
       </c>
       <c r="J19" s="71">
         <v>0.59299999999999997</v>
       </c>
-      <c r="K19" s="88">
-        <v>7.4999999999999993e-005</v>
+      <c r="K19" s="43">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="20" ht="12.75">
-      <c r="A20" s="89">
+      <c r="A20" s="88">
         <v>4.9000000000000004</v>
       </c>
-      <c r="B20" s="90">
+      <c r="B20" s="89">
         <v>5.2300000000000004</v>
       </c>
-      <c r="C20" s="54">
+      <c r="C20" s="90">
         <v>1.e-002</v>
       </c>
       <c r="D20" s="91">
@@ -2693,15 +2687,15 @@
         <f>2*PI()/H20</f>
         <v>5.2359877559829888</v>
       </c>
-      <c r="J20" s="90">
+      <c r="J20" s="89">
         <v>0.55700000000000005</v>
       </c>
-      <c r="K20" s="94">
-        <v>6.0000000000000002e-005</v>
+      <c r="K20" s="90">
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="23">
-      <c r="N23" s="95"/>
+      <c r="N23" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -160,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="57">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -392,29 +392,12 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="none"/>
       <right style="none"/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -425,9 +408,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -438,19 +419,116 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
+      <right style="thin">
+        <color theme="1"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
-      </top>
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -473,18 +551,7 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
+      <left style="thin">
         <color theme="1"/>
       </left>
       <right style="medium">
@@ -495,13 +562,57 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
+      <right style="thin">
+        <color theme="1"/>
       </right>
       <top style="none"/>
       <bottom style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -512,7 +623,7 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -521,20 +632,20 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
       </right>
       <top style="none"/>
       <bottom style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -542,9 +653,7 @@
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
+      <right style="none"/>
       <top style="medium">
         <color theme="1"/>
       </top>
@@ -554,37 +663,9 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
       </right>
       <top style="medium">
         <color theme="1"/>
@@ -598,64 +679,10 @@
       <left style="none"/>
       <right style="none"/>
       <top style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -728,84 +755,15 @@
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
       <bottom style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -815,29 +773,86 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
       </right>
       <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="97">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -857,90 +872,100 @@
     <xf fontId="0" fillId="6" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="42" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="33" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="4" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="43" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="46" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="47" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="48" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="45" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="46" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="47" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="51" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="52" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="53" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="55" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -949,17 +974,16 @@
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="55" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="56" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="51" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="52" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1481,591 +1505,590 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="13.15">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>0.29499999999999998</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>1.2e-002</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>2.4900000000000002</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>1.e-002</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <f>SQRT(A8^2+C8^2)</f>
         <v>2.4749781728905389</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>0.30199999999999999</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>1.2999999999999999e-002</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>0.29699999999999999</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>1.0999999999999999e-002</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>1.e-002</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <f>E2/2</f>
         <v>1.2374890864452694</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>0.24199999999999999</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>1.4e-002</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>2.4399999999999999</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>1.2999999999999999e-002</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>0.28199999999999997</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <v>1.2e-002</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>1.0999999999999999e-002</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <f>E2*2</f>
         <v>4.9499563457810778</v>
       </c>
     </row>
     <row r="7" ht="13.15">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" ht="12.75">
-      <c r="A8" s="17">
+      <c r="A8" s="16">
         <f>((A2/B2^2)+(A3/B3^2)+(A4/B4^2)+(A5/B5^2)+(A6/B6^2))/((1/B2^2)+(1/B3^2)+(1/B4^2)+(1/B5^2)+(1/B6^2))</f>
         <v>0.28512468408871228</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="16">
         <f>SQRT(1/((1/B2^2)+(1/B3^2)+(1/B4^2)+(1/B5^2)+(1/B6^2)))</f>
         <v>5.616574006704656e-003</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <f>((C2/D2^2)+(C3/D3^2)+(C4/D4^2)+(C5/D5^2)+(C6/D6^2))/((1/D2^2)+(1/D3^2)+(1/D4^2)+(1/D5^2)+(1/D6^2))</f>
         <v>2.4584997195053537</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)+(1/D5^2)+(1/D6^2)))</f>
         <v>4.9938375155813399e-003</v>
       </c>
     </row>
     <row r="9" ht="12.75">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" ht="13.15">
-      <c r="A10" s="19">
+      <c r="A10" s="18">
         <f>AVERAGE(A2:A6)</f>
         <v>0.28359999999999996</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <f>_xlfn.STDEV.S(A2:A6)/SQRT(5)</f>
         <v>1.0911461863563468e-002</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="20">
         <f>AVERAGE(C2:C6)</f>
         <v>2.4560000000000004</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <f>_xlfn.STDEV.S(C2:C6)/SQRT(5)</f>
         <v>8.7177978870813765e-003</v>
       </c>
     </row>
     <row r="11" ht="13.15"/>
     <row r="12">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="28" t="s">
+      <c r="F12" s="24"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="29" t="s">
+      <c r="I12" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="30" t="s">
+      <c r="J12" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="31" t="s">
+      <c r="K12" s="26" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10">
+      <c r="A13" s="28">
         <v>1.7</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="29">
         <v>1.27</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="30">
         <v>1.e-002</v>
       </c>
-      <c r="D13" s="33">
-        <f>2*PI()/B13</f>
+      <c r="D13" s="31">
+        <f t="shared" ref="D13:D16" si="0">2*PI()/B13</f>
         <v>4.9473900056532178</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="32">
         <v>5.04</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="33">
         <v>5.04</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="34">
         <v>4.9500000000000002</v>
       </c>
-      <c r="H13" s="10">
-        <f>AVERAGE(E13:G13)</f>
+      <c r="H13" s="35">
+        <f t="shared" ref="H13:H16" si="1">AVERAGE(E13:G13)</f>
         <v>5.0100000000000007</v>
       </c>
-      <c r="I13" s="37">
-        <f>2*PI()/H13</f>
+      <c r="I13" s="36">
+        <f t="shared" ref="I13:I16" si="2">2*PI()/H13</f>
         <v>1.2541288038282605</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13" s="37">
         <v>2.1600000000000001</v>
       </c>
-      <c r="K13" s="39">
+      <c r="K13" s="38">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10">
+      <c r="A14" s="8">
         <v>1.8</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="39">
         <v>1.4299999999999999</v>
       </c>
       <c r="C14" s="40">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="33">
-        <f>2*PI()/B14</f>
+      <c r="D14" s="41">
+        <f t="shared" si="0"/>
         <v>4.3938358791465637</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="42">
         <v>4.4100000000000001</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="43">
         <v>4.5300000000000002</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="44">
         <v>4.3700000000000001</v>
       </c>
-      <c r="H14" s="41">
-        <f>AVERAGE(E14:G14)</f>
+      <c r="H14" s="45">
+        <f t="shared" si="1"/>
         <v>4.4366666666666674</v>
       </c>
-      <c r="I14" s="37">
-        <f>2*PI()/H14</f>
+      <c r="I14" s="46">
+        <f t="shared" si="2"/>
         <v>1.4161950354274047</v>
       </c>
-      <c r="J14" s="42">
+      <c r="J14" s="47">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K14" s="43">
+      <c r="K14" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="44">
+      <c r="A15" s="49">
         <v>2</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="39">
         <v>1.6100000000000001</v>
       </c>
       <c r="C15" s="40">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="33">
-        <f>2*PI()/B15</f>
+      <c r="D15" s="41">
+        <f t="shared" si="0"/>
         <v>3.9025995696767612</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="42">
         <v>3.8599999999999999</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="43">
         <v>3.8700000000000001</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="44">
         <v>3.96</v>
       </c>
-      <c r="H15" s="41">
-        <f>AVERAGE(E15:G15)</f>
+      <c r="H15" s="45">
+        <f t="shared" si="1"/>
         <v>3.8966666666666669</v>
       </c>
-      <c r="I15" s="37">
-        <f>2*PI()/H15</f>
+      <c r="I15" s="46">
+        <f t="shared" si="2"/>
         <v>1.6124513192077636</v>
       </c>
-      <c r="J15" s="42">
+      <c r="J15" s="47">
         <v>2.6000000000000001</v>
       </c>
-      <c r="K15" s="43">
+      <c r="K15" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10">
+      <c r="A16" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="39">
         <v>2.0299999999999998</v>
       </c>
       <c r="C16" s="40">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="33">
-        <f>2*PI()/B16</f>
+      <c r="D16" s="41">
+        <f t="shared" si="0"/>
         <v>3.0951651759505352</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="42">
         <v>3.0800000000000001</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="43">
         <v>3.0800000000000001</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="44">
         <v>3.1099999999999999</v>
       </c>
-      <c r="H16" s="41">
-        <f>AVERAGE(E16:G16)</f>
+      <c r="H16" s="45">
+        <f t="shared" si="1"/>
         <v>3.0899999999999999</v>
       </c>
-      <c r="I16" s="37">
-        <f>2*PI()/H16</f>
+      <c r="I16" s="46">
+        <f t="shared" si="2"/>
         <v>2.0333933032943645</v>
       </c>
-      <c r="J16" s="42">
+      <c r="J16" s="47">
         <v>3.6699999999999999</v>
       </c>
-      <c r="K16" s="43">
+      <c r="K16" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10">
+      <c r="A17" s="50">
+        <v>2.7000000000000002</v>
+      </c>
+      <c r="B17" s="51">
+        <v>2.54</v>
+      </c>
+      <c r="C17" s="52">
+        <v>1.e-002</v>
+      </c>
+      <c r="D17" s="53">
+        <f>2*PI()/B17</f>
+        <v>2.4736950028266089</v>
+      </c>
+      <c r="E17" s="51">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="F17" s="51">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="G17" s="51">
+        <v>2.46</v>
+      </c>
+      <c r="H17" s="53">
+        <f>AVERAGE(E17:G17)</f>
+        <v>2.4933333333333332</v>
+      </c>
+      <c r="I17" s="54">
+        <f>2*PI()/H17</f>
+        <v>2.5199941071575882</v>
+      </c>
+      <c r="J17" s="51">
+        <v>6.1100000000000003</v>
+      </c>
+      <c r="K17" s="48">
+        <v>1.e-002</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8">
         <v>3.2000000000000002</v>
       </c>
-      <c r="B17">
+      <c r="B18" s="39">
         <v>3.1400000000000001</v>
-      </c>
-      <c r="C17" s="40">
-        <v>1.e-002</v>
-      </c>
-      <c r="D17" s="33">
-        <f>2*PI()/B17</f>
-        <v>2.0010144290380847</v>
-      </c>
-      <c r="E17" s="45">
-        <v>2</v>
-      </c>
-      <c r="F17" s="35">
-        <v>1.99</v>
-      </c>
-      <c r="G17" s="36">
-        <v>2</v>
-      </c>
-      <c r="H17" s="41">
-        <f>AVERAGE(E17:G17)</f>
-        <v>1.9966666666666668</v>
-      </c>
-      <c r="I17" s="37">
-        <f>2*PI()/H17</f>
-        <v>3.1468373825607276</v>
-      </c>
-      <c r="J17" s="42">
-        <v>2.9900000000000002</v>
-      </c>
-      <c r="K17" s="43">
-        <v>2.e-002</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10">
-        <v>3.6000000000000001</v>
-      </c>
-      <c r="B18">
-        <v>3.6800000000000002</v>
       </c>
       <c r="C18" s="40">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="41">
         <f>2*PI()/B18</f>
-        <v>1.7073873117335832</v>
-      </c>
-      <c r="E18" s="45">
-        <v>1.7</v>
-      </c>
-      <c r="F18" s="35">
-        <v>1.71</v>
-      </c>
-      <c r="G18" s="36">
-        <v>1.71</v>
-      </c>
-      <c r="H18" s="41">
+        <v>2.0010144290380847</v>
+      </c>
+      <c r="E18" s="55">
+        <v>2</v>
+      </c>
+      <c r="F18" s="43">
+        <v>1.99</v>
+      </c>
+      <c r="G18" s="44">
+        <v>2</v>
+      </c>
+      <c r="H18" s="45">
         <f>AVERAGE(E18:G18)</f>
-        <v>1.7066666666666668</v>
-      </c>
-      <c r="I18" s="37">
+        <v>1.9966666666666668</v>
+      </c>
+      <c r="I18" s="46">
         <f>2*PI()/H18</f>
-        <v>3.6815538909255388</v>
-      </c>
-      <c r="J18" s="42">
-        <v>1.5800000000000001</v>
-      </c>
-      <c r="K18" s="43">
+        <v>3.1468373825607276</v>
+      </c>
+      <c r="J18" s="47">
+        <v>2.9900000000000002</v>
+      </c>
+      <c r="K18" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10">
-        <v>4.2000000000000002</v>
-      </c>
-      <c r="B19">
-        <v>4.3899999999999997</v>
+      <c r="A19" s="8">
+        <v>3.6000000000000001</v>
+      </c>
+      <c r="B19" s="39">
+        <v>3.6800000000000002</v>
       </c>
       <c r="C19" s="40">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="41">
         <f>2*PI()/B19</f>
-        <v>1.4312495004964889</v>
-      </c>
-      <c r="E19" s="34">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="F19" s="35">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="G19" s="36">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="H19" s="41">
+        <v>1.7073873117335832</v>
+      </c>
+      <c r="E19" s="55">
+        <v>1.7</v>
+      </c>
+      <c r="F19" s="43">
+        <v>1.71</v>
+      </c>
+      <c r="G19" s="44">
+        <v>1.71</v>
+      </c>
+      <c r="H19" s="45">
         <f>AVERAGE(E19:G19)</f>
-        <v>1.4333333333333333</v>
-      </c>
-      <c r="I19" s="37">
+        <v>1.7066666666666668</v>
+      </c>
+      <c r="I19" s="46">
         <f>2*PI()/H19</f>
-        <v>4.3836176561718041</v>
-      </c>
-      <c r="J19" s="42">
-        <v>0.89300000000000002</v>
-      </c>
-      <c r="K19" s="43">
+        <v>3.6815538909255388</v>
+      </c>
+      <c r="J19" s="47">
+        <v>1.5800000000000001</v>
+      </c>
+      <c r="K19" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="B20">
-        <v>4.75</v>
+      <c r="A20" s="8">
+        <v>4.2000000000000002</v>
+      </c>
+      <c r="B20" s="39">
+        <v>4.3899999999999997</v>
       </c>
       <c r="C20" s="40">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="41">
         <f>2*PI()/B20</f>
+        <v>1.4312495004964889</v>
+      </c>
+      <c r="E20" s="42">
+        <v>1.4399999999999999</v>
+      </c>
+      <c r="F20" s="43">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="G20" s="44">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="H20" s="45">
+        <f>AVERAGE(E20:G20)</f>
+        <v>1.4333333333333333</v>
+      </c>
+      <c r="I20" s="46">
+        <f>2*PI()/H20</f>
+        <v>4.3836176561718041</v>
+      </c>
+      <c r="J20" s="47">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="K20" s="48">
+        <v>2.e-002</v>
+      </c>
+    </row>
+    <row r="21" ht="13.15">
+      <c r="A21" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="B21" s="39">
+        <v>4.75</v>
+      </c>
+      <c r="C21" s="40">
+        <v>1.e-002</v>
+      </c>
+      <c r="D21" s="41">
+        <f>2*PI()/B21</f>
         <v>1.3227758541430708</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E21" s="42">
         <v>1.3300000000000001</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F21" s="43">
         <v>1.3300000000000001</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G21" s="44">
         <v>1.3200000000000001</v>
       </c>
-      <c r="H20" s="41">
-        <f>AVERAGE(E20:G20)</f>
+      <c r="H21" s="45">
+        <f>AVERAGE(E21:G21)</f>
         <v>1.3266666666666669</v>
       </c>
-      <c r="I20" s="37">
-        <f>2*PI()/H20</f>
+      <c r="I21" s="46">
+        <f>2*PI()/H21</f>
         <v>4.7360693270197878</v>
       </c>
-      <c r="J20" s="42">
+      <c r="J21" s="47">
         <v>0.71399999999999997</v>
       </c>
-      <c r="K20" s="43">
+      <c r="K21" s="48">
         <v>2.e-002</v>
       </c>
     </row>
-    <row r="21" ht="13.15">
-      <c r="A21" s="10">
+    <row r="22" ht="13.5">
+      <c r="A22" s="11">
         <v>4.7000000000000002</v>
       </c>
-      <c r="B21">
+      <c r="B22" s="56">
         <v>4.9500000000000002</v>
       </c>
-      <c r="C21" s="46">
+      <c r="C22" s="57">
         <v>1.e-002</v>
       </c>
-      <c r="D21" s="47">
-        <f>2*PI()/B21</f>
+      <c r="D22" s="58">
+        <f>2*PI()/B22</f>
         <v>1.2693303650867851</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E22" s="59">
         <v>1.26</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F22" s="60">
         <v>1.28</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G22" s="61">
         <v>1.2669999999999999</v>
       </c>
-      <c r="H21" s="51">
-        <f>AVERAGE(E21:G21)</f>
+      <c r="H22" s="62">
+        <f>AVERAGE(E22:G22)</f>
         <v>1.2689999999999999</v>
       </c>
-      <c r="I21" s="52">
-        <f>2*PI()/H21</f>
+      <c r="I22" s="63">
+        <f>2*PI()/H22</f>
         <v>4.9512886581399425</v>
       </c>
-      <c r="J21" s="53">
+      <c r="J22" s="64">
         <v>0.63400000000000001</v>
       </c>
-      <c r="K21" s="54">
+      <c r="K22" s="65">
         <v>2.e-002</v>
       </c>
     </row>
-    <row r="22" ht="13.5">
-      <c r="A22" s="55" t="s">
+    <row r="25" ht="12.75">
+      <c r="A25" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="57"/>
-    </row>
-    <row r="23" ht="12.75">
-      <c r="A23" s="58">
-        <v>2.7000000000000002</v>
-      </c>
-      <c r="B23" s="59">
-        <v>2.54</v>
-      </c>
-      <c r="C23" s="60">
-        <v>1.e-002</v>
-      </c>
-      <c r="D23" s="61">
-        <f>2*PI()/B23</f>
-        <v>2.4736950028266089</v>
-      </c>
-      <c r="E23" s="62">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="F23" s="59">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="G23" s="63">
-        <v>2.46</v>
-      </c>
-      <c r="H23" s="61">
-        <f>AVERAGE(E23:G23)</f>
-        <v>2.4933333333333332</v>
-      </c>
-      <c r="I23" s="64">
-        <f>2*PI()/H23</f>
-        <v>2.5199941071575882</v>
-      </c>
-      <c r="J23" s="62">
-        <v>6.1100000000000003</v>
-      </c>
-      <c r="K23" s="65">
-        <v>1.e-002</v>
-      </c>
+      <c r="B25" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -2089,613 +2112,613 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="69" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67">
+      <c r="A2" s="70">
         <v>0.25600000000000001</v>
       </c>
-      <c r="B2" s="67">
+      <c r="B2" s="70">
         <v>4.5999999999999999e-003</v>
       </c>
-      <c r="C2" s="67">
+      <c r="C2" s="70">
         <v>2.5699999999999998</v>
       </c>
-      <c r="D2" s="68">
+      <c r="D2" s="71">
         <v>4.4000000000000003e-003</v>
       </c>
-      <c r="E2" s="69">
+      <c r="E2" s="72">
         <f>SQRT(A6^2+C6^2)</f>
         <v>2.6210670338218649</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
     </row>
     <row r="3">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>0.26700000000000002</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>2.0999999999999999e-003</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>2.5899999999999999</v>
       </c>
-      <c r="D3" s="71">
+      <c r="D3" s="74">
         <v>1.9e-003</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
     </row>
     <row r="4">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>0.27400000000000002</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <f>6*10^-4</f>
         <v>5.9999999999999995e-004</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>2.6099999999999999</v>
       </c>
-      <c r="D4" s="71">
+      <c r="D4" s="74">
         <f>7*10^-4</f>
         <v>6.9999999999999988e-004</v>
       </c>
-      <c r="E4" s="69">
+      <c r="E4" s="72">
         <f>E2/2</f>
         <v>1.3105335169109325</v>
       </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
     </row>
     <row r="5" ht="13.15">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
     </row>
     <row r="6" ht="13.15">
-      <c r="A6" s="73">
+      <c r="A6" s="76">
         <f>((A2/B2^2)+(A3/B3^2)+(A4/B4^2))/((1/B2^2)+(1/B3^2)+(1/B4^2))</f>
         <v>0.27320113772034554</v>
       </c>
-      <c r="B6" s="73">
+      <c r="B6" s="76">
         <f>SQRT(1/((1/B2^2)+(1/B3^2)+(1/B4^2)))</f>
         <v>5.724299964622563e-004</v>
       </c>
-      <c r="C6" s="73">
+      <c r="C6" s="76">
         <f>((C2/D2^2)+(C3/D3^2)+(C4/D4^2))/((1/D2^2)+(1/D3^2)+(1/D4^2))</f>
         <v>2.6067898906770486</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="77">
         <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)))</f>
         <v>6.4964141370326843e-004</v>
       </c>
-      <c r="E6" s="75">
+      <c r="E6" s="78">
         <f>E2*2</f>
         <v>5.2421340676437298</v>
       </c>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
+      <c r="E7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
     </row>
     <row r="8">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <f>AVERAGE(A2:A4)</f>
         <v>0.26566666666666666</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <f>_xlfn.STDEV.S(A2:A4)/SQRT(3)</f>
         <v>5.2387445485005749e-003</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <f>AVERAGE(C2:C4)</f>
         <v>2.5899999999999999</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <f>_xlfn.STDEV.S(C2:C4)/SQRT(3)</f>
         <v>1.1547005383792526e-002</v>
       </c>
-      <c r="E8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
+      <c r="E8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
     </row>
     <row r="9" ht="12.75">
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
     </row>
     <row r="10">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="79" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="77" t="s">
+      <c r="C10" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="78" t="s">
+      <c r="D10" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="79" t="s">
+      <c r="E10" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="80"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="82" t="s">
+      <c r="F10" s="83"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="83" t="s">
+      <c r="J10" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="84" t="s">
+      <c r="K10" s="86" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="85">
+      <c r="A11" s="87">
         <v>1.8</v>
       </c>
-      <c r="B11" s="86">
+      <c r="B11" s="88">
         <v>1.3100000000000001</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="89">
         <v>1.e-002</v>
       </c>
-      <c r="D11" s="33">
-        <f>2*PI()/B11</f>
+      <c r="D11" s="41">
+        <f t="shared" ref="D11:D20" si="3">2*PI()/B11</f>
         <v>4.79632466196915</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="45">
         <v>4.8399999999999999</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="45">
         <v>4.7400000000000002</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="45">
         <v>4.8200000000000003</v>
       </c>
-      <c r="H11" s="41">
-        <f>AVERAGE(E11:G11)</f>
+      <c r="H11" s="45">
+        <f t="shared" ref="H11:H16" si="4">AVERAGE(E11:G11)</f>
         <v>4.7999999999999998</v>
       </c>
-      <c r="I11" s="87">
-        <f>2*PI()/H11</f>
+      <c r="I11" s="90">
+        <f t="shared" ref="I11:I20" si="5">2*PI()/H11</f>
         <v>1.3089969389957472</v>
       </c>
-      <c r="J11" s="86">
+      <c r="J11" s="88">
         <v>2.21</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="89">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="85">
+      <c r="A12" s="87">
         <v>1.8200000000000001</v>
       </c>
-      <c r="B12" s="71">
+      <c r="B12" s="74">
         <v>1.3600000000000001</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="91">
         <v>1.e-002</v>
       </c>
-      <c r="D12" s="33">
-        <f>2*PI()/B12</f>
+      <c r="D12" s="41">
+        <f t="shared" si="3"/>
         <v>4.6199891964555775</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="45">
         <v>4.6100000000000003</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="45">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="45">
         <v>4.6500000000000004</v>
       </c>
-      <c r="H12" s="41">
-        <f>AVERAGE(E12:G12)</f>
+      <c r="H12" s="45">
+        <f t="shared" si="4"/>
         <v>4.6200000000000001</v>
       </c>
-      <c r="I12" s="87">
-        <f>2*PI()/H12</f>
+      <c r="I12" s="90">
+        <f t="shared" si="5"/>
         <v>1.3599968197358412</v>
       </c>
-      <c r="J12" s="71">
+      <c r="J12" s="74">
         <v>2.2400000000000002</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="91">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="85">
+      <c r="A13" s="87">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B13" s="71">
+      <c r="B13" s="74">
         <v>1.9099999999999999</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="91">
         <v>1.e-002</v>
       </c>
-      <c r="D13" s="33">
-        <f>2*PI()/B13</f>
+      <c r="D13" s="41">
+        <f t="shared" si="3"/>
         <v>3.2896258152772706</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="45">
         <v>3.2999999999999998</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="45">
         <v>3.29</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="45">
         <v>3.29</v>
       </c>
-      <c r="H13" s="41">
-        <f>AVERAGE(E13:G13)</f>
+      <c r="H13" s="45">
+        <f t="shared" si="4"/>
         <v>3.293333333333333</v>
       </c>
-      <c r="I13" s="87">
-        <f>2*PI()/H13</f>
+      <c r="I13" s="90">
+        <f t="shared" si="5"/>
         <v>1.9078497896294293</v>
       </c>
-      <c r="J13" s="71">
+      <c r="J13" s="74">
         <v>3.3799999999999999</v>
       </c>
-      <c r="K13" s="43">
+      <c r="K13" s="91">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="85">
+      <c r="A14" s="87">
         <v>3.3999999999999999</v>
       </c>
-      <c r="B14" s="71">
+      <c r="B14" s="74">
         <v>3.3799999999999999</v>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="91">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="33">
-        <f>2*PI()/B14</f>
+      <c r="D14" s="41">
+        <f t="shared" si="3"/>
         <v>1.8589305642543155</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="45">
         <v>1.8600000000000001</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="45">
         <v>1.8600000000000001</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="45">
         <v>1.8500000000000001</v>
       </c>
-      <c r="H14" s="41">
-        <f>AVERAGE(E14:G14)</f>
+      <c r="H14" s="45">
+        <f t="shared" si="4"/>
         <v>1.8566666666666667</v>
       </c>
-      <c r="I14" s="87">
-        <f>2*PI()/H14</f>
+      <c r="I14" s="90">
+        <f t="shared" si="5"/>
         <v>3.384121350366025</v>
       </c>
-      <c r="J14" s="71">
+      <c r="J14" s="74">
         <v>2.3599999999999999</v>
       </c>
-      <c r="K14" s="43">
+      <c r="K14" s="91">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="85">
+      <c r="A15" s="87">
         <v>3.7999999999999998</v>
       </c>
-      <c r="B15" s="71">
+      <c r="B15" s="74">
         <v>3.8900000000000001</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="91">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="33">
-        <f>2*PI()/B15</f>
+      <c r="D15" s="41">
+        <f t="shared" si="3"/>
         <v>1.6152147319227728</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="45">
         <v>1.6200000000000001</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="45">
         <v>1.6200000000000001</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="45">
         <v>1.6100000000000001</v>
       </c>
-      <c r="H15" s="41">
-        <f>AVERAGE(E15:G15)</f>
+      <c r="H15" s="45">
+        <f t="shared" si="4"/>
         <v>1.6166666666666669</v>
       </c>
-      <c r="I15" s="87">
-        <f>2*PI()/H15</f>
+      <c r="I15" s="90">
+        <f t="shared" si="5"/>
         <v>3.8865063755750011</v>
       </c>
-      <c r="J15" s="71">
+      <c r="J15" s="74">
         <v>1.3600000000000001</v>
       </c>
-      <c r="K15" s="43">
+      <c r="K15" s="91">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="16" ht="13.15">
-      <c r="A16" s="85">
+      <c r="A16" s="87">
         <v>4</v>
       </c>
-      <c r="B16" s="71">
+      <c r="B16" s="74">
         <v>4.0599999999999996</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="91">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="33">
-        <f>2*PI()/B16</f>
+      <c r="D16" s="41">
+        <f t="shared" si="3"/>
         <v>1.5475825879752676</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="45">
         <v>1.54</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="45">
         <v>1.55</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="45">
         <v>1.55</v>
       </c>
-      <c r="H16" s="41">
-        <f>AVERAGE(E16:G16)</f>
+      <c r="H16" s="45">
+        <f t="shared" si="4"/>
         <v>1.5466666666666666</v>
       </c>
-      <c r="I16" s="87">
-        <f>2*PI()/H16</f>
+      <c r="I16" s="90">
+        <f t="shared" si="5"/>
         <v>4.062404293435077</v>
       </c>
-      <c r="J16" s="71">
+      <c r="J16" s="74">
         <v>1.1699999999999999</v>
       </c>
-      <c r="K16" s="43">
+      <c r="K16" s="91">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" s="85">
+      <c r="A17" s="87">
         <v>4.2999999999999998</v>
       </c>
-      <c r="B17" s="42">
+      <c r="B17" s="47">
         <v>4.5</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="91">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="33">
-        <f>2*PI()/B17</f>
+      <c r="D17" s="41">
+        <f t="shared" si="3"/>
         <v>1.3962634015954636</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="45">
         <v>1.3999999999999999</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="45">
         <v>1.3999999999999999</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="45">
         <v>1.3999999999999999</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="45">
         <f>AVERAGE(F17:G17)</f>
         <v>1.3999999999999999</v>
       </c>
-      <c r="I17" s="87">
-        <f>2*PI()/H17</f>
+      <c r="I17" s="90">
+        <f t="shared" si="5"/>
         <v>4.4879895051282759</v>
       </c>
-      <c r="J17" s="71">
+      <c r="J17" s="74">
         <v>0.84499999999999997</v>
       </c>
-      <c r="K17" s="43">
+      <c r="K17" s="91">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="18" ht="12.75">
-      <c r="A18" s="85">
+      <c r="A18" s="87">
         <v>4.5999999999999996</v>
       </c>
-      <c r="B18" s="71">
+      <c r="B18" s="74">
         <v>4.8799999999999999</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="91">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="33">
-        <f>2*PI()/B18</f>
+      <c r="D18" s="41">
+        <f t="shared" si="3"/>
         <v>1.2875379727827021</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="45">
         <v>1.3</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="45">
         <v>1.29</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="45">
         <v>1.28</v>
       </c>
-      <c r="H18" s="41">
-        <f>AVERAGE(E18:G18)</f>
+      <c r="H18" s="45">
+        <f t="shared" ref="H18:H20" si="6">AVERAGE(E18:G18)</f>
         <v>1.29</v>
       </c>
-      <c r="I18" s="87">
-        <f>2*PI()/H18</f>
+      <c r="I18" s="90">
+        <f t="shared" si="5"/>
         <v>4.8706862846353376</v>
       </c>
-      <c r="J18" s="71">
+      <c r="J18" s="74">
         <v>0.67300000000000004</v>
       </c>
-      <c r="K18" s="43">
+      <c r="K18" s="91">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="19" ht="12.75">
-      <c r="A19" s="85">
+      <c r="A19" s="87">
         <v>4.7999999999999998</v>
       </c>
-      <c r="B19" s="71">
+      <c r="B19" s="74">
         <v>5.1100000000000003</v>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="91">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="33">
-        <f>2*PI()/B19</f>
+      <c r="D19" s="41">
+        <f t="shared" si="3"/>
         <v>1.2295861657885687</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="45">
         <v>1.22</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="45">
         <v>1.23</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="45">
         <v>1.23</v>
       </c>
-      <c r="H19" s="41">
-        <f>AVERAGE(E19:G19)</f>
+      <c r="H19" s="45">
+        <f t="shared" si="6"/>
         <v>1.2266666666666668</v>
       </c>
-      <c r="I19" s="87">
-        <f>2*PI()/H19</f>
+      <c r="I19" s="90">
+        <f t="shared" si="5"/>
         <v>5.122161935200749</v>
       </c>
-      <c r="J19" s="71">
+      <c r="J19" s="74">
         <v>0.59299999999999997</v>
       </c>
-      <c r="K19" s="43">
+      <c r="K19" s="91">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="20" ht="12.75">
-      <c r="A20" s="88">
+      <c r="A20" s="92">
         <v>4.9000000000000004</v>
       </c>
-      <c r="B20" s="89">
+      <c r="B20" s="93">
         <v>5.2300000000000004</v>
       </c>
-      <c r="C20" s="90">
+      <c r="C20" s="94">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="91">
-        <f>2*PI()/B20</f>
+      <c r="D20" s="58">
+        <f t="shared" si="3"/>
         <v>1.2013738637054656</v>
       </c>
-      <c r="E20" s="92">
+      <c r="E20" s="62">
         <v>1.2</v>
       </c>
-      <c r="F20" s="92">
+      <c r="F20" s="62">
         <v>1.2</v>
       </c>
-      <c r="G20" s="92">
+      <c r="G20" s="62">
         <v>1.2</v>
       </c>
-      <c r="H20" s="92">
-        <f>AVERAGE(E20:G20)</f>
+      <c r="H20" s="62">
+        <f t="shared" si="6"/>
         <v>1.2</v>
       </c>
-      <c r="I20" s="93">
-        <f>2*PI()/H20</f>
+      <c r="I20" s="95">
+        <f t="shared" si="5"/>
         <v>5.2359877559829888</v>
       </c>
-      <c r="J20" s="89">
+      <c r="J20" s="93">
         <v>0.55700000000000005</v>
       </c>
-      <c r="K20" s="90">
+      <c r="K20" s="94">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="23">
-      <c r="N23" s="94"/>
+      <c r="N23" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -562,28 +562,6 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="none"/>
       <right style="thin">
         <color theme="1"/>
@@ -673,6 +651,28 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -919,36 +919,36 @@
     <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="42" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="4" borderId="41" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="43" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="43" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="43" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="43" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="46" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -982,7 +982,7 @@
     <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="56" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1852,76 +1852,76 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50">
-        <v>2.7000000000000002</v>
-      </c>
-      <c r="B17" s="51">
-        <v>2.54</v>
-      </c>
-      <c r="C17" s="52">
+      <c r="A17" s="8">
+        <v>3.2000000000000002</v>
+      </c>
+      <c r="B17" s="39">
+        <v>3.1400000000000001</v>
+      </c>
+      <c r="C17" s="40">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="41">
         <f>2*PI()/B17</f>
-        <v>2.4736950028266089</v>
-      </c>
-      <c r="E17" s="51">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="F17" s="51">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="G17" s="51">
-        <v>2.46</v>
-      </c>
-      <c r="H17" s="53">
+        <v>2.0010144290380847</v>
+      </c>
+      <c r="E17" s="50">
+        <v>2</v>
+      </c>
+      <c r="F17" s="43">
+        <v>1.99</v>
+      </c>
+      <c r="G17" s="44">
+        <v>2</v>
+      </c>
+      <c r="H17" s="45">
         <f>AVERAGE(E17:G17)</f>
-        <v>2.4933333333333332</v>
-      </c>
-      <c r="I17" s="54">
+        <v>1.9966666666666668</v>
+      </c>
+      <c r="I17" s="46">
         <f>2*PI()/H17</f>
-        <v>2.5199941071575882</v>
-      </c>
-      <c r="J17" s="51">
-        <v>6.1100000000000003</v>
+        <v>3.1468373825607276</v>
+      </c>
+      <c r="J17" s="47">
+        <v>2.9900000000000002</v>
       </c>
       <c r="K17" s="48">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8">
-        <v>3.2000000000000002</v>
+        <v>3.6000000000000001</v>
       </c>
       <c r="B18" s="39">
-        <v>3.1400000000000001</v>
+        <v>3.6800000000000002</v>
       </c>
       <c r="C18" s="40">
         <v>1.e-002</v>
       </c>
       <c r="D18" s="41">
         <f>2*PI()/B18</f>
-        <v>2.0010144290380847</v>
-      </c>
-      <c r="E18" s="55">
-        <v>2</v>
+        <v>1.7073873117335832</v>
+      </c>
+      <c r="E18" s="50">
+        <v>1.7</v>
       </c>
       <c r="F18" s="43">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="G18" s="44">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="H18" s="45">
         <f>AVERAGE(E18:G18)</f>
-        <v>1.9966666666666668</v>
+        <v>1.7066666666666668</v>
       </c>
       <c r="I18" s="46">
         <f>2*PI()/H18</f>
-        <v>3.1468373825607276</v>
+        <v>3.6815538909255388</v>
       </c>
       <c r="J18" s="47">
-        <v>2.9900000000000002</v>
+        <v>1.5800000000000001</v>
       </c>
       <c r="K18" s="48">
         <v>2.e-002</v>
@@ -1929,37 +1929,37 @@
     </row>
     <row r="19">
       <c r="A19" s="8">
-        <v>3.6000000000000001</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="B19" s="39">
-        <v>3.6800000000000002</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="C19" s="40">
         <v>1.e-002</v>
       </c>
       <c r="D19" s="41">
         <f>2*PI()/B19</f>
-        <v>1.7073873117335832</v>
-      </c>
-      <c r="E19" s="55">
-        <v>1.7</v>
+        <v>1.4312495004964889</v>
+      </c>
+      <c r="E19" s="42">
+        <v>1.4399999999999999</v>
       </c>
       <c r="F19" s="43">
-        <v>1.71</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="G19" s="44">
-        <v>1.71</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H19" s="45">
         <f>AVERAGE(E19:G19)</f>
-        <v>1.7066666666666668</v>
+        <v>1.4333333333333333</v>
       </c>
       <c r="I19" s="46">
         <f>2*PI()/H19</f>
-        <v>3.6815538909255388</v>
+        <v>4.3836176561718041</v>
       </c>
       <c r="J19" s="47">
-        <v>1.5800000000000001</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="K19" s="48">
         <v>2.e-002</v>
@@ -1967,123 +1967,124 @@
     </row>
     <row r="20">
       <c r="A20" s="8">
-        <v>4.2000000000000002</v>
+        <v>4.5</v>
       </c>
       <c r="B20" s="39">
-        <v>4.3899999999999997</v>
+        <v>4.75</v>
       </c>
       <c r="C20" s="40">
         <v>1.e-002</v>
       </c>
       <c r="D20" s="41">
         <f>2*PI()/B20</f>
-        <v>1.4312495004964889</v>
+        <v>1.3227758541430708</v>
       </c>
       <c r="E20" s="42">
-        <v>1.4399999999999999</v>
+        <v>1.3300000000000001</v>
       </c>
       <c r="F20" s="43">
-        <v>1.4299999999999999</v>
+        <v>1.3300000000000001</v>
       </c>
       <c r="G20" s="44">
-        <v>1.4299999999999999</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="H20" s="45">
         <f>AVERAGE(E20:G20)</f>
-        <v>1.4333333333333333</v>
+        <v>1.3266666666666669</v>
       </c>
       <c r="I20" s="46">
         <f>2*PI()/H20</f>
-        <v>4.3836176561718041</v>
+        <v>4.7360693270197878</v>
       </c>
       <c r="J20" s="47">
-        <v>0.89300000000000002</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="K20" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="21" ht="13.15">
-      <c r="A21" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="B21" s="39">
-        <v>4.75</v>
-      </c>
-      <c r="C21" s="40">
+      <c r="A21" s="11">
+        <v>4.7000000000000002</v>
+      </c>
+      <c r="B21" s="51">
+        <v>4.9500000000000002</v>
+      </c>
+      <c r="C21" s="52">
         <v>1.e-002</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="53">
         <f>2*PI()/B21</f>
-        <v>1.3227758541430708</v>
-      </c>
-      <c r="E21" s="42">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="F21" s="43">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="G21" s="44">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="H21" s="45">
+        <v>1.2693303650867851</v>
+      </c>
+      <c r="E21" s="54">
+        <v>1.26</v>
+      </c>
+      <c r="F21" s="55">
+        <v>1.28</v>
+      </c>
+      <c r="G21" s="56">
+        <v>1.2669999999999999</v>
+      </c>
+      <c r="H21" s="57">
         <f>AVERAGE(E21:G21)</f>
-        <v>1.3266666666666669</v>
-      </c>
-      <c r="I21" s="46">
+        <v>1.2689999999999999</v>
+      </c>
+      <c r="I21" s="58">
         <f>2*PI()/H21</f>
-        <v>4.7360693270197878</v>
-      </c>
-      <c r="J21" s="47">
-        <v>0.71399999999999997</v>
-      </c>
-      <c r="K21" s="48">
+        <v>4.9512886581399425</v>
+      </c>
+      <c r="J21" s="59">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="K21" s="60">
         <v>2.e-002</v>
       </c>
     </row>
-    <row r="22" ht="13.5">
-      <c r="A22" s="11">
-        <v>4.7000000000000002</v>
-      </c>
-      <c r="B22" s="56">
-        <v>4.9500000000000002</v>
-      </c>
-      <c r="C22" s="57">
+    <row r="22" ht="13.5"/>
+    <row r="25" ht="12.75">
+      <c r="A25" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="62"/>
+    </row>
+    <row r="27" ht="12.75">
+      <c r="A27" s="63">
+        <v>2.7000000000000002</v>
+      </c>
+      <c r="B27" s="64">
+        <v>2.54</v>
+      </c>
+      <c r="C27" s="65">
         <v>1.e-002</v>
       </c>
-      <c r="D22" s="58">
-        <f>2*PI()/B22</f>
-        <v>1.2693303650867851</v>
-      </c>
-      <c r="E22" s="59">
-        <v>1.26</v>
-      </c>
-      <c r="F22" s="60">
-        <v>1.28</v>
-      </c>
-      <c r="G22" s="61">
-        <v>1.2669999999999999</v>
-      </c>
-      <c r="H22" s="62">
-        <f>AVERAGE(E22:G22)</f>
-        <v>1.2689999999999999</v>
-      </c>
-      <c r="I22" s="63">
-        <f>2*PI()/H22</f>
-        <v>4.9512886581399425</v>
-      </c>
-      <c r="J22" s="64">
-        <v>0.63400000000000001</v>
-      </c>
-      <c r="K22" s="65">
-        <v>2.e-002</v>
-      </c>
-    </row>
-    <row r="25" ht="12.75">
-      <c r="A25" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="67"/>
+      <c r="D27" s="66">
+        <f>2*PI()/B27</f>
+        <v>2.4736950028266089</v>
+      </c>
+      <c r="E27" s="64">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="F27" s="64">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="G27" s="64">
+        <v>2.46</v>
+      </c>
+      <c r="H27" s="66">
+        <f>AVERAGE(E27:G27)</f>
+        <v>2.4933333333333332</v>
+      </c>
+      <c r="I27" s="67">
+        <f>2*PI()/H27</f>
+        <v>2.5199941071575882</v>
+      </c>
+      <c r="J27" s="64">
+        <v>6.1100000000000003</v>
+      </c>
+      <c r="K27" s="48">
+        <v>1.e-002</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2689,20 +2690,20 @@
       <c r="C20" s="94">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="58">
+      <c r="D20" s="53">
         <f t="shared" si="3"/>
         <v>1.2013738637054656</v>
       </c>
-      <c r="E20" s="62">
+      <c r="E20" s="57">
         <v>1.2</v>
       </c>
-      <c r="F20" s="62">
+      <c r="F20" s="57">
         <v>1.2</v>
       </c>
-      <c r="G20" s="62">
+      <c r="G20" s="57">
         <v>1.2</v>
       </c>
-      <c r="H20" s="62">
+      <c r="H20" s="57">
         <f t="shared" si="6"/>
         <v>1.2</v>
       </c>

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -160,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="57">
+  <borders count="56">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -615,19 +615,6 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="medium">
         <color theme="1"/>
       </left>
@@ -850,7 +837,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="96">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -937,35 +924,34 @@
     <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="36" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="37" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="4" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="41" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="43" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="43" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="43" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="43" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="45" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="46" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="47" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="48" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="47" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="51" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="52" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="51" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="52" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="53" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="55" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -974,13 +960,13 @@
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="55" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="56" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="55" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -1734,7 +1720,7 @@
         <v>2.1600000000000001</v>
       </c>
       <c r="K13" s="38">
-        <v>2.e-002</v>
+        <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="14">
@@ -1772,7 +1758,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="K14" s="48">
-        <v>2.e-002</v>
+        <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="15">
@@ -1810,7 +1796,7 @@
         <v>2.6000000000000001</v>
       </c>
       <c r="K15" s="48">
-        <v>2.e-002</v>
+        <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="16">
@@ -1848,7 +1834,7 @@
         <v>3.6699999999999999</v>
       </c>
       <c r="K16" s="48">
-        <v>2.e-002</v>
+        <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="17">
@@ -1886,7 +1872,7 @@
         <v>2.9900000000000002</v>
       </c>
       <c r="K17" s="48">
-        <v>2.e-002</v>
+        <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="18">
@@ -1924,7 +1910,7 @@
         <v>1.5800000000000001</v>
       </c>
       <c r="K18" s="48">
-        <v>2.e-002</v>
+        <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="19">
@@ -1962,7 +1948,7 @@
         <v>0.89300000000000002</v>
       </c>
       <c r="K19" s="48">
-        <v>2.e-002</v>
+        <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="20">
@@ -2000,7 +1986,7 @@
         <v>0.71399999999999997</v>
       </c>
       <c r="K20" s="48">
-        <v>2.e-002</v>
+        <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="21" ht="13.15">
@@ -2037,49 +2023,49 @@
       <c r="J21" s="59">
         <v>0.63400000000000001</v>
       </c>
-      <c r="K21" s="60">
-        <v>2.e-002</v>
+      <c r="K21" s="48">
+        <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="22" ht="13.5"/>
     <row r="25" ht="12.75">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="62"/>
+      <c r="B25" s="61"/>
     </row>
     <row r="27" ht="12.75">
-      <c r="A27" s="63">
+      <c r="A27" s="62">
         <v>2.7000000000000002</v>
       </c>
-      <c r="B27" s="64">
+      <c r="B27" s="63">
         <v>2.54</v>
       </c>
-      <c r="C27" s="65">
+      <c r="C27" s="64">
         <v>1.e-002</v>
       </c>
-      <c r="D27" s="66">
+      <c r="D27" s="65">
         <f>2*PI()/B27</f>
         <v>2.4736950028266089</v>
       </c>
-      <c r="E27" s="64">
+      <c r="E27" s="63">
         <v>2.5099999999999998</v>
       </c>
-      <c r="F27" s="64">
+      <c r="F27" s="63">
         <v>2.5099999999999998</v>
       </c>
-      <c r="G27" s="64">
+      <c r="G27" s="63">
         <v>2.46</v>
       </c>
-      <c r="H27" s="66">
+      <c r="H27" s="65">
         <f>AVERAGE(E27:G27)</f>
         <v>2.4933333333333332</v>
       </c>
-      <c r="I27" s="67">
+      <c r="I27" s="66">
         <f>2*PI()/H27</f>
         <v>2.5199941071575882</v>
       </c>
-      <c r="J27" s="64">
+      <c r="J27" s="63">
         <v>6.1100000000000003</v>
       </c>
       <c r="K27" s="48">
@@ -2113,45 +2099,45 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="69" t="s">
+      <c r="E1" s="68" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="70">
+      <c r="A2" s="69">
         <v>0.25600000000000001</v>
       </c>
-      <c r="B2" s="70">
+      <c r="B2" s="69">
         <v>4.5999999999999999e-003</v>
       </c>
-      <c r="C2" s="70">
+      <c r="C2" s="69">
         <v>2.5699999999999998</v>
       </c>
-      <c r="D2" s="71">
+      <c r="D2" s="70">
         <v>4.4000000000000003e-003</v>
       </c>
-      <c r="E2" s="72">
+      <c r="E2" s="71">
         <f>SQRT(A6^2+C6^2)</f>
         <v>2.6210670338218649</v>
       </c>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2163,18 +2149,18 @@
       <c r="C3" s="9">
         <v>2.5899999999999999</v>
       </c>
-      <c r="D3" s="74">
+      <c r="D3" s="73">
         <v>1.9e-003</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2187,20 +2173,20 @@
       <c r="C4" s="9">
         <v>2.6099999999999999</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="73">
         <f>7*10^-4</f>
         <v>6.9999999999999988e-004</v>
       </c>
-      <c r="E4" s="72">
+      <c r="E4" s="71">
         <f>E2/2</f>
         <v>1.3105335169109325</v>
       </c>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
     </row>
     <row r="5" ht="13.15">
       <c r="A5" s="14" t="s">
@@ -2215,43 +2201,43 @@
       <c r="D5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="75" t="s">
+      <c r="E5" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
     </row>
     <row r="6" ht="13.15">
-      <c r="A6" s="76">
+      <c r="A6" s="75">
         <f>((A2/B2^2)+(A3/B3^2)+(A4/B4^2))/((1/B2^2)+(1/B3^2)+(1/B4^2))</f>
         <v>0.27320113772034554</v>
       </c>
-      <c r="B6" s="76">
+      <c r="B6" s="75">
         <f>SQRT(1/((1/B2^2)+(1/B3^2)+(1/B4^2)))</f>
         <v>5.724299964622563e-004</v>
       </c>
-      <c r="C6" s="76">
+      <c r="C6" s="75">
         <f>((C2/D2^2)+(C3/D3^2)+(C4/D4^2))/((1/D2^2)+(1/D3^2)+(1/D4^2))</f>
         <v>2.6067898906770486</v>
       </c>
-      <c r="D6" s="77">
+      <c r="D6" s="76">
         <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)))</f>
         <v>6.4964141370326843e-004</v>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="77">
         <f>E2*2</f>
         <v>5.2421340676437298</v>
       </c>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
@@ -2266,13 +2252,13 @@
       <c r="D7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
+      <c r="E7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
     </row>
     <row r="8">
       <c r="A8" s="18">
@@ -2291,61 +2277,61 @@
         <f>_xlfn.STDEV.S(C2:C4)/SQRT(3)</f>
         <v>1.1547005383792526e-002</v>
       </c>
-      <c r="E8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="73"/>
-      <c r="L8" s="73"/>
+      <c r="E8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
     </row>
     <row r="9" ht="12.75">
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="73"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
     </row>
     <row r="10">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="78" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="80" t="s">
+      <c r="C10" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="81" t="s">
+      <c r="D10" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="82" t="s">
+      <c r="E10" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="83"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="81" t="s">
+      <c r="F10" s="82"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="80" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="85" t="s">
+      <c r="J10" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="86" t="s">
+      <c r="K10" s="85" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="87">
+      <c r="A11" s="86">
         <v>1.8</v>
       </c>
-      <c r="B11" s="88">
+      <c r="B11" s="87">
         <v>1.3100000000000001</v>
       </c>
-      <c r="C11" s="89">
+      <c r="C11" s="88">
         <v>1.e-002</v>
       </c>
       <c r="D11" s="41">
@@ -2365,25 +2351,25 @@
         <f t="shared" ref="H11:H16" si="4">AVERAGE(E11:G11)</f>
         <v>4.7999999999999998</v>
       </c>
-      <c r="I11" s="90">
+      <c r="I11" s="89">
         <f t="shared" ref="I11:I20" si="5">2*PI()/H11</f>
         <v>1.3089969389957472</v>
       </c>
-      <c r="J11" s="88">
+      <c r="J11" s="87">
         <v>2.21</v>
       </c>
-      <c r="K11" s="89">
+      <c r="K11" s="88">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="87">
+      <c r="A12" s="86">
         <v>1.8200000000000001</v>
       </c>
-      <c r="B12" s="74">
+      <c r="B12" s="73">
         <v>1.3600000000000001</v>
       </c>
-      <c r="C12" s="91">
+      <c r="C12" s="90">
         <v>1.e-002</v>
       </c>
       <c r="D12" s="41">
@@ -2403,25 +2389,25 @@
         <f t="shared" si="4"/>
         <v>4.6200000000000001</v>
       </c>
-      <c r="I12" s="90">
+      <c r="I12" s="89">
         <f t="shared" si="5"/>
         <v>1.3599968197358412</v>
       </c>
-      <c r="J12" s="74">
+      <c r="J12" s="73">
         <v>2.2400000000000002</v>
       </c>
-      <c r="K12" s="91">
+      <c r="K12" s="90">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="87">
+      <c r="A13" s="86">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B13" s="74">
+      <c r="B13" s="73">
         <v>1.9099999999999999</v>
       </c>
-      <c r="C13" s="91">
+      <c r="C13" s="90">
         <v>1.e-002</v>
       </c>
       <c r="D13" s="41">
@@ -2441,25 +2427,25 @@
         <f t="shared" si="4"/>
         <v>3.293333333333333</v>
       </c>
-      <c r="I13" s="90">
+      <c r="I13" s="89">
         <f t="shared" si="5"/>
         <v>1.9078497896294293</v>
       </c>
-      <c r="J13" s="74">
+      <c r="J13" s="73">
         <v>3.3799999999999999</v>
       </c>
-      <c r="K13" s="91">
+      <c r="K13" s="90">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="87">
+      <c r="A14" s="86">
         <v>3.3999999999999999</v>
       </c>
-      <c r="B14" s="74">
+      <c r="B14" s="73">
         <v>3.3799999999999999</v>
       </c>
-      <c r="C14" s="91">
+      <c r="C14" s="90">
         <v>1.e-002</v>
       </c>
       <c r="D14" s="41">
@@ -2479,25 +2465,25 @@
         <f t="shared" si="4"/>
         <v>1.8566666666666667</v>
       </c>
-      <c r="I14" s="90">
+      <c r="I14" s="89">
         <f t="shared" si="5"/>
         <v>3.384121350366025</v>
       </c>
-      <c r="J14" s="74">
+      <c r="J14" s="73">
         <v>2.3599999999999999</v>
       </c>
-      <c r="K14" s="91">
+      <c r="K14" s="90">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="87">
+      <c r="A15" s="86">
         <v>3.7999999999999998</v>
       </c>
-      <c r="B15" s="74">
+      <c r="B15" s="73">
         <v>3.8900000000000001</v>
       </c>
-      <c r="C15" s="91">
+      <c r="C15" s="90">
         <v>1.e-002</v>
       </c>
       <c r="D15" s="41">
@@ -2517,25 +2503,25 @@
         <f t="shared" si="4"/>
         <v>1.6166666666666669</v>
       </c>
-      <c r="I15" s="90">
+      <c r="I15" s="89">
         <f t="shared" si="5"/>
         <v>3.8865063755750011</v>
       </c>
-      <c r="J15" s="74">
+      <c r="J15" s="73">
         <v>1.3600000000000001</v>
       </c>
-      <c r="K15" s="91">
+      <c r="K15" s="90">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="16" ht="13.15">
-      <c r="A16" s="87">
+      <c r="A16" s="86">
         <v>4</v>
       </c>
-      <c r="B16" s="74">
+      <c r="B16" s="73">
         <v>4.0599999999999996</v>
       </c>
-      <c r="C16" s="91">
+      <c r="C16" s="90">
         <v>1.e-002</v>
       </c>
       <c r="D16" s="41">
@@ -2555,25 +2541,25 @@
         <f t="shared" si="4"/>
         <v>1.5466666666666666</v>
       </c>
-      <c r="I16" s="90">
+      <c r="I16" s="89">
         <f t="shared" si="5"/>
         <v>4.062404293435077</v>
       </c>
-      <c r="J16" s="74">
+      <c r="J16" s="73">
         <v>1.1699999999999999</v>
       </c>
-      <c r="K16" s="91">
+      <c r="K16" s="90">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" s="87">
+      <c r="A17" s="86">
         <v>4.2999999999999998</v>
       </c>
       <c r="B17" s="47">
         <v>4.5</v>
       </c>
-      <c r="C17" s="91">
+      <c r="C17" s="90">
         <v>1.e-002</v>
       </c>
       <c r="D17" s="41">
@@ -2593,25 +2579,25 @@
         <f>AVERAGE(F17:G17)</f>
         <v>1.3999999999999999</v>
       </c>
-      <c r="I17" s="90">
+      <c r="I17" s="89">
         <f t="shared" si="5"/>
         <v>4.4879895051282759</v>
       </c>
-      <c r="J17" s="74">
+      <c r="J17" s="73">
         <v>0.84499999999999997</v>
       </c>
-      <c r="K17" s="91">
+      <c r="K17" s="90">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="18" ht="12.75">
-      <c r="A18" s="87">
+      <c r="A18" s="86">
         <v>4.5999999999999996</v>
       </c>
-      <c r="B18" s="74">
+      <c r="B18" s="73">
         <v>4.8799999999999999</v>
       </c>
-      <c r="C18" s="91">
+      <c r="C18" s="90">
         <v>1.e-002</v>
       </c>
       <c r="D18" s="41">
@@ -2631,25 +2617,25 @@
         <f t="shared" ref="H18:H20" si="6">AVERAGE(E18:G18)</f>
         <v>1.29</v>
       </c>
-      <c r="I18" s="90">
+      <c r="I18" s="89">
         <f t="shared" si="5"/>
         <v>4.8706862846353376</v>
       </c>
-      <c r="J18" s="74">
+      <c r="J18" s="73">
         <v>0.67300000000000004</v>
       </c>
-      <c r="K18" s="91">
+      <c r="K18" s="90">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="19" ht="12.75">
-      <c r="A19" s="87">
+      <c r="A19" s="86">
         <v>4.7999999999999998</v>
       </c>
-      <c r="B19" s="74">
+      <c r="B19" s="73">
         <v>5.1100000000000003</v>
       </c>
-      <c r="C19" s="91">
+      <c r="C19" s="90">
         <v>1.e-002</v>
       </c>
       <c r="D19" s="41">
@@ -2669,25 +2655,25 @@
         <f t="shared" si="6"/>
         <v>1.2266666666666668</v>
       </c>
-      <c r="I19" s="90">
+      <c r="I19" s="89">
         <f t="shared" si="5"/>
         <v>5.122161935200749</v>
       </c>
-      <c r="J19" s="74">
+      <c r="J19" s="73">
         <v>0.59299999999999997</v>
       </c>
-      <c r="K19" s="91">
+      <c r="K19" s="90">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="20" ht="12.75">
-      <c r="A20" s="92">
+      <c r="A20" s="91">
         <v>4.9000000000000004</v>
       </c>
-      <c r="B20" s="93">
+      <c r="B20" s="92">
         <v>5.2300000000000004</v>
       </c>
-      <c r="C20" s="94">
+      <c r="C20" s="93">
         <v>1.e-002</v>
       </c>
       <c r="D20" s="53">
@@ -2707,19 +2693,19 @@
         <f t="shared" si="6"/>
         <v>1.2</v>
       </c>
-      <c r="I20" s="95">
+      <c r="I20" s="94">
         <f t="shared" si="5"/>
         <v>5.2359877559829888</v>
       </c>
-      <c r="J20" s="93">
+      <c r="J20" s="92">
         <v>0.55700000000000005</v>
       </c>
-      <c r="K20" s="94">
+      <c r="K20" s="93">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="23">
-      <c r="N23" s="96"/>
+      <c r="N23" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -562,6 +562,28 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="none"/>
       <right style="thin">
         <color theme="1"/>
@@ -638,28 +660,6 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -906,35 +906,35 @@
     <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="41" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="4" borderId="42" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="42" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="42" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="45" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -968,7 +968,7 @@
     <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="55" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1838,38 +1838,38 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8">
-        <v>3.2000000000000002</v>
-      </c>
-      <c r="B17" s="39">
-        <v>3.1400000000000001</v>
-      </c>
-      <c r="C17" s="40">
+      <c r="A17" s="50">
+        <v>2.7000000000000002</v>
+      </c>
+      <c r="B17" s="51">
+        <v>2.54</v>
+      </c>
+      <c r="C17" s="52">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="53">
         <f>2*PI()/B17</f>
-        <v>2.0010144290380847</v>
-      </c>
-      <c r="E17" s="50">
-        <v>2</v>
-      </c>
-      <c r="F17" s="43">
-        <v>1.99</v>
-      </c>
-      <c r="G17" s="44">
-        <v>2</v>
-      </c>
-      <c r="H17" s="45">
+        <v>2.4736950028266089</v>
+      </c>
+      <c r="E17" s="51">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="F17" s="51">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="G17" s="51">
+        <v>2.46</v>
+      </c>
+      <c r="H17" s="53">
         <f>AVERAGE(E17:G17)</f>
-        <v>1.9966666666666668</v>
-      </c>
-      <c r="I17" s="46">
+        <v>2.4933333333333332</v>
+      </c>
+      <c r="I17" s="54">
         <f>2*PI()/H17</f>
-        <v>3.1468373825607276</v>
-      </c>
-      <c r="J17" s="47">
-        <v>2.9900000000000002</v>
+        <v>2.5199941071575882</v>
+      </c>
+      <c r="J17" s="51">
+        <v>6.1100000000000003</v>
       </c>
       <c r="K17" s="48">
         <v>2.9999999999999999e-002</v>
@@ -1877,37 +1877,37 @@
     </row>
     <row r="18">
       <c r="A18" s="8">
-        <v>3.6000000000000001</v>
+        <v>3.2000000000000002</v>
       </c>
       <c r="B18" s="39">
-        <v>3.6800000000000002</v>
+        <v>3.1400000000000001</v>
       </c>
       <c r="C18" s="40">
         <v>1.e-002</v>
       </c>
       <c r="D18" s="41">
         <f>2*PI()/B18</f>
-        <v>1.7073873117335832</v>
-      </c>
-      <c r="E18" s="50">
-        <v>1.7</v>
+        <v>2.0010144290380847</v>
+      </c>
+      <c r="E18" s="55">
+        <v>2</v>
       </c>
       <c r="F18" s="43">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="G18" s="44">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="H18" s="45">
         <f>AVERAGE(E18:G18)</f>
-        <v>1.7066666666666668</v>
+        <v>1.9966666666666668</v>
       </c>
       <c r="I18" s="46">
         <f>2*PI()/H18</f>
-        <v>3.6815538909255388</v>
+        <v>3.1468373825607276</v>
       </c>
       <c r="J18" s="47">
-        <v>1.5800000000000001</v>
+        <v>2.9900000000000002</v>
       </c>
       <c r="K18" s="48">
         <v>2.9999999999999999e-002</v>
@@ -1915,37 +1915,37 @@
     </row>
     <row r="19">
       <c r="A19" s="8">
-        <v>4.2000000000000002</v>
+        <v>3.6000000000000001</v>
       </c>
       <c r="B19" s="39">
-        <v>4.3899999999999997</v>
+        <v>3.6800000000000002</v>
       </c>
       <c r="C19" s="40">
         <v>1.e-002</v>
       </c>
       <c r="D19" s="41">
         <f>2*PI()/B19</f>
-        <v>1.4312495004964889</v>
-      </c>
-      <c r="E19" s="42">
-        <v>1.4399999999999999</v>
+        <v>1.7073873117335832</v>
+      </c>
+      <c r="E19" s="55">
+        <v>1.7</v>
       </c>
       <c r="F19" s="43">
-        <v>1.4299999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="G19" s="44">
-        <v>1.4299999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="H19" s="45">
         <f>AVERAGE(E19:G19)</f>
-        <v>1.4333333333333333</v>
+        <v>1.7066666666666668</v>
       </c>
       <c r="I19" s="46">
         <f>2*PI()/H19</f>
-        <v>4.3836176561718041</v>
+        <v>3.6815538909255388</v>
       </c>
       <c r="J19" s="47">
-        <v>0.89300000000000002</v>
+        <v>1.5800000000000001</v>
       </c>
       <c r="K19" s="48">
         <v>2.9999999999999999e-002</v>
@@ -1953,124 +1953,123 @@
     </row>
     <row r="20">
       <c r="A20" s="8">
-        <v>4.5</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="B20" s="39">
-        <v>4.75</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="C20" s="40">
         <v>1.e-002</v>
       </c>
       <c r="D20" s="41">
         <f>2*PI()/B20</f>
-        <v>1.3227758541430708</v>
+        <v>1.4312495004964889</v>
       </c>
       <c r="E20" s="42">
-        <v>1.3300000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="F20" s="43">
-        <v>1.3300000000000001</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="G20" s="44">
-        <v>1.3200000000000001</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H20" s="45">
         <f>AVERAGE(E20:G20)</f>
-        <v>1.3266666666666669</v>
+        <v>1.4333333333333333</v>
       </c>
       <c r="I20" s="46">
         <f>2*PI()/H20</f>
-        <v>4.7360693270197878</v>
+        <v>4.3836176561718041</v>
       </c>
       <c r="J20" s="47">
-        <v>0.71399999999999997</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="K20" s="48">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="21" ht="13.15">
-      <c r="A21" s="11">
-        <v>4.7000000000000002</v>
-      </c>
-      <c r="B21" s="51">
-        <v>4.9500000000000002</v>
-      </c>
-      <c r="C21" s="52">
+      <c r="A21" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="B21" s="39">
+        <v>4.75</v>
+      </c>
+      <c r="C21" s="40">
         <v>1.e-002</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="41">
         <f>2*PI()/B21</f>
-        <v>1.2693303650867851</v>
-      </c>
-      <c r="E21" s="54">
-        <v>1.26</v>
-      </c>
-      <c r="F21" s="55">
-        <v>1.28</v>
-      </c>
-      <c r="G21" s="56">
-        <v>1.2669999999999999</v>
-      </c>
-      <c r="H21" s="57">
+        <v>1.3227758541430708</v>
+      </c>
+      <c r="E21" s="42">
+        <v>1.3300000000000001</v>
+      </c>
+      <c r="F21" s="43">
+        <v>1.3300000000000001</v>
+      </c>
+      <c r="G21" s="44">
+        <v>1.3200000000000001</v>
+      </c>
+      <c r="H21" s="45">
         <f>AVERAGE(E21:G21)</f>
-        <v>1.2689999999999999</v>
-      </c>
-      <c r="I21" s="58">
+        <v>1.3266666666666669</v>
+      </c>
+      <c r="I21" s="46">
         <f>2*PI()/H21</f>
-        <v>4.9512886581399425</v>
-      </c>
-      <c r="J21" s="59">
-        <v>0.63400000000000001</v>
+        <v>4.7360693270197878</v>
+      </c>
+      <c r="J21" s="47">
+        <v>0.71399999999999997</v>
       </c>
       <c r="K21" s="48">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
-    <row r="22" ht="13.5"/>
+    <row r="22" ht="13.5">
+      <c r="A22" s="11">
+        <v>4.7000000000000002</v>
+      </c>
+      <c r="B22" s="56">
+        <v>4.9500000000000002</v>
+      </c>
+      <c r="C22" s="57">
+        <v>1.e-002</v>
+      </c>
+      <c r="D22" s="58">
+        <f>2*PI()/B22</f>
+        <v>1.2693303650867851</v>
+      </c>
+      <c r="E22" s="59">
+        <v>1.26</v>
+      </c>
+      <c r="F22" s="60">
+        <v>1.28</v>
+      </c>
+      <c r="G22" s="61">
+        <v>1.2669999999999999</v>
+      </c>
+      <c r="H22" s="62">
+        <f>AVERAGE(E22:G22)</f>
+        <v>1.2689999999999999</v>
+      </c>
+      <c r="I22" s="63">
+        <f>2*PI()/H22</f>
+        <v>4.9512886581399425</v>
+      </c>
+      <c r="J22" s="64">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="K22" s="48">
+        <v>2.9999999999999999e-002</v>
+      </c>
+    </row>
     <row r="25" ht="12.75">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="61"/>
-    </row>
-    <row r="27" ht="12.75">
-      <c r="A27" s="62">
-        <v>2.7000000000000002</v>
-      </c>
-      <c r="B27" s="63">
-        <v>2.54</v>
-      </c>
-      <c r="C27" s="64">
-        <v>1.e-002</v>
-      </c>
-      <c r="D27" s="65">
-        <f>2*PI()/B27</f>
-        <v>2.4736950028266089</v>
-      </c>
-      <c r="E27" s="63">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="F27" s="63">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="G27" s="63">
-        <v>2.46</v>
-      </c>
-      <c r="H27" s="65">
-        <f>AVERAGE(E27:G27)</f>
-        <v>2.4933333333333332</v>
-      </c>
-      <c r="I27" s="66">
-        <f>2*PI()/H27</f>
-        <v>2.5199941071575882</v>
-      </c>
-      <c r="J27" s="63">
-        <v>6.1100000000000003</v>
-      </c>
-      <c r="K27" s="48">
-        <v>1.e-002</v>
-      </c>
+      <c r="B25" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2676,20 +2675,20 @@
       <c r="C20" s="93">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="58">
         <f t="shared" si="3"/>
         <v>1.2013738637054656</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="62">
         <v>1.2</v>
       </c>
-      <c r="F20" s="57">
+      <c r="F20" s="62">
         <v>1.2</v>
       </c>
-      <c r="G20" s="57">
+      <c r="G20" s="62">
         <v>1.2</v>
       </c>
-      <c r="H20" s="57">
+      <c r="H20" s="62">
         <f t="shared" si="6"/>
         <v>1.2</v>
       </c>

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -160,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="51">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -437,41 +437,6 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right style="none"/>
       <top style="medium">
         <color theme="1"/>
@@ -481,6 +446,19 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right style="none"/>
       <top style="medium">
         <color theme="1"/>
@@ -515,16 +493,9 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
       <right style="medium">
         <color theme="1"/>
       </right>
@@ -559,72 +530,6 @@
       </right>
       <top style="none"/>
       <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -637,6 +542,28 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="medium">
         <color theme="1"/>
       </left>
@@ -660,6 +587,28 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -823,13 +772,13 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -837,7 +786,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -874,84 +823,83 @@
     <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
     <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="41" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="42" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="4" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="45" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="46" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="47" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="46" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="47" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="51" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="52" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="53" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -960,15 +908,15 @@
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="55" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1693,7 +1641,7 @@
         <v>1.27</v>
       </c>
       <c r="C13" s="30">
-        <v>1.e-002</v>
+        <v>2.e-002</v>
       </c>
       <c r="D13" s="31">
         <f t="shared" ref="D13:D16" si="0">2*PI()/B13</f>
@@ -1727,75 +1675,75 @@
       <c r="A14" s="8">
         <v>1.8</v>
       </c>
-      <c r="B14" s="39">
+      <c r="B14">
         <v>1.4299999999999999</v>
       </c>
-      <c r="C14" s="40">
-        <v>1.e-002</v>
-      </c>
-      <c r="D14" s="41">
+      <c r="C14" s="39">
+        <v>2.e-002</v>
+      </c>
+      <c r="D14" s="40">
         <f t="shared" si="0"/>
         <v>4.3938358791465637</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="41">
         <v>4.4100000000000001</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="42">
         <v>4.5300000000000002</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="43">
         <v>4.3700000000000001</v>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="44">
         <f t="shared" si="1"/>
         <v>4.4366666666666674</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="45">
         <f t="shared" si="2"/>
         <v>1.4161950354274047</v>
       </c>
-      <c r="J14" s="47">
+      <c r="J14" s="46">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K14" s="48">
+      <c r="K14" s="47">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="49">
+      <c r="A15" s="48">
         <v>2</v>
       </c>
-      <c r="B15" s="39">
+      <c r="B15">
         <v>1.6100000000000001</v>
       </c>
-      <c r="C15" s="40">
-        <v>1.e-002</v>
-      </c>
-      <c r="D15" s="41">
+      <c r="C15" s="39">
+        <v>2.e-002</v>
+      </c>
+      <c r="D15" s="40">
         <f t="shared" si="0"/>
         <v>3.9025995696767612</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="41">
         <v>3.8599999999999999</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="42">
         <v>3.8700000000000001</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="43">
         <v>3.96</v>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="44">
         <f t="shared" si="1"/>
         <v>3.8966666666666669</v>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="45">
         <f t="shared" si="2"/>
         <v>1.6124513192077636</v>
       </c>
-      <c r="J15" s="47">
+      <c r="J15" s="46">
         <v>2.6000000000000001</v>
       </c>
-      <c r="K15" s="48">
+      <c r="K15" s="47">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
@@ -1803,278 +1751,278 @@
       <c r="A16" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B16" s="39">
+      <c r="B16">
         <v>2.0299999999999998</v>
       </c>
-      <c r="C16" s="40">
-        <v>1.e-002</v>
-      </c>
-      <c r="D16" s="41">
+      <c r="C16" s="39">
+        <v>2.e-002</v>
+      </c>
+      <c r="D16" s="40">
         <f t="shared" si="0"/>
         <v>3.0951651759505352</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="41">
         <v>3.0800000000000001</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="42">
         <v>3.0800000000000001</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="43">
         <v>3.1099999999999999</v>
       </c>
-      <c r="H16" s="45">
+      <c r="H16" s="44">
         <f t="shared" si="1"/>
         <v>3.0899999999999999</v>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="45">
         <f t="shared" si="2"/>
         <v>2.0333933032943645</v>
       </c>
-      <c r="J16" s="47">
+      <c r="J16" s="46">
         <v>3.6699999999999999</v>
       </c>
-      <c r="K16" s="48">
+      <c r="K16" s="47">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50">
-        <v>2.7000000000000002</v>
-      </c>
-      <c r="B17" s="51">
-        <v>2.54</v>
-      </c>
-      <c r="C17" s="52">
-        <v>1.e-002</v>
-      </c>
-      <c r="D17" s="53">
+      <c r="A17" s="8">
+        <v>3.2000000000000002</v>
+      </c>
+      <c r="B17">
+        <v>3.1400000000000001</v>
+      </c>
+      <c r="C17" s="39">
+        <v>2.e-002</v>
+      </c>
+      <c r="D17" s="40">
         <f>2*PI()/B17</f>
-        <v>2.4736950028266089</v>
-      </c>
-      <c r="E17" s="51">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="F17" s="51">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="G17" s="51">
-        <v>2.46</v>
-      </c>
-      <c r="H17" s="53">
+        <v>2.0010144290380847</v>
+      </c>
+      <c r="E17" s="49">
+        <v>2</v>
+      </c>
+      <c r="F17" s="42">
+        <v>1.99</v>
+      </c>
+      <c r="G17" s="43">
+        <v>2</v>
+      </c>
+      <c r="H17" s="44">
         <f>AVERAGE(E17:G17)</f>
-        <v>2.4933333333333332</v>
-      </c>
-      <c r="I17" s="54">
+        <v>1.9966666666666668</v>
+      </c>
+      <c r="I17" s="45">
         <f>2*PI()/H17</f>
-        <v>2.5199941071575882</v>
-      </c>
-      <c r="J17" s="51">
-        <v>6.1100000000000003</v>
-      </c>
-      <c r="K17" s="48">
+        <v>3.1468373825607276</v>
+      </c>
+      <c r="J17" s="46">
+        <v>2.9900000000000002</v>
+      </c>
+      <c r="K17" s="47">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8">
-        <v>3.2000000000000002</v>
-      </c>
-      <c r="B18" s="39">
-        <v>3.1400000000000001</v>
-      </c>
-      <c r="C18" s="40">
-        <v>1.e-002</v>
-      </c>
-      <c r="D18" s="41">
+        <v>3.6000000000000001</v>
+      </c>
+      <c r="B18">
+        <v>3.6800000000000002</v>
+      </c>
+      <c r="C18" s="39">
+        <v>2.e-002</v>
+      </c>
+      <c r="D18" s="40">
         <f>2*PI()/B18</f>
-        <v>2.0010144290380847</v>
-      </c>
-      <c r="E18" s="55">
-        <v>2</v>
-      </c>
-      <c r="F18" s="43">
-        <v>1.99</v>
-      </c>
-      <c r="G18" s="44">
-        <v>2</v>
-      </c>
-      <c r="H18" s="45">
+        <v>1.7073873117335832</v>
+      </c>
+      <c r="E18" s="49">
+        <v>1.7</v>
+      </c>
+      <c r="F18" s="42">
+        <v>1.71</v>
+      </c>
+      <c r="G18" s="43">
+        <v>1.71</v>
+      </c>
+      <c r="H18" s="44">
         <f>AVERAGE(E18:G18)</f>
-        <v>1.9966666666666668</v>
-      </c>
-      <c r="I18" s="46">
+        <v>1.7066666666666668</v>
+      </c>
+      <c r="I18" s="45">
         <f>2*PI()/H18</f>
-        <v>3.1468373825607276</v>
-      </c>
-      <c r="J18" s="47">
-        <v>2.9900000000000002</v>
-      </c>
-      <c r="K18" s="48">
+        <v>3.6815538909255388</v>
+      </c>
+      <c r="J18" s="46">
+        <v>1.5800000000000001</v>
+      </c>
+      <c r="K18" s="47">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8">
-        <v>3.6000000000000001</v>
-      </c>
-      <c r="B19" s="39">
-        <v>3.6800000000000002</v>
-      </c>
-      <c r="C19" s="40">
-        <v>1.e-002</v>
-      </c>
-      <c r="D19" s="41">
+        <v>4.2000000000000002</v>
+      </c>
+      <c r="B19">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="C19" s="39">
+        <v>2.e-002</v>
+      </c>
+      <c r="D19" s="40">
         <f>2*PI()/B19</f>
-        <v>1.7073873117335832</v>
-      </c>
-      <c r="E19" s="55">
-        <v>1.7</v>
-      </c>
-      <c r="F19" s="43">
-        <v>1.71</v>
-      </c>
-      <c r="G19" s="44">
-        <v>1.71</v>
-      </c>
-      <c r="H19" s="45">
+        <v>1.4312495004964889</v>
+      </c>
+      <c r="E19" s="41">
+        <v>1.4399999999999999</v>
+      </c>
+      <c r="F19" s="42">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="G19" s="43">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="H19" s="44">
         <f>AVERAGE(E19:G19)</f>
-        <v>1.7066666666666668</v>
-      </c>
-      <c r="I19" s="46">
+        <v>1.4333333333333333</v>
+      </c>
+      <c r="I19" s="45">
         <f>2*PI()/H19</f>
-        <v>3.6815538909255388</v>
-      </c>
-      <c r="J19" s="47">
-        <v>1.5800000000000001</v>
-      </c>
-      <c r="K19" s="48">
+        <v>4.3836176561718041</v>
+      </c>
+      <c r="J19" s="46">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="K19" s="47">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8">
-        <v>4.2000000000000002</v>
-      </c>
-      <c r="B20" s="39">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="C20" s="40">
+        <v>4.5</v>
+      </c>
+      <c r="B20">
+        <v>4.75</v>
+      </c>
+      <c r="C20" s="39">
+        <v>2.e-002</v>
+      </c>
+      <c r="D20" s="40">
+        <f>2*PI()/B20</f>
+        <v>1.3227758541430708</v>
+      </c>
+      <c r="E20" s="41">
+        <v>1.3300000000000001</v>
+      </c>
+      <c r="F20" s="42">
+        <v>1.3300000000000001</v>
+      </c>
+      <c r="G20" s="43">
+        <v>1.3200000000000001</v>
+      </c>
+      <c r="H20" s="44">
+        <f>AVERAGE(E20:G20)</f>
+        <v>1.3266666666666669</v>
+      </c>
+      <c r="I20" s="45">
+        <f>2*PI()/H20</f>
+        <v>4.7360693270197878</v>
+      </c>
+      <c r="J20" s="46">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="K20" s="47">
+        <v>2.9999999999999999e-002</v>
+      </c>
+    </row>
+    <row r="21" ht="13.15">
+      <c r="A21" s="11">
+        <v>4.7000000000000002</v>
+      </c>
+      <c r="B21" s="50">
+        <v>4.9500000000000002</v>
+      </c>
+      <c r="C21" s="51">
+        <v>2.e-002</v>
+      </c>
+      <c r="D21" s="52">
+        <f>2*PI()/B21</f>
+        <v>1.2693303650867851</v>
+      </c>
+      <c r="E21" s="53">
+        <v>1.26</v>
+      </c>
+      <c r="F21" s="54">
+        <v>1.28</v>
+      </c>
+      <c r="G21" s="55">
+        <v>1.2669999999999999</v>
+      </c>
+      <c r="H21" s="56">
+        <f>AVERAGE(E21:G21)</f>
+        <v>1.2689999999999999</v>
+      </c>
+      <c r="I21" s="57">
+        <f>2*PI()/H21</f>
+        <v>4.9512886581399425</v>
+      </c>
+      <c r="J21" s="58">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="K21" s="47">
+        <v>2.9999999999999999e-002</v>
+      </c>
+    </row>
+    <row r="22" ht="13.5">
+      <c r="A22" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="60"/>
+    </row>
+    <row r="23" ht="12.75">
+      <c r="A23" s="61">
+        <v>2.7000000000000002</v>
+      </c>
+      <c r="B23" s="62">
+        <v>2.54</v>
+      </c>
+      <c r="C23" s="63">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="41">
-        <f>2*PI()/B20</f>
-        <v>1.4312495004964889</v>
-      </c>
-      <c r="E20" s="42">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="F20" s="43">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="G20" s="44">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="H20" s="45">
-        <f>AVERAGE(E20:G20)</f>
-        <v>1.4333333333333333</v>
-      </c>
-      <c r="I20" s="46">
-        <f>2*PI()/H20</f>
-        <v>4.3836176561718041</v>
-      </c>
-      <c r="J20" s="47">
-        <v>0.89300000000000002</v>
-      </c>
-      <c r="K20" s="48">
+      <c r="D23" s="64">
+        <f>2*PI()/B23</f>
+        <v>2.4736950028266089</v>
+      </c>
+      <c r="E23" s="62">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="F23" s="62">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="G23" s="62">
+        <v>2.46</v>
+      </c>
+      <c r="H23" s="64">
+        <f>AVERAGE(E23:G23)</f>
+        <v>2.4933333333333332</v>
+      </c>
+      <c r="I23" s="65">
+        <f>2*PI()/H23</f>
+        <v>2.5199941071575882</v>
+      </c>
+      <c r="J23" s="62">
+        <v>6.1100000000000003</v>
+      </c>
+      <c r="K23" s="47">
         <v>2.9999999999999999e-002</v>
       </c>
-    </row>
-    <row r="21" ht="13.15">
-      <c r="A21" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="B21" s="39">
-        <v>4.75</v>
-      </c>
-      <c r="C21" s="40">
-        <v>1.e-002</v>
-      </c>
-      <c r="D21" s="41">
-        <f>2*PI()/B21</f>
-        <v>1.3227758541430708</v>
-      </c>
-      <c r="E21" s="42">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="F21" s="43">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="G21" s="44">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="H21" s="45">
-        <f>AVERAGE(E21:G21)</f>
-        <v>1.3266666666666669</v>
-      </c>
-      <c r="I21" s="46">
-        <f>2*PI()/H21</f>
-        <v>4.7360693270197878</v>
-      </c>
-      <c r="J21" s="47">
-        <v>0.71399999999999997</v>
-      </c>
-      <c r="K21" s="48">
-        <v>2.9999999999999999e-002</v>
-      </c>
-    </row>
-    <row r="22" ht="13.5">
-      <c r="A22" s="11">
-        <v>4.7000000000000002</v>
-      </c>
-      <c r="B22" s="56">
-        <v>4.9500000000000002</v>
-      </c>
-      <c r="C22" s="57">
-        <v>1.e-002</v>
-      </c>
-      <c r="D22" s="58">
-        <f>2*PI()/B22</f>
-        <v>1.2693303650867851</v>
-      </c>
-      <c r="E22" s="59">
-        <v>1.26</v>
-      </c>
-      <c r="F22" s="60">
-        <v>1.28</v>
-      </c>
-      <c r="G22" s="61">
-        <v>1.2669999999999999</v>
-      </c>
-      <c r="H22" s="62">
-        <f>AVERAGE(E22:G22)</f>
-        <v>1.2689999999999999</v>
-      </c>
-      <c r="I22" s="63">
-        <f>2*PI()/H22</f>
-        <v>4.9512886581399425</v>
-      </c>
-      <c r="J22" s="64">
-        <v>0.63400000000000001</v>
-      </c>
-      <c r="K22" s="48">
-        <v>2.9999999999999999e-002</v>
-      </c>
-    </row>
-    <row r="25" ht="12.75">
-      <c r="A25" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -2098,45 +2046,45 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="67" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="69">
+      <c r="A2" s="68">
         <v>0.25600000000000001</v>
       </c>
-      <c r="B2" s="69">
+      <c r="B2" s="68">
         <v>4.5999999999999999e-003</v>
       </c>
-      <c r="C2" s="69">
+      <c r="C2" s="68">
         <v>2.5699999999999998</v>
       </c>
-      <c r="D2" s="70">
+      <c r="D2" s="69">
         <v>4.4000000000000003e-003</v>
       </c>
-      <c r="E2" s="71">
+      <c r="E2" s="70">
         <f>SQRT(A6^2+C6^2)</f>
         <v>2.6210670338218649</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2148,18 +2096,18 @@
       <c r="C3" s="9">
         <v>2.5899999999999999</v>
       </c>
-      <c r="D3" s="73">
+      <c r="D3" s="72">
         <v>1.9e-003</v>
       </c>
-      <c r="E3" s="74" t="s">
+      <c r="E3" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2172,20 +2120,20 @@
       <c r="C4" s="9">
         <v>2.6099999999999999</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="72">
         <f>7*10^-4</f>
         <v>6.9999999999999988e-004</v>
       </c>
-      <c r="E4" s="71">
+      <c r="E4" s="70">
         <f>E2/2</f>
         <v>1.3105335169109325</v>
       </c>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
     </row>
     <row r="5" ht="13.15">
       <c r="A5" s="14" t="s">
@@ -2200,43 +2148,43 @@
       <c r="D5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="74" t="s">
+      <c r="E5" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
     </row>
     <row r="6" ht="13.15">
-      <c r="A6" s="75">
+      <c r="A6" s="74">
         <f>((A2/B2^2)+(A3/B3^2)+(A4/B4^2))/((1/B2^2)+(1/B3^2)+(1/B4^2))</f>
         <v>0.27320113772034554</v>
       </c>
-      <c r="B6" s="75">
+      <c r="B6" s="74">
         <f>SQRT(1/((1/B2^2)+(1/B3^2)+(1/B4^2)))</f>
         <v>5.724299964622563e-004</v>
       </c>
-      <c r="C6" s="75">
+      <c r="C6" s="74">
         <f>((C2/D2^2)+(C3/D3^2)+(C4/D4^2))/((1/D2^2)+(1/D3^2)+(1/D4^2))</f>
         <v>2.6067898906770486</v>
       </c>
-      <c r="D6" s="76">
+      <c r="D6" s="75">
         <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)))</f>
         <v>6.4964141370326843e-004</v>
       </c>
-      <c r="E6" s="77">
+      <c r="E6" s="76">
         <f>E2*2</f>
         <v>5.2421340676437298</v>
       </c>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
@@ -2251,13 +2199,13 @@
       <c r="D7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
+      <c r="E7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
     </row>
     <row r="8">
       <c r="A8" s="18">
@@ -2276,435 +2224,435 @@
         <f>_xlfn.STDEV.S(C2:C4)/SQRT(3)</f>
         <v>1.1547005383792526e-002</v>
       </c>
-      <c r="E8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
+      <c r="E8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
     </row>
     <row r="9" ht="12.75">
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
     </row>
     <row r="10">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="77" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="81" t="s">
+      <c r="E10" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="82"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="80" t="s">
+      <c r="F10" s="81"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="79" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="84" t="s">
+      <c r="J10" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="85" t="s">
+      <c r="K10" s="84" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="86">
+      <c r="A11" s="85">
         <v>1.8</v>
       </c>
-      <c r="B11" s="87">
+      <c r="B11" s="86">
         <v>1.3100000000000001</v>
       </c>
-      <c r="C11" s="88">
+      <c r="C11" s="87">
         <v>1.e-002</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="40">
         <f t="shared" ref="D11:D20" si="3">2*PI()/B11</f>
         <v>4.79632466196915</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="44">
         <v>4.8399999999999999</v>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="44">
         <v>4.7400000000000002</v>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="44">
         <v>4.8200000000000003</v>
       </c>
-      <c r="H11" s="45">
+      <c r="H11" s="44">
         <f t="shared" ref="H11:H16" si="4">AVERAGE(E11:G11)</f>
         <v>4.7999999999999998</v>
       </c>
-      <c r="I11" s="89">
+      <c r="I11" s="88">
         <f t="shared" ref="I11:I20" si="5">2*PI()/H11</f>
         <v>1.3089969389957472</v>
       </c>
-      <c r="J11" s="87">
+      <c r="J11" s="86">
         <v>2.21</v>
       </c>
-      <c r="K11" s="88">
+      <c r="K11" s="87">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="86">
+      <c r="A12" s="85">
         <v>1.8200000000000001</v>
       </c>
-      <c r="B12" s="73">
+      <c r="B12" s="72">
         <v>1.3600000000000001</v>
       </c>
-      <c r="C12" s="90">
+      <c r="C12" s="89">
         <v>1.e-002</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="40">
         <f t="shared" si="3"/>
         <v>4.6199891964555775</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="44">
         <v>4.6100000000000003</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="44">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G12" s="45">
+      <c r="G12" s="44">
         <v>4.6500000000000004</v>
       </c>
-      <c r="H12" s="45">
+      <c r="H12" s="44">
         <f t="shared" si="4"/>
         <v>4.6200000000000001</v>
       </c>
-      <c r="I12" s="89">
+      <c r="I12" s="88">
         <f t="shared" si="5"/>
         <v>1.3599968197358412</v>
       </c>
-      <c r="J12" s="73">
+      <c r="J12" s="72">
         <v>2.2400000000000002</v>
       </c>
-      <c r="K12" s="90">
+      <c r="K12" s="89">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="86">
+      <c r="A13" s="85">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B13" s="73">
+      <c r="B13" s="72">
         <v>1.9099999999999999</v>
       </c>
-      <c r="C13" s="90">
+      <c r="C13" s="89">
         <v>1.e-002</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="40">
         <f t="shared" si="3"/>
         <v>3.2896258152772706</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="44">
         <v>3.2999999999999998</v>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="44">
         <v>3.29</v>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="44">
         <v>3.29</v>
       </c>
-      <c r="H13" s="45">
+      <c r="H13" s="44">
         <f t="shared" si="4"/>
         <v>3.293333333333333</v>
       </c>
-      <c r="I13" s="89">
+      <c r="I13" s="88">
         <f t="shared" si="5"/>
         <v>1.9078497896294293</v>
       </c>
-      <c r="J13" s="73">
+      <c r="J13" s="72">
         <v>3.3799999999999999</v>
       </c>
-      <c r="K13" s="90">
+      <c r="K13" s="89">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="86">
+      <c r="A14" s="85">
         <v>3.3999999999999999</v>
       </c>
-      <c r="B14" s="73">
+      <c r="B14" s="72">
         <v>3.3799999999999999</v>
       </c>
-      <c r="C14" s="90">
+      <c r="C14" s="89">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="40">
         <f t="shared" si="3"/>
         <v>1.8589305642543155</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="44">
         <v>1.8600000000000001</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="44">
         <v>1.8600000000000001</v>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="44">
         <v>1.8500000000000001</v>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="44">
         <f t="shared" si="4"/>
         <v>1.8566666666666667</v>
       </c>
-      <c r="I14" s="89">
+      <c r="I14" s="88">
         <f t="shared" si="5"/>
         <v>3.384121350366025</v>
       </c>
-      <c r="J14" s="73">
+      <c r="J14" s="72">
         <v>2.3599999999999999</v>
       </c>
-      <c r="K14" s="90">
+      <c r="K14" s="89">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="86">
+      <c r="A15" s="85">
         <v>3.7999999999999998</v>
       </c>
-      <c r="B15" s="73">
+      <c r="B15" s="72">
         <v>3.8900000000000001</v>
       </c>
-      <c r="C15" s="90">
+      <c r="C15" s="89">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="40">
         <f t="shared" si="3"/>
         <v>1.6152147319227728</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="44">
         <v>1.6200000000000001</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="44">
         <v>1.6200000000000001</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="44">
         <v>1.6100000000000001</v>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="44">
         <f t="shared" si="4"/>
         <v>1.6166666666666669</v>
       </c>
-      <c r="I15" s="89">
+      <c r="I15" s="88">
         <f t="shared" si="5"/>
         <v>3.8865063755750011</v>
       </c>
-      <c r="J15" s="73">
+      <c r="J15" s="72">
         <v>1.3600000000000001</v>
       </c>
-      <c r="K15" s="90">
+      <c r="K15" s="89">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="16" ht="13.15">
-      <c r="A16" s="86">
+      <c r="A16" s="85">
         <v>4</v>
       </c>
-      <c r="B16" s="73">
+      <c r="B16" s="72">
         <v>4.0599999999999996</v>
       </c>
-      <c r="C16" s="90">
+      <c r="C16" s="89">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="40">
         <f t="shared" si="3"/>
         <v>1.5475825879752676</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="44">
         <v>1.54</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="44">
         <v>1.55</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="44">
         <v>1.55</v>
       </c>
-      <c r="H16" s="45">
+      <c r="H16" s="44">
         <f t="shared" si="4"/>
         <v>1.5466666666666666</v>
       </c>
-      <c r="I16" s="89">
+      <c r="I16" s="88">
         <f t="shared" si="5"/>
         <v>4.062404293435077</v>
       </c>
-      <c r="J16" s="73">
+      <c r="J16" s="72">
         <v>1.1699999999999999</v>
       </c>
-      <c r="K16" s="90">
+      <c r="K16" s="89">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" s="86">
+      <c r="A17" s="85">
         <v>4.2999999999999998</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="46">
         <v>4.5</v>
       </c>
-      <c r="C17" s="90">
+      <c r="C17" s="89">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="40">
         <f t="shared" si="3"/>
         <v>1.3962634015954636</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="44">
         <v>1.3999999999999999</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="44">
         <v>1.3999999999999999</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="44">
         <v>1.3999999999999999</v>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="44">
         <f>AVERAGE(F17:G17)</f>
         <v>1.3999999999999999</v>
       </c>
-      <c r="I17" s="89">
+      <c r="I17" s="88">
         <f t="shared" si="5"/>
         <v>4.4879895051282759</v>
       </c>
-      <c r="J17" s="73">
+      <c r="J17" s="72">
         <v>0.84499999999999997</v>
       </c>
-      <c r="K17" s="90">
+      <c r="K17" s="89">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="18" ht="12.75">
-      <c r="A18" s="86">
+      <c r="A18" s="85">
         <v>4.5999999999999996</v>
       </c>
-      <c r="B18" s="73">
+      <c r="B18" s="72">
         <v>4.8799999999999999</v>
       </c>
-      <c r="C18" s="90">
+      <c r="C18" s="89">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="40">
         <f t="shared" si="3"/>
         <v>1.2875379727827021</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="44">
         <v>1.3</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="44">
         <v>1.29</v>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="44">
         <v>1.28</v>
       </c>
-      <c r="H18" s="45">
+      <c r="H18" s="44">
         <f t="shared" ref="H18:H20" si="6">AVERAGE(E18:G18)</f>
         <v>1.29</v>
       </c>
-      <c r="I18" s="89">
+      <c r="I18" s="88">
         <f t="shared" si="5"/>
         <v>4.8706862846353376</v>
       </c>
-      <c r="J18" s="73">
+      <c r="J18" s="72">
         <v>0.67300000000000004</v>
       </c>
-      <c r="K18" s="90">
+      <c r="K18" s="89">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="19" ht="12.75">
-      <c r="A19" s="86">
+      <c r="A19" s="85">
         <v>4.7999999999999998</v>
       </c>
-      <c r="B19" s="73">
+      <c r="B19" s="72">
         <v>5.1100000000000003</v>
       </c>
-      <c r="C19" s="90">
+      <c r="C19" s="89">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="40">
         <f t="shared" si="3"/>
         <v>1.2295861657885687</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="44">
         <v>1.22</v>
       </c>
-      <c r="F19" s="45">
+      <c r="F19" s="44">
         <v>1.23</v>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="44">
         <v>1.23</v>
       </c>
-      <c r="H19" s="45">
+      <c r="H19" s="44">
         <f t="shared" si="6"/>
         <v>1.2266666666666668</v>
       </c>
-      <c r="I19" s="89">
+      <c r="I19" s="88">
         <f t="shared" si="5"/>
         <v>5.122161935200749</v>
       </c>
-      <c r="J19" s="73">
+      <c r="J19" s="72">
         <v>0.59299999999999997</v>
       </c>
-      <c r="K19" s="90">
+      <c r="K19" s="89">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="20" ht="12.75">
-      <c r="A20" s="91">
+      <c r="A20" s="90">
         <v>4.9000000000000004</v>
       </c>
-      <c r="B20" s="92">
+      <c r="B20" s="91">
         <v>5.2300000000000004</v>
       </c>
-      <c r="C20" s="93">
+      <c r="C20" s="92">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="58">
+      <c r="D20" s="52">
         <f t="shared" si="3"/>
         <v>1.2013738637054656</v>
       </c>
-      <c r="E20" s="62">
+      <c r="E20" s="56">
         <v>1.2</v>
       </c>
-      <c r="F20" s="62">
+      <c r="F20" s="56">
         <v>1.2</v>
       </c>
-      <c r="G20" s="62">
+      <c r="G20" s="56">
         <v>1.2</v>
       </c>
-      <c r="H20" s="62">
+      <c r="H20" s="56">
         <f t="shared" si="6"/>
         <v>1.2</v>
       </c>
-      <c r="I20" s="94">
+      <c r="I20" s="93">
         <f t="shared" si="5"/>
         <v>5.2359877559829888</v>
       </c>
-      <c r="J20" s="92">
+      <c r="J20" s="91">
         <v>0.55700000000000005</v>
       </c>
-      <c r="K20" s="93">
+      <c r="K20" s="92">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="23">
-      <c r="N23" s="95"/>
+      <c r="N23" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -160,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="55">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -437,6 +437,41 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right style="none"/>
       <top style="medium">
         <color theme="1"/>
@@ -446,19 +481,6 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right style="none"/>
       <top style="medium">
         <color theme="1"/>
@@ -480,22 +502,16 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
+      <left style="none"/>
       <right style="medium">
         <color theme="1"/>
       </right>
@@ -522,7 +538,7 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color theme="1"/>
       </left>
       <right style="medium">
@@ -530,6 +546,50 @@
       </right>
       <top style="none"/>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -542,13 +602,152 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -559,227 +758,66 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
   </borders>
@@ -823,83 +861,86 @@
     <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="4" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="42" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="41" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="41" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="45" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="46" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="47" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="46" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="47" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="6" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="51" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="52" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="53" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -908,16 +949,13 @@
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1641,7 +1679,7 @@
         <v>1.27</v>
       </c>
       <c r="C13" s="30">
-        <v>2.e-002</v>
+        <v>1.e-002</v>
       </c>
       <c r="D13" s="31">
         <f t="shared" ref="D13:D16" si="0">2*PI()/B13</f>
@@ -1668,354 +1706,354 @@
         <v>2.1600000000000001</v>
       </c>
       <c r="K13" s="38">
-        <v>2.9999999999999999e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8">
         <v>1.8</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="39">
         <v>1.4299999999999999</v>
       </c>
-      <c r="C14" s="39">
-        <v>2.e-002</v>
-      </c>
-      <c r="D14" s="40">
+      <c r="C14" s="40">
+        <v>1.e-002</v>
+      </c>
+      <c r="D14" s="41">
         <f t="shared" si="0"/>
         <v>4.3938358791465637</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="42">
         <v>4.4100000000000001</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="43">
         <v>4.5300000000000002</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="44">
         <v>4.3700000000000001</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="45">
         <f t="shared" si="1"/>
         <v>4.4366666666666674</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="46">
         <f t="shared" si="2"/>
         <v>1.4161950354274047</v>
       </c>
-      <c r="J14" s="46">
+      <c r="J14" s="47">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K14" s="47">
-        <v>2.9999999999999999e-002</v>
+      <c r="K14" s="48">
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48">
+      <c r="A15" s="49">
         <v>2</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="39">
         <v>1.6100000000000001</v>
       </c>
-      <c r="C15" s="39">
-        <v>2.e-002</v>
-      </c>
-      <c r="D15" s="40">
+      <c r="C15" s="40">
+        <v>1.e-002</v>
+      </c>
+      <c r="D15" s="41">
         <f t="shared" si="0"/>
         <v>3.9025995696767612</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="42">
         <v>3.8599999999999999</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="43">
         <v>3.8700000000000001</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="44">
         <v>3.96</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="45">
         <f t="shared" si="1"/>
         <v>3.8966666666666669</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="46">
         <f t="shared" si="2"/>
         <v>1.6124513192077636</v>
       </c>
-      <c r="J15" s="46">
+      <c r="J15" s="47">
         <v>2.6000000000000001</v>
       </c>
-      <c r="K15" s="47">
-        <v>2.9999999999999999e-002</v>
+      <c r="K15" s="48">
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="39">
         <v>2.0299999999999998</v>
       </c>
-      <c r="C16" s="39">
-        <v>2.e-002</v>
-      </c>
-      <c r="D16" s="40">
+      <c r="C16" s="40">
+        <v>1.e-002</v>
+      </c>
+      <c r="D16" s="41">
         <f t="shared" si="0"/>
         <v>3.0951651759505352</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="42">
         <v>3.0800000000000001</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="43">
         <v>3.0800000000000001</v>
       </c>
-      <c r="G16" s="43">
+      <c r="G16" s="44">
         <v>3.1099999999999999</v>
       </c>
-      <c r="H16" s="44">
+      <c r="H16" s="45">
         <f t="shared" si="1"/>
         <v>3.0899999999999999</v>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="46">
         <f t="shared" si="2"/>
         <v>2.0333933032943645</v>
       </c>
-      <c r="J16" s="46">
+      <c r="J16" s="47">
         <v>3.6699999999999999</v>
       </c>
-      <c r="K16" s="47">
-        <v>2.9999999999999999e-002</v>
+      <c r="K16" s="48">
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8">
         <v>3.2000000000000002</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="39">
         <v>3.1400000000000001</v>
       </c>
-      <c r="C17" s="39">
-        <v>2.e-002</v>
-      </c>
-      <c r="D17" s="40">
+      <c r="C17" s="40">
+        <v>1.e-002</v>
+      </c>
+      <c r="D17" s="41">
         <f>2*PI()/B17</f>
         <v>2.0010144290380847</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="50">
         <v>2</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="43">
         <v>1.99</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="44">
         <v>2</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="45">
         <f>AVERAGE(E17:G17)</f>
         <v>1.9966666666666668</v>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="46">
         <f>2*PI()/H17</f>
         <v>3.1468373825607276</v>
       </c>
-      <c r="J17" s="46">
+      <c r="J17" s="47">
         <v>2.9900000000000002</v>
       </c>
-      <c r="K17" s="47">
-        <v>2.9999999999999999e-002</v>
+      <c r="K17" s="48">
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8">
         <v>3.6000000000000001</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="39">
         <v>3.6800000000000002</v>
       </c>
-      <c r="C18" s="39">
-        <v>2.e-002</v>
-      </c>
-      <c r="D18" s="40">
+      <c r="C18" s="40">
+        <v>1.e-002</v>
+      </c>
+      <c r="D18" s="41">
         <f>2*PI()/B18</f>
         <v>1.7073873117335832</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="50">
         <v>1.7</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="43">
         <v>1.71</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="44">
         <v>1.71</v>
       </c>
-      <c r="H18" s="44">
+      <c r="H18" s="45">
         <f>AVERAGE(E18:G18)</f>
         <v>1.7066666666666668</v>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="46">
         <f>2*PI()/H18</f>
         <v>3.6815538909255388</v>
       </c>
-      <c r="J18" s="46">
+      <c r="J18" s="47">
         <v>1.5800000000000001</v>
       </c>
-      <c r="K18" s="47">
-        <v>2.9999999999999999e-002</v>
+      <c r="K18" s="48">
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8">
         <v>4.2000000000000002</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="39">
         <v>4.3899999999999997</v>
       </c>
-      <c r="C19" s="39">
-        <v>2.e-002</v>
-      </c>
-      <c r="D19" s="40">
+      <c r="C19" s="40">
+        <v>1.e-002</v>
+      </c>
+      <c r="D19" s="41">
         <f>2*PI()/B19</f>
         <v>1.4312495004964889</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="42">
         <v>1.4399999999999999</v>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="43">
         <v>1.4299999999999999</v>
       </c>
-      <c r="G19" s="43">
+      <c r="G19" s="44">
         <v>1.4299999999999999</v>
       </c>
-      <c r="H19" s="44">
+      <c r="H19" s="45">
         <f>AVERAGE(E19:G19)</f>
         <v>1.4333333333333333</v>
       </c>
-      <c r="I19" s="45">
+      <c r="I19" s="46">
         <f>2*PI()/H19</f>
         <v>4.3836176561718041</v>
       </c>
-      <c r="J19" s="46">
+      <c r="J19" s="47">
         <v>0.89300000000000002</v>
       </c>
-      <c r="K19" s="47">
-        <v>2.9999999999999999e-002</v>
+      <c r="K19" s="48">
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8">
         <v>4.5</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="39">
         <v>4.75</v>
       </c>
-      <c r="C20" s="39">
-        <v>2.e-002</v>
-      </c>
-      <c r="D20" s="40">
+      <c r="C20" s="40">
+        <v>1.e-002</v>
+      </c>
+      <c r="D20" s="41">
         <f>2*PI()/B20</f>
         <v>1.3227758541430708</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="42">
         <v>1.3300000000000001</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="43">
         <v>1.3300000000000001</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="44">
         <v>1.3200000000000001</v>
       </c>
-      <c r="H20" s="44">
+      <c r="H20" s="45">
         <f>AVERAGE(E20:G20)</f>
         <v>1.3266666666666669</v>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="46">
         <f>2*PI()/H20</f>
         <v>4.7360693270197878</v>
       </c>
-      <c r="J20" s="46">
+      <c r="J20" s="47">
         <v>0.71399999999999997</v>
       </c>
-      <c r="K20" s="47">
-        <v>2.9999999999999999e-002</v>
+      <c r="K20" s="48">
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="21" ht="13.15">
       <c r="A21" s="11">
         <v>4.7000000000000002</v>
       </c>
-      <c r="B21" s="50">
+      <c r="B21" s="51">
         <v>4.9500000000000002</v>
       </c>
-      <c r="C21" s="51">
-        <v>2.e-002</v>
-      </c>
-      <c r="D21" s="52">
+      <c r="C21" s="52">
+        <v>1.e-002</v>
+      </c>
+      <c r="D21" s="53">
         <f>2*PI()/B21</f>
         <v>1.2693303650867851</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="54">
         <v>1.26</v>
       </c>
-      <c r="F21" s="54">
+      <c r="F21" s="55">
         <v>1.28</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="56">
         <v>1.2669999999999999</v>
       </c>
-      <c r="H21" s="56">
+      <c r="H21" s="57">
         <f>AVERAGE(E21:G21)</f>
         <v>1.2689999999999999</v>
       </c>
-      <c r="I21" s="57">
+      <c r="I21" s="58">
         <f>2*PI()/H21</f>
         <v>4.9512886581399425</v>
       </c>
-      <c r="J21" s="58">
+      <c r="J21" s="59">
         <v>0.63400000000000001</v>
       </c>
-      <c r="K21" s="47">
-        <v>2.9999999999999999e-002</v>
+      <c r="K21" s="60">
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="22" ht="13.5">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="62"/>
     </row>
     <row r="23" ht="12.75">
-      <c r="A23" s="61">
+      <c r="A23" s="63">
         <v>2.7000000000000002</v>
       </c>
-      <c r="B23" s="62">
+      <c r="B23" s="64">
         <v>2.54</v>
       </c>
-      <c r="C23" s="63">
+      <c r="C23" s="65">
         <v>1.e-002</v>
       </c>
-      <c r="D23" s="64">
+      <c r="D23" s="66">
         <f>2*PI()/B23</f>
         <v>2.4736950028266089</v>
       </c>
-      <c r="E23" s="62">
+      <c r="E23" s="64">
         <v>2.5099999999999998</v>
       </c>
-      <c r="F23" s="62">
+      <c r="F23" s="64">
         <v>2.5099999999999998</v>
       </c>
-      <c r="G23" s="62">
+      <c r="G23" s="64">
         <v>2.46</v>
       </c>
-      <c r="H23" s="64">
+      <c r="H23" s="66">
         <f>AVERAGE(E23:G23)</f>
         <v>2.4933333333333332</v>
       </c>
-      <c r="I23" s="65">
+      <c r="I23" s="67">
         <f>2*PI()/H23</f>
         <v>2.5199941071575882</v>
       </c>
-      <c r="J23" s="62">
+      <c r="J23" s="64">
         <v>6.1100000000000003</v>
       </c>
-      <c r="K23" s="47">
+      <c r="K23" s="68">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
@@ -2046,45 +2084,45 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="70" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="68">
+      <c r="A2" s="71">
         <v>0.25600000000000001</v>
       </c>
-      <c r="B2" s="68">
+      <c r="B2" s="71">
         <v>4.5999999999999999e-003</v>
       </c>
-      <c r="C2" s="68">
+      <c r="C2" s="71">
         <v>2.5699999999999998</v>
       </c>
-      <c r="D2" s="69">
+      <c r="D2" s="72">
         <v>4.4000000000000003e-003</v>
       </c>
-      <c r="E2" s="70">
+      <c r="E2" s="73">
         <f>SQRT(A6^2+C6^2)</f>
         <v>2.6210670338218649</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2096,18 +2134,18 @@
       <c r="C3" s="9">
         <v>2.5899999999999999</v>
       </c>
-      <c r="D3" s="72">
+      <c r="D3" s="75">
         <v>1.9e-003</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2120,20 +2158,20 @@
       <c r="C4" s="9">
         <v>2.6099999999999999</v>
       </c>
-      <c r="D4" s="72">
+      <c r="D4" s="75">
         <f>7*10^-4</f>
         <v>6.9999999999999988e-004</v>
       </c>
-      <c r="E4" s="70">
+      <c r="E4" s="73">
         <f>E2/2</f>
         <v>1.3105335169109325</v>
       </c>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
     </row>
     <row r="5" ht="13.15">
       <c r="A5" s="14" t="s">
@@ -2148,43 +2186,43 @@
       <c r="D5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
     </row>
     <row r="6" ht="13.15">
-      <c r="A6" s="74">
+      <c r="A6" s="77">
         <f>((A2/B2^2)+(A3/B3^2)+(A4/B4^2))/((1/B2^2)+(1/B3^2)+(1/B4^2))</f>
         <v>0.27320113772034554</v>
       </c>
-      <c r="B6" s="74">
+      <c r="B6" s="77">
         <f>SQRT(1/((1/B2^2)+(1/B3^2)+(1/B4^2)))</f>
         <v>5.724299964622563e-004</v>
       </c>
-      <c r="C6" s="74">
+      <c r="C6" s="77">
         <f>((C2/D2^2)+(C3/D3^2)+(C4/D4^2))/((1/D2^2)+(1/D3^2)+(1/D4^2))</f>
         <v>2.6067898906770486</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="78">
         <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)))</f>
         <v>6.4964141370326843e-004</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="79">
         <f>E2*2</f>
         <v>5.2421340676437298</v>
       </c>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
@@ -2199,13 +2237,13 @@
       <c r="D7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
+      <c r="E7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
     </row>
     <row r="8">
       <c r="A8" s="18">
@@ -2224,419 +2262,419 @@
         <f>_xlfn.STDEV.S(C2:C4)/SQRT(3)</f>
         <v>1.1547005383792526e-002</v>
       </c>
-      <c r="E8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
+      <c r="E8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="74"/>
     </row>
     <row r="9" ht="12.75">
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="74"/>
+      <c r="J9" s="74"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="74"/>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="80" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="78" t="s">
+      <c r="C10" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="79" t="s">
+      <c r="D10" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="80" t="s">
+      <c r="E10" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="81"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="79" t="s">
+      <c r="F10" s="84"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="82" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="83" t="s">
+      <c r="J10" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="84" t="s">
+      <c r="K10" s="87" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="85">
+      <c r="A11" s="88">
         <v>1.8</v>
       </c>
-      <c r="B11" s="86">
+      <c r="B11" s="89">
         <v>1.3100000000000001</v>
       </c>
-      <c r="C11" s="87">
+      <c r="C11" s="38">
         <v>1.e-002</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="41">
         <f t="shared" ref="D11:D20" si="3">2*PI()/B11</f>
         <v>4.79632466196915</v>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="45">
         <v>4.8399999999999999</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="45">
         <v>4.7400000000000002</v>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="45">
         <v>4.8200000000000003</v>
       </c>
-      <c r="H11" s="44">
+      <c r="H11" s="45">
         <f t="shared" ref="H11:H16" si="4">AVERAGE(E11:G11)</f>
         <v>4.7999999999999998</v>
       </c>
-      <c r="I11" s="88">
+      <c r="I11" s="90">
         <f t="shared" ref="I11:I20" si="5">2*PI()/H11</f>
         <v>1.3089969389957472</v>
       </c>
-      <c r="J11" s="86">
+      <c r="J11" s="89">
         <v>2.21</v>
       </c>
-      <c r="K11" s="87">
+      <c r="K11" s="38">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="85">
+      <c r="A12" s="88">
         <v>1.8200000000000001</v>
       </c>
-      <c r="B12" s="72">
+      <c r="B12" s="75">
         <v>1.3600000000000001</v>
       </c>
-      <c r="C12" s="89">
+      <c r="C12" s="48">
         <v>1.e-002</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="41">
         <f t="shared" si="3"/>
         <v>4.6199891964555775</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="45">
         <v>4.6100000000000003</v>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="45">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="45">
         <v>4.6500000000000004</v>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="45">
         <f t="shared" si="4"/>
         <v>4.6200000000000001</v>
       </c>
-      <c r="I12" s="88">
+      <c r="I12" s="90">
         <f t="shared" si="5"/>
         <v>1.3599968197358412</v>
       </c>
-      <c r="J12" s="72">
+      <c r="J12" s="75">
         <v>2.2400000000000002</v>
       </c>
-      <c r="K12" s="89">
+      <c r="K12" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="85">
+      <c r="A13" s="88">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B13" s="72">
+      <c r="B13" s="75">
         <v>1.9099999999999999</v>
       </c>
-      <c r="C13" s="89">
+      <c r="C13" s="48">
         <v>1.e-002</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="41">
         <f t="shared" si="3"/>
         <v>3.2896258152772706</v>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="45">
         <v>3.2999999999999998</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="45">
         <v>3.29</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="45">
         <v>3.29</v>
       </c>
-      <c r="H13" s="44">
+      <c r="H13" s="45">
         <f t="shared" si="4"/>
         <v>3.293333333333333</v>
       </c>
-      <c r="I13" s="88">
+      <c r="I13" s="90">
         <f t="shared" si="5"/>
         <v>1.9078497896294293</v>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="75">
         <v>3.3799999999999999</v>
       </c>
-      <c r="K13" s="89">
+      <c r="K13" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="85">
+      <c r="A14" s="88">
         <v>3.3999999999999999</v>
       </c>
-      <c r="B14" s="72">
+      <c r="B14" s="75">
         <v>3.3799999999999999</v>
       </c>
-      <c r="C14" s="89">
+      <c r="C14" s="48">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="41">
         <f t="shared" si="3"/>
         <v>1.8589305642543155</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="45">
         <v>1.8600000000000001</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="45">
         <v>1.8600000000000001</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="45">
         <v>1.8500000000000001</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="45">
         <f t="shared" si="4"/>
         <v>1.8566666666666667</v>
       </c>
-      <c r="I14" s="88">
+      <c r="I14" s="90">
         <f t="shared" si="5"/>
         <v>3.384121350366025</v>
       </c>
-      <c r="J14" s="72">
+      <c r="J14" s="75">
         <v>2.3599999999999999</v>
       </c>
-      <c r="K14" s="89">
+      <c r="K14" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="85">
+      <c r="A15" s="88">
         <v>3.7999999999999998</v>
       </c>
-      <c r="B15" s="72">
+      <c r="B15" s="75">
         <v>3.8900000000000001</v>
       </c>
-      <c r="C15" s="89">
+      <c r="C15" s="48">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="41">
         <f t="shared" si="3"/>
         <v>1.6152147319227728</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="45">
         <v>1.6200000000000001</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="45">
         <v>1.6200000000000001</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="45">
         <v>1.6100000000000001</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="45">
         <f t="shared" si="4"/>
         <v>1.6166666666666669</v>
       </c>
-      <c r="I15" s="88">
+      <c r="I15" s="90">
         <f t="shared" si="5"/>
         <v>3.8865063755750011</v>
       </c>
-      <c r="J15" s="72">
+      <c r="J15" s="75">
         <v>1.3600000000000001</v>
       </c>
-      <c r="K15" s="89">
+      <c r="K15" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="16" ht="13.15">
-      <c r="A16" s="85">
+      <c r="A16" s="88">
         <v>4</v>
       </c>
-      <c r="B16" s="72">
+      <c r="B16" s="75">
         <v>4.0599999999999996</v>
       </c>
-      <c r="C16" s="89">
+      <c r="C16" s="48">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="41">
         <f t="shared" si="3"/>
         <v>1.5475825879752676</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="45">
         <v>1.54</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="45">
         <v>1.55</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="45">
         <v>1.55</v>
       </c>
-      <c r="H16" s="44">
+      <c r="H16" s="45">
         <f t="shared" si="4"/>
         <v>1.5466666666666666</v>
       </c>
-      <c r="I16" s="88">
+      <c r="I16" s="90">
         <f t="shared" si="5"/>
         <v>4.062404293435077</v>
       </c>
-      <c r="J16" s="72">
+      <c r="J16" s="75">
         <v>1.1699999999999999</v>
       </c>
-      <c r="K16" s="89">
+      <c r="K16" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" s="85">
+      <c r="A17" s="88">
         <v>4.2999999999999998</v>
       </c>
-      <c r="B17" s="46">
+      <c r="B17" s="47">
         <v>4.5</v>
       </c>
-      <c r="C17" s="89">
+      <c r="C17" s="48">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="41">
         <f t="shared" si="3"/>
         <v>1.3962634015954636</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="45">
         <v>1.3999999999999999</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="45">
         <v>1.3999999999999999</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="45">
         <v>1.3999999999999999</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="45">
         <f>AVERAGE(F17:G17)</f>
         <v>1.3999999999999999</v>
       </c>
-      <c r="I17" s="88">
+      <c r="I17" s="90">
         <f t="shared" si="5"/>
         <v>4.4879895051282759</v>
       </c>
-      <c r="J17" s="72">
+      <c r="J17" s="75">
         <v>0.84499999999999997</v>
       </c>
-      <c r="K17" s="89">
+      <c r="K17" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="18" ht="12.75">
-      <c r="A18" s="85">
+      <c r="A18" s="88">
         <v>4.5999999999999996</v>
       </c>
-      <c r="B18" s="72">
+      <c r="B18" s="75">
         <v>4.8799999999999999</v>
       </c>
-      <c r="C18" s="89">
+      <c r="C18" s="48">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="41">
         <f t="shared" si="3"/>
         <v>1.2875379727827021</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="45">
         <v>1.3</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="45">
         <v>1.29</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="45">
         <v>1.28</v>
       </c>
-      <c r="H18" s="44">
+      <c r="H18" s="45">
         <f t="shared" ref="H18:H20" si="6">AVERAGE(E18:G18)</f>
         <v>1.29</v>
       </c>
-      <c r="I18" s="88">
+      <c r="I18" s="90">
         <f t="shared" si="5"/>
         <v>4.8706862846353376</v>
       </c>
-      <c r="J18" s="72">
+      <c r="J18" s="75">
         <v>0.67300000000000004</v>
       </c>
-      <c r="K18" s="89">
+      <c r="K18" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="19" ht="12.75">
-      <c r="A19" s="85">
+      <c r="A19" s="88">
         <v>4.7999999999999998</v>
       </c>
-      <c r="B19" s="72">
+      <c r="B19" s="75">
         <v>5.1100000000000003</v>
       </c>
-      <c r="C19" s="89">
+      <c r="C19" s="48">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="41">
         <f t="shared" si="3"/>
         <v>1.2295861657885687</v>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="45">
         <v>1.22</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="45">
         <v>1.23</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="45">
         <v>1.23</v>
       </c>
-      <c r="H19" s="44">
+      <c r="H19" s="45">
         <f t="shared" si="6"/>
         <v>1.2266666666666668</v>
       </c>
-      <c r="I19" s="88">
+      <c r="I19" s="90">
         <f t="shared" si="5"/>
         <v>5.122161935200749</v>
       </c>
-      <c r="J19" s="72">
+      <c r="J19" s="75">
         <v>0.59299999999999997</v>
       </c>
-      <c r="K19" s="89">
+      <c r="K19" s="48">
         <v>2.e-002</v>
       </c>
     </row>
     <row r="20" ht="12.75">
-      <c r="A20" s="90">
+      <c r="A20" s="91">
         <v>4.9000000000000004</v>
       </c>
-      <c r="B20" s="91">
+      <c r="B20" s="92">
         <v>5.2300000000000004</v>
       </c>
-      <c r="C20" s="92">
+      <c r="C20" s="60">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="53">
         <f t="shared" si="3"/>
         <v>1.2013738637054656</v>
       </c>
-      <c r="E20" s="56">
+      <c r="E20" s="57">
         <v>1.2</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="57">
         <v>1.2</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="57">
         <v>1.2</v>
       </c>
-      <c r="H20" s="56">
+      <c r="H20" s="57">
         <f t="shared" si="6"/>
         <v>1.2</v>
       </c>
@@ -2644,10 +2682,10 @@
         <f t="shared" si="5"/>
         <v>5.2359877559829888</v>
       </c>
-      <c r="J20" s="91">
+      <c r="J20" s="92">
         <v>0.55700000000000005</v>
       </c>
-      <c r="K20" s="92">
+      <c r="K20" s="60">
         <v>2.e-002</v>
       </c>
     </row>

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Smorzate forzate (4mm)" sheetId="1" state="visible" r:id="rId4"/>
@@ -2344,7 +2344,7 @@
         <v>2.21</v>
       </c>
       <c r="K11" s="38">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="12">
@@ -2382,7 +2382,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="K12" s="48">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="13">
@@ -2420,7 +2420,7 @@
         <v>3.3799999999999999</v>
       </c>
       <c r="K13" s="48">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="14">
@@ -2458,7 +2458,7 @@
         <v>2.3599999999999999</v>
       </c>
       <c r="K14" s="48">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="15">
@@ -2496,7 +2496,7 @@
         <v>1.3600000000000001</v>
       </c>
       <c r="K15" s="48">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="16" ht="13.15">
@@ -2534,7 +2534,7 @@
         <v>1.1699999999999999</v>
       </c>
       <c r="K16" s="48">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="17" ht="12.75">
@@ -2572,7 +2572,7 @@
         <v>0.84499999999999997</v>
       </c>
       <c r="K17" s="48">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="18" ht="12.75">
@@ -2610,7 +2610,7 @@
         <v>0.67300000000000004</v>
       </c>
       <c r="K18" s="48">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="19" ht="12.75">
@@ -2648,7 +2648,7 @@
         <v>0.59299999999999997</v>
       </c>
       <c r="K19" s="48">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="20" ht="12.75">
@@ -2686,7 +2686,7 @@
         <v>0.55700000000000005</v>
       </c>
       <c r="K20" s="60">
-        <v>2.e-002</v>
+        <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="23">

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Smorzate forzate (4mm)" sheetId="1" state="visible" r:id="rId4"/>
@@ -160,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="66">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -661,6 +661,147 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="none"/>
       <right style="none"/>
       <top style="medium">
@@ -824,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="109">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -862,7 +1003,7 @@
     <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -872,13 +1013,12 @@
     <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -888,8 +1028,7 @@
     <xf fontId="0" fillId="0" borderId="30" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -898,7 +1037,7 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -908,8 +1047,7 @@
     <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="36" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -926,21 +1064,46 @@
     <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="45" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="46" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="47" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="46" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="47" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="48" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="49" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="50" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="51" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="52" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="53" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="55" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="56" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="57" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="58" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="48" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="49" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="51" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="52" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="59" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="60" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="61" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="62" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="63" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="53" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="64" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="65" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -949,14 +1112,14 @@
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="65" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1676,14 +1839,14 @@
         <v>1.7</v>
       </c>
       <c r="B13" s="29">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="C13" s="30">
         <v>1.e-002</v>
       </c>
       <c r="D13" s="31">
         <f t="shared" ref="D13:D16" si="0">2*PI()/B13</f>
-        <v>4.9473900056532178</v>
+        <v>5.026548245743669</v>
       </c>
       <c r="E13" s="32">
         <v>5.04</v>
@@ -1698,14 +1861,14 @@
         <f t="shared" ref="H13:H16" si="1">AVERAGE(E13:G13)</f>
         <v>5.0100000000000007</v>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="31">
         <f t="shared" ref="I13:I16" si="2">2*PI()/H13</f>
         <v>1.2541288038282605</v>
       </c>
-      <c r="J13" s="37">
+      <c r="J13" s="36">
         <v>2.1600000000000001</v>
       </c>
-      <c r="K13" s="38">
+      <c r="K13" s="37">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1713,75 +1876,75 @@
       <c r="A14" s="8">
         <v>1.8</v>
       </c>
-      <c r="B14" s="39">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="C14" s="40">
+      <c r="B14" s="38">
+        <v>1.4199999999999999</v>
+      </c>
+      <c r="C14" s="39">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="40">
         <f t="shared" si="0"/>
-        <v>4.3938358791465637</v>
-      </c>
-      <c r="E14" s="42">
+        <v>4.4247783853377367</v>
+      </c>
+      <c r="E14" s="41">
         <v>4.4100000000000001</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="42">
         <v>4.5300000000000002</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="43">
         <v>4.3700000000000001</v>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="44">
         <f t="shared" si="1"/>
         <v>4.4366666666666674</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="40">
         <f t="shared" si="2"/>
         <v>1.4161950354274047</v>
       </c>
-      <c r="J14" s="47">
+      <c r="J14" s="45">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K14" s="48">
+      <c r="K14" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="49">
+      <c r="A15" s="47">
         <v>2</v>
       </c>
-      <c r="B15" s="39">
+      <c r="B15" s="38">
         <v>1.6100000000000001</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="39">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="40">
         <f t="shared" si="0"/>
         <v>3.9025995696767612</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="41">
         <v>3.8599999999999999</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="42">
         <v>3.8700000000000001</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="43">
         <v>3.96</v>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="44">
         <f t="shared" si="1"/>
         <v>3.8966666666666669</v>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="40">
         <f t="shared" si="2"/>
         <v>1.6124513192077636</v>
       </c>
-      <c r="J15" s="47">
+      <c r="J15" s="45">
         <v>2.6000000000000001</v>
       </c>
-      <c r="K15" s="48">
+      <c r="K15" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1789,37 +1952,37 @@
       <c r="A16" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B16" s="39">
+      <c r="B16" s="38">
         <v>2.0299999999999998</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="39">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="40">
         <f t="shared" si="0"/>
         <v>3.0951651759505352</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="41">
         <v>3.0800000000000001</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="42">
         <v>3.0800000000000001</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="43">
         <v>3.1099999999999999</v>
       </c>
-      <c r="H16" s="45">
+      <c r="H16" s="44">
         <f t="shared" si="1"/>
         <v>3.0899999999999999</v>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="40">
         <f t="shared" si="2"/>
         <v>2.0333933032943645</v>
       </c>
-      <c r="J16" s="47">
+      <c r="J16" s="45">
         <v>3.6699999999999999</v>
       </c>
-      <c r="K16" s="48">
+      <c r="K16" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1827,37 +1990,37 @@
       <c r="A17" s="8">
         <v>3.2000000000000002</v>
       </c>
-      <c r="B17" s="39">
+      <c r="B17" s="38">
         <v>3.1400000000000001</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="39">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="40">
         <f>2*PI()/B17</f>
         <v>2.0010144290380847</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="48">
         <v>2</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="42">
         <v>1.99</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="43">
         <v>2</v>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="44">
         <f>AVERAGE(E17:G17)</f>
         <v>1.9966666666666668</v>
       </c>
-      <c r="I17" s="46">
+      <c r="I17" s="40">
         <f>2*PI()/H17</f>
         <v>3.1468373825607276</v>
       </c>
-      <c r="J17" s="47">
+      <c r="J17" s="45">
         <v>2.9900000000000002</v>
       </c>
-      <c r="K17" s="48">
+      <c r="K17" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1865,37 +2028,37 @@
       <c r="A18" s="8">
         <v>3.6000000000000001</v>
       </c>
-      <c r="B18" s="39">
+      <c r="B18" s="38">
         <v>3.6800000000000002</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="39">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="40">
         <f>2*PI()/B18</f>
         <v>1.7073873117335832</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="48">
         <v>1.7</v>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="42">
         <v>1.71</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="43">
         <v>1.71</v>
       </c>
-      <c r="H18" s="45">
+      <c r="H18" s="44">
         <f>AVERAGE(E18:G18)</f>
         <v>1.7066666666666668</v>
       </c>
-      <c r="I18" s="46">
+      <c r="I18" s="40">
         <f>2*PI()/H18</f>
         <v>3.6815538909255388</v>
       </c>
-      <c r="J18" s="47">
+      <c r="J18" s="45">
         <v>1.5800000000000001</v>
       </c>
-      <c r="K18" s="48">
+      <c r="K18" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1903,37 +2066,37 @@
       <c r="A19" s="8">
         <v>4.2000000000000002</v>
       </c>
-      <c r="B19" s="39">
+      <c r="B19" s="38">
         <v>4.3899999999999997</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="39">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="40">
         <f>2*PI()/B19</f>
         <v>1.4312495004964889</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="41">
         <v>1.4399999999999999</v>
       </c>
-      <c r="F19" s="43">
+      <c r="F19" s="42">
         <v>1.4299999999999999</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="43">
         <v>1.4299999999999999</v>
       </c>
-      <c r="H19" s="45">
+      <c r="H19" s="44">
         <f>AVERAGE(E19:G19)</f>
         <v>1.4333333333333333</v>
       </c>
-      <c r="I19" s="46">
+      <c r="I19" s="40">
         <f>2*PI()/H19</f>
         <v>4.3836176561718041</v>
       </c>
-      <c r="J19" s="47">
+      <c r="J19" s="45">
         <v>0.89300000000000002</v>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1941,37 +2104,37 @@
       <c r="A20" s="8">
         <v>4.5</v>
       </c>
-      <c r="B20" s="39">
+      <c r="B20" s="38">
         <v>4.75</v>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="39">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="40">
         <f>2*PI()/B20</f>
         <v>1.3227758541430708</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="41">
         <v>1.3300000000000001</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="42">
         <v>1.3300000000000001</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="43">
         <v>1.3200000000000001</v>
       </c>
-      <c r="H20" s="45">
+      <c r="H20" s="44">
         <f>AVERAGE(E20:G20)</f>
         <v>1.3266666666666669</v>
       </c>
-      <c r="I20" s="46">
+      <c r="I20" s="40">
         <f>2*PI()/H20</f>
         <v>4.7360693270197878</v>
       </c>
-      <c r="J20" s="47">
+      <c r="J20" s="45">
         <v>0.71399999999999997</v>
       </c>
-      <c r="K20" s="48">
+      <c r="K20" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1979,88 +2142,516 @@
       <c r="A21" s="11">
         <v>4.7000000000000002</v>
       </c>
-      <c r="B21" s="51">
+      <c r="B21" s="49">
         <v>4.9500000000000002</v>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="50">
         <v>1.e-002</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="51">
         <f>2*PI()/B21</f>
         <v>1.2693303650867851</v>
       </c>
-      <c r="E21" s="54">
+      <c r="E21" s="52">
         <v>1.26</v>
       </c>
-      <c r="F21" s="55">
+      <c r="F21" s="53">
         <v>1.28</v>
       </c>
-      <c r="G21" s="56">
+      <c r="G21" s="54">
         <v>1.2669999999999999</v>
       </c>
-      <c r="H21" s="57">
+      <c r="H21" s="55">
         <f>AVERAGE(E21:G21)</f>
         <v>1.2689999999999999</v>
       </c>
-      <c r="I21" s="58">
+      <c r="I21" s="51">
         <f>2*PI()/H21</f>
         <v>4.9512886581399425</v>
       </c>
-      <c r="J21" s="59">
+      <c r="J21" s="56">
         <v>0.63400000000000001</v>
       </c>
-      <c r="K21" s="60">
+      <c r="K21" s="57">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="22" ht="13.5">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="62"/>
+      <c r="B22" s="59"/>
     </row>
     <row r="23" ht="12.75">
-      <c r="A23" s="63">
+      <c r="A23" s="60">
         <v>2.7000000000000002</v>
       </c>
-      <c r="B23" s="64">
+      <c r="B23" s="61">
         <v>2.54</v>
       </c>
-      <c r="C23" s="65">
+      <c r="C23" s="62">
         <v>1.e-002</v>
       </c>
-      <c r="D23" s="66">
+      <c r="D23" s="63">
         <f>2*PI()/B23</f>
         <v>2.4736950028266089</v>
       </c>
-      <c r="E23" s="64">
+      <c r="E23" s="61">
         <v>2.5099999999999998</v>
       </c>
-      <c r="F23" s="64">
+      <c r="F23" s="61">
         <v>2.5099999999999998</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G23" s="61">
         <v>2.46</v>
       </c>
-      <c r="H23" s="66">
+      <c r="H23" s="63">
         <f>AVERAGE(E23:G23)</f>
         <v>2.4933333333333332</v>
       </c>
-      <c r="I23" s="67">
+      <c r="I23" s="64">
         <f>2*PI()/H23</f>
         <v>2.5199941071575882</v>
       </c>
-      <c r="J23" s="64">
+      <c r="J23" s="61">
         <v>6.1100000000000003</v>
       </c>
-      <c r="K23" s="68">
+      <c r="K23" s="65">
         <v>2.9999999999999999e-002</v>
       </c>
     </row>
+    <row r="26" ht="12.75">
+      <c r="A26" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="71" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="67" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" ht="12.75">
+      <c r="A27" s="28">
+        <v>1.7</v>
+      </c>
+      <c r="B27" s="29">
+        <v>1.27</v>
+      </c>
+      <c r="C27" s="72">
+        <v>1.e-002</v>
+      </c>
+      <c r="D27" s="73">
+        <f>2*PI()/B27</f>
+        <v>4.9473900056532178</v>
+      </c>
+      <c r="E27" s="42">
+        <v>5.04</v>
+      </c>
+      <c r="F27" s="42">
+        <v>5.04</v>
+      </c>
+      <c r="G27" s="34">
+        <v>4.9500000000000002</v>
+      </c>
+      <c r="H27" s="35">
+        <f>AVERAGE(E27:G27)</f>
+        <v>5.0100000000000007</v>
+      </c>
+      <c r="I27" s="35">
+        <f>2*PI()/H27</f>
+        <v>1.2541288038282605</v>
+      </c>
+      <c r="J27" s="74">
+        <v>2.1600000000000001</v>
+      </c>
+      <c r="K27" s="37">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="28" ht="12.75">
+      <c r="A28" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="B28" s="38">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="C28" s="65">
+        <v>1.e-002</v>
+      </c>
+      <c r="D28" s="75">
+        <f>2*PI()/B28</f>
+        <v>4.3938358791465637</v>
+      </c>
+      <c r="E28" s="42">
+        <v>4.4100000000000001</v>
+      </c>
+      <c r="F28" s="42">
+        <v>4.5300000000000002</v>
+      </c>
+      <c r="G28" s="43">
+        <v>4.3700000000000001</v>
+      </c>
+      <c r="H28" s="44">
+        <f>AVERAGE(E28:G28)</f>
+        <v>4.4366666666666674</v>
+      </c>
+      <c r="I28" s="44">
+        <f>2*PI()/H28</f>
+        <v>1.4161950354274047</v>
+      </c>
+      <c r="J28" s="76">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K28" s="46">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="29" ht="12.75">
+      <c r="A29" s="47">
+        <v>2</v>
+      </c>
+      <c r="B29" s="38">
+        <v>1.6100000000000001</v>
+      </c>
+      <c r="C29" s="65">
+        <v>1.e-002</v>
+      </c>
+      <c r="D29" s="75">
+        <f>2*PI()/B29</f>
+        <v>3.9025995696767612</v>
+      </c>
+      <c r="E29" s="42">
+        <v>3.8599999999999999</v>
+      </c>
+      <c r="F29" s="42">
+        <v>3.8700000000000001</v>
+      </c>
+      <c r="G29" s="43">
+        <v>3.96</v>
+      </c>
+      <c r="H29" s="44">
+        <f>AVERAGE(E29:G29)</f>
+        <v>3.8966666666666669</v>
+      </c>
+      <c r="I29" s="44">
+        <f>2*PI()/H29</f>
+        <v>1.6124513192077636</v>
+      </c>
+      <c r="J29" s="76">
+        <v>2.6000000000000001</v>
+      </c>
+      <c r="K29" s="46">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="30" ht="12.75">
+      <c r="A30" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B30" s="38">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="C30" s="65">
+        <v>1.e-002</v>
+      </c>
+      <c r="D30" s="75">
+        <f>2*PI()/B30</f>
+        <v>3.0951651759505352</v>
+      </c>
+      <c r="E30" s="42">
+        <v>3.0800000000000001</v>
+      </c>
+      <c r="F30" s="42">
+        <v>3.0800000000000001</v>
+      </c>
+      <c r="G30" s="43">
+        <v>3.1099999999999999</v>
+      </c>
+      <c r="H30" s="44">
+        <f>AVERAGE(E30:G30)</f>
+        <v>3.0899999999999999</v>
+      </c>
+      <c r="I30" s="44">
+        <f>2*PI()/H30</f>
+        <v>2.0333933032943645</v>
+      </c>
+      <c r="J30" s="76">
+        <v>3.6699999999999999</v>
+      </c>
+      <c r="K30" s="46">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="31" ht="12.75">
+      <c r="A31" s="8">
+        <v>3.2000000000000002</v>
+      </c>
+      <c r="B31" s="38">
+        <v>3.1400000000000001</v>
+      </c>
+      <c r="C31" s="65">
+        <v>1.e-002</v>
+      </c>
+      <c r="D31" s="75">
+        <f>2*PI()/B31</f>
+        <v>2.0010144290380847</v>
+      </c>
+      <c r="E31" s="77">
+        <v>2</v>
+      </c>
+      <c r="F31" s="42">
+        <v>1.99</v>
+      </c>
+      <c r="G31" s="43">
+        <v>2</v>
+      </c>
+      <c r="H31" s="44">
+        <f>AVERAGE(E31:G31)</f>
+        <v>1.9966666666666668</v>
+      </c>
+      <c r="I31" s="44">
+        <f>2*PI()/H31</f>
+        <v>3.1468373825607276</v>
+      </c>
+      <c r="J31" s="76">
+        <v>2.9900000000000002</v>
+      </c>
+      <c r="K31" s="46">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="32" ht="12.75">
+      <c r="A32" s="8">
+        <v>3.6000000000000001</v>
+      </c>
+      <c r="B32" s="38">
+        <v>3.6800000000000002</v>
+      </c>
+      <c r="C32" s="65">
+        <v>1.e-002</v>
+      </c>
+      <c r="D32" s="75">
+        <f>2*PI()/B32</f>
+        <v>1.7073873117335832</v>
+      </c>
+      <c r="E32" s="77">
+        <v>1.7</v>
+      </c>
+      <c r="F32" s="42">
+        <v>1.71</v>
+      </c>
+      <c r="G32" s="43">
+        <v>1.71</v>
+      </c>
+      <c r="H32" s="44">
+        <f>AVERAGE(E32:G32)</f>
+        <v>1.7066666666666668</v>
+      </c>
+      <c r="I32" s="44">
+        <f>2*PI()/H32</f>
+        <v>3.6815538909255388</v>
+      </c>
+      <c r="J32" s="76">
+        <v>1.5800000000000001</v>
+      </c>
+      <c r="K32" s="46">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="33" ht="12.75">
+      <c r="A33" s="8">
+        <v>4.2000000000000002</v>
+      </c>
+      <c r="B33" s="38">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="C33" s="65">
+        <v>1.e-002</v>
+      </c>
+      <c r="D33" s="75">
+        <f>2*PI()/B33</f>
+        <v>1.4312495004964889</v>
+      </c>
+      <c r="E33" s="42">
+        <v>1.4399999999999999</v>
+      </c>
+      <c r="F33" s="42">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="G33" s="43">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="H33" s="44">
+        <f>AVERAGE(E33:G33)</f>
+        <v>1.4333333333333333</v>
+      </c>
+      <c r="I33" s="44">
+        <f>2*PI()/H33</f>
+        <v>4.3836176561718041</v>
+      </c>
+      <c r="J33" s="76">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="K33" s="46">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="34" ht="12.75">
+      <c r="A34" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="B34" s="38">
+        <v>4.75</v>
+      </c>
+      <c r="C34" s="65">
+        <v>1.e-002</v>
+      </c>
+      <c r="D34" s="75">
+        <f>2*PI()/B34</f>
+        <v>1.3227758541430708</v>
+      </c>
+      <c r="E34" s="42">
+        <v>1.3300000000000001</v>
+      </c>
+      <c r="F34" s="42">
+        <v>1.3300000000000001</v>
+      </c>
+      <c r="G34" s="43">
+        <v>1.3200000000000001</v>
+      </c>
+      <c r="H34" s="44">
+        <f>AVERAGE(E34:G34)</f>
+        <v>1.3266666666666669</v>
+      </c>
+      <c r="I34" s="44">
+        <f>2*PI()/H34</f>
+        <v>4.7360693270197878</v>
+      </c>
+      <c r="J34" s="76">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="K34" s="46">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="35" ht="12.75">
+      <c r="A35" s="11">
+        <v>4.7000000000000002</v>
+      </c>
+      <c r="B35" s="49">
+        <v>4.9500000000000002</v>
+      </c>
+      <c r="C35" s="78">
+        <v>1.e-002</v>
+      </c>
+      <c r="D35" s="79">
+        <f>2*PI()/B35</f>
+        <v>1.2693303650867851</v>
+      </c>
+      <c r="E35" s="52">
+        <v>1.26</v>
+      </c>
+      <c r="F35" s="53">
+        <v>1.28</v>
+      </c>
+      <c r="G35" s="54">
+        <v>1.2669999999999999</v>
+      </c>
+      <c r="H35" s="55">
+        <f>AVERAGE(E35:G35)</f>
+        <v>1.2689999999999999</v>
+      </c>
+      <c r="I35" s="55">
+        <f>2*PI()/H35</f>
+        <v>4.9512886581399425</v>
+      </c>
+      <c r="J35" s="80">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="K35" s="57">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="36" ht="12.75">
+      <c r="A36" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="59"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="81"/>
+    </row>
+    <row r="37" ht="12.75">
+      <c r="A37" s="82">
+        <v>2.7000000000000002</v>
+      </c>
+      <c r="B37" s="83">
+        <v>2.54</v>
+      </c>
+      <c r="C37" s="61">
+        <v>1.e-002</v>
+      </c>
+      <c r="D37" s="63">
+        <f>2*PI()/B37</f>
+        <v>2.4736950028266089</v>
+      </c>
+      <c r="E37" s="61">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="F37" s="61">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="G37" s="61">
+        <v>2.46</v>
+      </c>
+      <c r="H37" s="63">
+        <f>AVERAGE(E37:G37)</f>
+        <v>2.4933333333333332</v>
+      </c>
+      <c r="I37" s="64">
+        <f>2*PI()/H37</f>
+        <v>2.5199941071575882</v>
+      </c>
+      <c r="J37" s="61">
+        <v>6.1100000000000003</v>
+      </c>
+      <c r="K37" s="65">
+        <v>2.9999999999999999e-002</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -2084,45 +2675,45 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="69" t="s">
+      <c r="D1" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="70" t="s">
+      <c r="E1" s="85" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71">
+      <c r="A2" s="86">
         <v>0.25600000000000001</v>
       </c>
-      <c r="B2" s="71">
+      <c r="B2" s="86">
         <v>4.5999999999999999e-003</v>
       </c>
-      <c r="C2" s="71">
+      <c r="C2" s="86">
         <v>2.5699999999999998</v>
       </c>
-      <c r="D2" s="72">
+      <c r="D2" s="87">
         <v>4.4000000000000003e-003</v>
       </c>
-      <c r="E2" s="73">
+      <c r="E2" s="88">
         <f>SQRT(A6^2+C6^2)</f>
         <v>2.6210670338218649</v>
       </c>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2134,18 +2725,18 @@
       <c r="C3" s="9">
         <v>2.5899999999999999</v>
       </c>
-      <c r="D3" s="75">
+      <c r="D3" s="89">
         <v>1.9e-003</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2158,20 +2749,20 @@
       <c r="C4" s="9">
         <v>2.6099999999999999</v>
       </c>
-      <c r="D4" s="75">
+      <c r="D4" s="89">
         <f>7*10^-4</f>
         <v>6.9999999999999988e-004</v>
       </c>
-      <c r="E4" s="73">
+      <c r="E4" s="88">
         <f>E2/2</f>
         <v>1.3105335169109325</v>
       </c>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
     </row>
     <row r="5" ht="13.15">
       <c r="A5" s="14" t="s">
@@ -2186,43 +2777,43 @@
       <c r="D5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
     </row>
     <row r="6" ht="13.15">
-      <c r="A6" s="77">
+      <c r="A6" s="91">
         <f>((A2/B2^2)+(A3/B3^2)+(A4/B4^2))/((1/B2^2)+(1/B3^2)+(1/B4^2))</f>
         <v>0.27320113772034554</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B6" s="91">
         <f>SQRT(1/((1/B2^2)+(1/B3^2)+(1/B4^2)))</f>
         <v>5.724299964622563e-004</v>
       </c>
-      <c r="C6" s="77">
+      <c r="C6" s="91">
         <f>((C2/D2^2)+(C3/D3^2)+(C4/D4^2))/((1/D2^2)+(1/D3^2)+(1/D4^2))</f>
         <v>2.6067898906770486</v>
       </c>
-      <c r="D6" s="78">
+      <c r="D6" s="92">
         <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)))</f>
         <v>6.4964141370326843e-004</v>
       </c>
-      <c r="E6" s="79">
+      <c r="E6" s="93">
         <f>E2*2</f>
         <v>5.2421340676437298</v>
       </c>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
@@ -2237,13 +2828,13 @@
       <c r="D7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
+      <c r="E7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
     </row>
     <row r="8">
       <c r="A8" s="18">
@@ -2262,435 +2853,435 @@
         <f>_xlfn.STDEV.S(C2:C4)/SQRT(3)</f>
         <v>1.1547005383792526e-002</v>
       </c>
-      <c r="E8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
+      <c r="E8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
     </row>
     <row r="9" ht="12.75">
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81"/>
+      <c r="L9" s="81"/>
     </row>
     <row r="10">
-      <c r="A10" s="80" t="s">
+      <c r="A10" s="94" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="81" t="s">
+      <c r="C10" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="82" t="s">
+      <c r="D10" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="84"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="82" t="s">
+      <c r="F10" s="98"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="96" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="86" t="s">
+      <c r="J10" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="87" t="s">
+      <c r="K10" s="101" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="88">
+      <c r="A11" s="102">
         <v>1.8</v>
       </c>
-      <c r="B11" s="89">
+      <c r="B11" s="103">
         <v>1.3100000000000001</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="37">
         <v>1.e-002</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="40">
         <f t="shared" ref="D11:D20" si="3">2*PI()/B11</f>
         <v>4.79632466196915</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="104">
         <v>4.8399999999999999</v>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="104">
         <v>4.7400000000000002</v>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="104">
         <v>4.8200000000000003</v>
       </c>
-      <c r="H11" s="45">
+      <c r="H11" s="44">
         <f t="shared" ref="H11:H16" si="4">AVERAGE(E11:G11)</f>
         <v>4.7999999999999998</v>
       </c>
-      <c r="I11" s="90">
+      <c r="I11" s="44">
         <f t="shared" ref="I11:I20" si="5">2*PI()/H11</f>
         <v>1.3089969389957472</v>
       </c>
-      <c r="J11" s="89">
+      <c r="J11" s="103">
         <v>2.21</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11" s="37">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="88">
+      <c r="A12" s="102">
         <v>1.8200000000000001</v>
       </c>
-      <c r="B12" s="75">
+      <c r="B12" s="89">
         <v>1.3600000000000001</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="46">
         <v>1.e-002</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="40">
         <f t="shared" si="3"/>
         <v>4.6199891964555775</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="104">
         <v>4.6100000000000003</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="104">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G12" s="45">
+      <c r="G12" s="104">
         <v>4.6500000000000004</v>
       </c>
-      <c r="H12" s="45">
+      <c r="H12" s="44">
         <f t="shared" si="4"/>
         <v>4.6200000000000001</v>
       </c>
-      <c r="I12" s="90">
+      <c r="I12" s="44">
         <f t="shared" si="5"/>
         <v>1.3599968197358412</v>
       </c>
-      <c r="J12" s="75">
+      <c r="J12" s="89">
         <v>2.2400000000000002</v>
       </c>
-      <c r="K12" s="48">
+      <c r="K12" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="88">
+      <c r="A13" s="102">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B13" s="75">
+      <c r="B13" s="89">
         <v>1.9099999999999999</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="46">
         <v>1.e-002</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="40">
         <f t="shared" si="3"/>
         <v>3.2896258152772706</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="104">
         <v>3.2999999999999998</v>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="104">
         <v>3.29</v>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="104">
         <v>3.29</v>
       </c>
-      <c r="H13" s="45">
+      <c r="H13" s="44">
         <f t="shared" si="4"/>
         <v>3.293333333333333</v>
       </c>
-      <c r="I13" s="90">
+      <c r="I13" s="44">
         <f t="shared" si="5"/>
         <v>1.9078497896294293</v>
       </c>
-      <c r="J13" s="75">
+      <c r="J13" s="89">
         <v>3.3799999999999999</v>
       </c>
-      <c r="K13" s="48">
+      <c r="K13" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="88">
+      <c r="A14" s="102">
         <v>3.3999999999999999</v>
       </c>
-      <c r="B14" s="75">
+      <c r="B14" s="89">
         <v>3.3799999999999999</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="46">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="40">
         <f t="shared" si="3"/>
         <v>1.8589305642543155</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="104">
         <v>1.8600000000000001</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="104">
         <v>1.8600000000000001</v>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="104">
         <v>1.8500000000000001</v>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="44">
         <f t="shared" si="4"/>
         <v>1.8566666666666667</v>
       </c>
-      <c r="I14" s="90">
+      <c r="I14" s="44">
         <f t="shared" si="5"/>
         <v>3.384121350366025</v>
       </c>
-      <c r="J14" s="75">
+      <c r="J14" s="89">
         <v>2.3599999999999999</v>
       </c>
-      <c r="K14" s="48">
+      <c r="K14" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="88">
+      <c r="A15" s="102">
         <v>3.7999999999999998</v>
       </c>
-      <c r="B15" s="75">
+      <c r="B15" s="89">
         <v>3.8900000000000001</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="46">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="40">
         <f t="shared" si="3"/>
         <v>1.6152147319227728</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="104">
         <v>1.6200000000000001</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="104">
         <v>1.6200000000000001</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="104">
         <v>1.6100000000000001</v>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="44">
         <f t="shared" si="4"/>
         <v>1.6166666666666669</v>
       </c>
-      <c r="I15" s="90">
+      <c r="I15" s="44">
         <f t="shared" si="5"/>
         <v>3.8865063755750011</v>
       </c>
-      <c r="J15" s="75">
+      <c r="J15" s="89">
         <v>1.3600000000000001</v>
       </c>
-      <c r="K15" s="48">
+      <c r="K15" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="16" ht="13.15">
-      <c r="A16" s="88">
+      <c r="A16" s="102">
         <v>4</v>
       </c>
-      <c r="B16" s="75">
+      <c r="B16" s="89">
         <v>4.0599999999999996</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="46">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="40">
         <f t="shared" si="3"/>
         <v>1.5475825879752676</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="104">
         <v>1.54</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="104">
         <v>1.55</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="104">
         <v>1.55</v>
       </c>
-      <c r="H16" s="45">
+      <c r="H16" s="44">
         <f t="shared" si="4"/>
         <v>1.5466666666666666</v>
       </c>
-      <c r="I16" s="90">
+      <c r="I16" s="44">
         <f t="shared" si="5"/>
         <v>4.062404293435077</v>
       </c>
-      <c r="J16" s="75">
+      <c r="J16" s="89">
         <v>1.1699999999999999</v>
       </c>
-      <c r="K16" s="48">
+      <c r="K16" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" s="88">
+      <c r="A17" s="102">
         <v>4.2999999999999998</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="45">
         <v>4.5</v>
       </c>
-      <c r="C17" s="48">
+      <c r="C17" s="46">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="40">
         <f t="shared" si="3"/>
         <v>1.3962634015954636</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="104">
         <v>1.3999999999999999</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="104">
         <v>1.3999999999999999</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="104">
         <v>1.3999999999999999</v>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="44">
         <f>AVERAGE(F17:G17)</f>
         <v>1.3999999999999999</v>
       </c>
-      <c r="I17" s="90">
+      <c r="I17" s="44">
         <f t="shared" si="5"/>
         <v>4.4879895051282759</v>
       </c>
-      <c r="J17" s="75">
+      <c r="J17" s="89">
         <v>0.84499999999999997</v>
       </c>
-      <c r="K17" s="48">
+      <c r="K17" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="18" ht="12.75">
-      <c r="A18" s="88">
+      <c r="A18" s="102">
         <v>4.5999999999999996</v>
       </c>
-      <c r="B18" s="75">
+      <c r="B18" s="89">
         <v>4.8799999999999999</v>
       </c>
-      <c r="C18" s="48">
+      <c r="C18" s="46">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="40">
         <f t="shared" si="3"/>
         <v>1.2875379727827021</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="104">
         <v>1.3</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="104">
         <v>1.29</v>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="104">
         <v>1.28</v>
       </c>
-      <c r="H18" s="45">
+      <c r="H18" s="44">
         <f t="shared" ref="H18:H20" si="6">AVERAGE(E18:G18)</f>
         <v>1.29</v>
       </c>
-      <c r="I18" s="90">
+      <c r="I18" s="44">
         <f t="shared" si="5"/>
         <v>4.8706862846353376</v>
       </c>
-      <c r="J18" s="75">
+      <c r="J18" s="89">
         <v>0.67300000000000004</v>
       </c>
-      <c r="K18" s="48">
+      <c r="K18" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="19" ht="12.75">
-      <c r="A19" s="88">
+      <c r="A19" s="102">
         <v>4.7999999999999998</v>
       </c>
-      <c r="B19" s="75">
+      <c r="B19" s="89">
         <v>5.1100000000000003</v>
       </c>
-      <c r="C19" s="48">
+      <c r="C19" s="46">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="40">
         <f t="shared" si="3"/>
         <v>1.2295861657885687</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="104">
         <v>1.22</v>
       </c>
-      <c r="F19" s="45">
+      <c r="F19" s="104">
         <v>1.23</v>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="104">
         <v>1.23</v>
       </c>
-      <c r="H19" s="45">
+      <c r="H19" s="44">
         <f t="shared" si="6"/>
         <v>1.2266666666666668</v>
       </c>
-      <c r="I19" s="90">
+      <c r="I19" s="44">
         <f t="shared" si="5"/>
         <v>5.122161935200749</v>
       </c>
-      <c r="J19" s="75">
+      <c r="J19" s="89">
         <v>0.59299999999999997</v>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="46">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="20" ht="12.75">
-      <c r="A20" s="91">
+      <c r="A20" s="105">
         <v>4.9000000000000004</v>
       </c>
-      <c r="B20" s="92">
+      <c r="B20" s="106">
         <v>5.2300000000000004</v>
       </c>
-      <c r="C20" s="60">
+      <c r="C20" s="57">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="51">
         <f t="shared" si="3"/>
         <v>1.2013738637054656</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="107">
         <v>1.2</v>
       </c>
-      <c r="F20" s="57">
+      <c r="F20" s="107">
         <v>1.2</v>
       </c>
-      <c r="G20" s="57">
+      <c r="G20" s="107">
         <v>1.2</v>
       </c>
-      <c r="H20" s="57">
+      <c r="H20" s="55">
         <f t="shared" si="6"/>
         <v>1.2</v>
       </c>
-      <c r="I20" s="93">
+      <c r="I20" s="55">
         <f t="shared" si="5"/>
         <v>5.2359877559829888</v>
       </c>
-      <c r="J20" s="92">
+      <c r="J20" s="106">
         <v>0.55700000000000005</v>
       </c>
-      <c r="K20" s="60">
+      <c r="K20" s="57">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="23">
-      <c r="N23" s="94"/>
+      <c r="N23" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -160,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="66">
+  <borders count="59">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -392,34 +392,55 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="none"/>
       <right style="none"/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -447,9 +468,22 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="none"/>
       <right style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </right>
       <top style="medium">
         <color theme="1"/>
@@ -458,32 +492,256 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
       <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -492,39 +750,23 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
+      <right style="none"/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -544,40 +786,24 @@
       <right style="medium">
         <color theme="1"/>
       </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
+      <bottom style="medium">
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -588,384 +814,95 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="90">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -987,44 +924,34 @@
     <xf fontId="0" fillId="6" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="30" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1032,78 +959,52 @@
     <xf fontId="0" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="0" fillId="4" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="41" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="41" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="43" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="4" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="46" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="47" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="48" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="49" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="50" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="51" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="52" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="53" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="42" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="43" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="45" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="46" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="47" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="48" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="49" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="50" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="51" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="52" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="53" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="55" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="56" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="57" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="58" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="59" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="60" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="61" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="62" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="63" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="64" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="65" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="56" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1112,13 +1013,16 @@
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="65" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="56" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="57" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="58" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="49" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1824,51 +1728,51 @@
       <c r="H12" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="26" t="s">
+      <c r="I12" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="27" t="s">
+      <c r="J12" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="22" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28">
+      <c r="A13" s="27">
         <v>1.7</v>
       </c>
-      <c r="B13" s="29">
-        <v>1.25</v>
-      </c>
-      <c r="C13" s="30">
+      <c r="B13" s="28">
+        <v>1.27</v>
+      </c>
+      <c r="C13" s="29">
         <v>1.e-002</v>
       </c>
-      <c r="D13" s="31">
-        <f t="shared" ref="D13:D16" si="0">2*PI()/B13</f>
-        <v>5.026548245743669</v>
-      </c>
-      <c r="E13" s="32">
+      <c r="D13" s="30">
+        <f>2*PI()/B13</f>
+        <v>4.9473900056532178</v>
+      </c>
+      <c r="E13" s="31">
         <v>5.04</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="31">
         <v>5.04</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="32">
         <v>4.9500000000000002</v>
       </c>
-      <c r="H13" s="35">
-        <f t="shared" ref="H13:H16" si="1">AVERAGE(E13:G13)</f>
+      <c r="H13" s="33">
+        <f>AVERAGE(E13:G13)</f>
         <v>5.0100000000000007</v>
       </c>
-      <c r="I13" s="31">
-        <f t="shared" ref="I13:I16" si="2">2*PI()/H13</f>
+      <c r="I13" s="33">
+        <f>2*PI()/H13</f>
         <v>1.2541288038282605</v>
       </c>
-      <c r="J13" s="36">
+      <c r="J13" s="34">
         <v>2.1600000000000001</v>
       </c>
-      <c r="K13" s="37">
+      <c r="K13" s="35">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1876,75 +1780,75 @@
       <c r="A14" s="8">
         <v>1.8</v>
       </c>
-      <c r="B14" s="38">
-        <v>1.4199999999999999</v>
-      </c>
-      <c r="C14" s="39">
+      <c r="B14" s="36">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="C14" s="37">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="40">
-        <f t="shared" si="0"/>
-        <v>4.4247783853377367</v>
-      </c>
-      <c r="E14" s="41">
+      <c r="D14" s="38">
+        <f>2*PI()/B14</f>
+        <v>4.3938358791465637</v>
+      </c>
+      <c r="E14" s="31">
         <v>4.4100000000000001</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="31">
         <v>4.5300000000000002</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="39">
         <v>4.3700000000000001</v>
       </c>
-      <c r="H14" s="44">
-        <f t="shared" si="1"/>
+      <c r="H14" s="40">
+        <f>AVERAGE(E14:G14)</f>
         <v>4.4366666666666674</v>
       </c>
       <c r="I14" s="40">
-        <f t="shared" si="2"/>
+        <f>2*PI()/H14</f>
         <v>1.4161950354274047</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="41">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K14" s="46">
+      <c r="K14" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47">
+      <c r="A15" s="43">
         <v>2</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="36">
         <v>1.6100000000000001</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="37">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="40">
-        <f t="shared" si="0"/>
+      <c r="D15" s="38">
+        <f>2*PI()/B15</f>
         <v>3.9025995696767612</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="31">
         <v>3.8599999999999999</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="31">
         <v>3.8700000000000001</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="39">
         <v>3.96</v>
       </c>
-      <c r="H15" s="44">
-        <f t="shared" si="1"/>
+      <c r="H15" s="40">
+        <f>AVERAGE(E15:G15)</f>
         <v>3.8966666666666669</v>
       </c>
       <c r="I15" s="40">
-        <f t="shared" si="2"/>
+        <f>2*PI()/H15</f>
         <v>1.6124513192077636</v>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="41">
         <v>2.6000000000000001</v>
       </c>
-      <c r="K15" s="46">
+      <c r="K15" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1952,37 +1856,37 @@
       <c r="A16" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="36">
         <v>2.0299999999999998</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="37">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="40">
-        <f t="shared" si="0"/>
+      <c r="D16" s="38">
+        <f>2*PI()/B16</f>
         <v>3.0951651759505352</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="31">
         <v>3.0800000000000001</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="31">
         <v>3.0800000000000001</v>
       </c>
-      <c r="G16" s="43">
+      <c r="G16" s="39">
         <v>3.1099999999999999</v>
       </c>
-      <c r="H16" s="44">
-        <f t="shared" si="1"/>
+      <c r="H16" s="40">
+        <f>AVERAGE(E16:G16)</f>
         <v>3.0899999999999999</v>
       </c>
       <c r="I16" s="40">
-        <f t="shared" si="2"/>
+        <f>2*PI()/H16</f>
         <v>2.0333933032943645</v>
       </c>
-      <c r="J16" s="45">
+      <c r="J16" s="41">
         <v>3.6699999999999999</v>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1990,26 +1894,26 @@
       <c r="A17" s="8">
         <v>3.2000000000000002</v>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="36">
         <v>3.1400000000000001</v>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="37">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="38">
         <f>2*PI()/B17</f>
         <v>2.0010144290380847</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="44">
         <v>2</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="31">
         <v>1.99</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="39">
         <v>2</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="40">
         <f>AVERAGE(E17:G17)</f>
         <v>1.9966666666666668</v>
       </c>
@@ -2017,10 +1921,10 @@
         <f>2*PI()/H17</f>
         <v>3.1468373825607276</v>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="41">
         <v>2.9900000000000002</v>
       </c>
-      <c r="K17" s="46">
+      <c r="K17" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -2028,26 +1932,26 @@
       <c r="A18" s="8">
         <v>3.6000000000000001</v>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="36">
         <v>3.6800000000000002</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="37">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="38">
         <f>2*PI()/B18</f>
         <v>1.7073873117335832</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="44">
         <v>1.7</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="31">
         <v>1.71</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="39">
         <v>1.71</v>
       </c>
-      <c r="H18" s="44">
+      <c r="H18" s="40">
         <f>AVERAGE(E18:G18)</f>
         <v>1.7066666666666668</v>
       </c>
@@ -2055,10 +1959,10 @@
         <f>2*PI()/H18</f>
         <v>3.6815538909255388</v>
       </c>
-      <c r="J18" s="45">
+      <c r="J18" s="41">
         <v>1.5800000000000001</v>
       </c>
-      <c r="K18" s="46">
+      <c r="K18" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -2066,26 +1970,26 @@
       <c r="A19" s="8">
         <v>4.2000000000000002</v>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="36">
         <v>4.3899999999999997</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="37">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="38">
         <f>2*PI()/B19</f>
         <v>1.4312495004964889</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="31">
         <v>1.4399999999999999</v>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="31">
         <v>1.4299999999999999</v>
       </c>
-      <c r="G19" s="43">
+      <c r="G19" s="39">
         <v>1.4299999999999999</v>
       </c>
-      <c r="H19" s="44">
+      <c r="H19" s="40">
         <f>AVERAGE(E19:G19)</f>
         <v>1.4333333333333333</v>
       </c>
@@ -2093,10 +1997,10 @@
         <f>2*PI()/H19</f>
         <v>4.3836176561718041</v>
       </c>
-      <c r="J19" s="45">
+      <c r="J19" s="41">
         <v>0.89300000000000002</v>
       </c>
-      <c r="K19" s="46">
+      <c r="K19" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -2104,26 +2008,26 @@
       <c r="A20" s="8">
         <v>4.5</v>
       </c>
-      <c r="B20" s="38">
+      <c r="B20" s="36">
         <v>4.75</v>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="37">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="38">
         <f>2*PI()/B20</f>
         <v>1.3227758541430708</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="31">
         <v>1.3300000000000001</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="31">
         <v>1.3300000000000001</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="39">
         <v>1.3200000000000001</v>
       </c>
-      <c r="H20" s="44">
+      <c r="H20" s="40">
         <f>AVERAGE(E20:G20)</f>
         <v>1.3266666666666669</v>
       </c>
@@ -2131,10 +2035,10 @@
         <f>2*PI()/H20</f>
         <v>4.7360693270197878</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="41">
         <v>0.71399999999999997</v>
       </c>
-      <c r="K20" s="46">
+      <c r="K20" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -2142,26 +2046,26 @@
       <c r="A21" s="11">
         <v>4.7000000000000002</v>
       </c>
-      <c r="B21" s="49">
+      <c r="B21" s="45">
         <v>4.9500000000000002</v>
       </c>
-      <c r="C21" s="50">
+      <c r="C21" s="46">
         <v>1.e-002</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="47">
         <f>2*PI()/B21</f>
         <v>1.2693303650867851</v>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="48">
         <v>1.26</v>
       </c>
-      <c r="F21" s="53">
+      <c r="F21" s="49">
         <v>1.28</v>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="50">
         <v>1.2669999999999999</v>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="51">
         <f>AVERAGE(E21:G21)</f>
         <v>1.2689999999999999</v>
       </c>
@@ -2169,489 +2073,70 @@
         <f>2*PI()/H21</f>
         <v>4.9512886581399425</v>
       </c>
-      <c r="J21" s="56">
+      <c r="J21" s="52">
         <v>0.63400000000000001</v>
       </c>
-      <c r="K21" s="57">
+      <c r="K21" s="53">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="22" ht="13.5">
-      <c r="A22" s="58" t="s">
+      <c r="A22" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="59"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
     </row>
     <row r="23" ht="12.75">
-      <c r="A23" s="60">
+      <c r="A23" s="57">
         <v>2.7000000000000002</v>
       </c>
-      <c r="B23" s="61">
+      <c r="B23" s="58">
         <v>2.54</v>
       </c>
-      <c r="C23" s="62">
+      <c r="C23" s="58">
         <v>1.e-002</v>
       </c>
-      <c r="D23" s="63">
+      <c r="D23" s="59">
         <f>2*PI()/B23</f>
         <v>2.4736950028266089</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="58">
         <v>2.5099999999999998</v>
       </c>
-      <c r="F23" s="61">
+      <c r="F23" s="58">
         <v>2.5099999999999998</v>
       </c>
-      <c r="G23" s="61">
+      <c r="G23" s="58">
         <v>2.46</v>
       </c>
-      <c r="H23" s="63">
+      <c r="H23" s="59">
         <f>AVERAGE(E23:G23)</f>
         <v>2.4933333333333332</v>
       </c>
-      <c r="I23" s="64">
+      <c r="I23" s="60">
         <f>2*PI()/H23</f>
         <v>2.5199941071575882</v>
       </c>
-      <c r="J23" s="61">
+      <c r="J23" s="58">
         <v>6.1100000000000003</v>
       </c>
-      <c r="K23" s="65">
-        <v>2.9999999999999999e-002</v>
-      </c>
-    </row>
-    <row r="26" ht="12.75">
-      <c r="A26" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="66" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="66" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" s="67" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" ht="12.75">
-      <c r="A27" s="28">
-        <v>1.7</v>
-      </c>
-      <c r="B27" s="29">
-        <v>1.27</v>
-      </c>
-      <c r="C27" s="72">
-        <v>1.e-002</v>
-      </c>
-      <c r="D27" s="73">
-        <f>2*PI()/B27</f>
-        <v>4.9473900056532178</v>
-      </c>
-      <c r="E27" s="42">
-        <v>5.04</v>
-      </c>
-      <c r="F27" s="42">
-        <v>5.04</v>
-      </c>
-      <c r="G27" s="34">
-        <v>4.9500000000000002</v>
-      </c>
-      <c r="H27" s="35">
-        <f>AVERAGE(E27:G27)</f>
-        <v>5.0100000000000007</v>
-      </c>
-      <c r="I27" s="35">
-        <f>2*PI()/H27</f>
-        <v>1.2541288038282605</v>
-      </c>
-      <c r="J27" s="74">
-        <v>2.1600000000000001</v>
-      </c>
-      <c r="K27" s="37">
+      <c r="K23" s="61">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
-    <row r="28" ht="12.75">
-      <c r="A28" s="8">
-        <v>1.8</v>
-      </c>
-      <c r="B28" s="38">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="C28" s="65">
-        <v>1.e-002</v>
-      </c>
-      <c r="D28" s="75">
-        <f>2*PI()/B28</f>
-        <v>4.3938358791465637</v>
-      </c>
-      <c r="E28" s="42">
-        <v>4.4100000000000001</v>
-      </c>
-      <c r="F28" s="42">
-        <v>4.5300000000000002</v>
-      </c>
-      <c r="G28" s="43">
-        <v>4.3700000000000001</v>
-      </c>
-      <c r="H28" s="44">
-        <f>AVERAGE(E28:G28)</f>
-        <v>4.4366666666666674</v>
-      </c>
-      <c r="I28" s="44">
-        <f>2*PI()/H28</f>
-        <v>1.4161950354274047</v>
-      </c>
-      <c r="J28" s="76">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="K28" s="46">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
-    <row r="29" ht="12.75">
-      <c r="A29" s="47">
-        <v>2</v>
-      </c>
-      <c r="B29" s="38">
-        <v>1.6100000000000001</v>
-      </c>
-      <c r="C29" s="65">
-        <v>1.e-002</v>
-      </c>
-      <c r="D29" s="75">
-        <f>2*PI()/B29</f>
-        <v>3.9025995696767612</v>
-      </c>
-      <c r="E29" s="42">
-        <v>3.8599999999999999</v>
-      </c>
-      <c r="F29" s="42">
-        <v>3.8700000000000001</v>
-      </c>
-      <c r="G29" s="43">
-        <v>3.96</v>
-      </c>
-      <c r="H29" s="44">
-        <f>AVERAGE(E29:G29)</f>
-        <v>3.8966666666666669</v>
-      </c>
-      <c r="I29" s="44">
-        <f>2*PI()/H29</f>
-        <v>1.6124513192077636</v>
-      </c>
-      <c r="J29" s="76">
-        <v>2.6000000000000001</v>
-      </c>
-      <c r="K29" s="46">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
-    <row r="30" ht="12.75">
-      <c r="A30" s="8">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B30" s="38">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="C30" s="65">
-        <v>1.e-002</v>
-      </c>
-      <c r="D30" s="75">
-        <f>2*PI()/B30</f>
-        <v>3.0951651759505352</v>
-      </c>
-      <c r="E30" s="42">
-        <v>3.0800000000000001</v>
-      </c>
-      <c r="F30" s="42">
-        <v>3.0800000000000001</v>
-      </c>
-      <c r="G30" s="43">
-        <v>3.1099999999999999</v>
-      </c>
-      <c r="H30" s="44">
-        <f>AVERAGE(E30:G30)</f>
-        <v>3.0899999999999999</v>
-      </c>
-      <c r="I30" s="44">
-        <f>2*PI()/H30</f>
-        <v>2.0333933032943645</v>
-      </c>
-      <c r="J30" s="76">
-        <v>3.6699999999999999</v>
-      </c>
-      <c r="K30" s="46">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
-    <row r="31" ht="12.75">
-      <c r="A31" s="8">
-        <v>3.2000000000000002</v>
-      </c>
-      <c r="B31" s="38">
-        <v>3.1400000000000001</v>
-      </c>
-      <c r="C31" s="65">
-        <v>1.e-002</v>
-      </c>
-      <c r="D31" s="75">
-        <f>2*PI()/B31</f>
-        <v>2.0010144290380847</v>
-      </c>
-      <c r="E31" s="77">
-        <v>2</v>
-      </c>
-      <c r="F31" s="42">
-        <v>1.99</v>
-      </c>
-      <c r="G31" s="43">
-        <v>2</v>
-      </c>
-      <c r="H31" s="44">
-        <f>AVERAGE(E31:G31)</f>
-        <v>1.9966666666666668</v>
-      </c>
-      <c r="I31" s="44">
-        <f>2*PI()/H31</f>
-        <v>3.1468373825607276</v>
-      </c>
-      <c r="J31" s="76">
-        <v>2.9900000000000002</v>
-      </c>
-      <c r="K31" s="46">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
-    <row r="32" ht="12.75">
-      <c r="A32" s="8">
-        <v>3.6000000000000001</v>
-      </c>
-      <c r="B32" s="38">
-        <v>3.6800000000000002</v>
-      </c>
-      <c r="C32" s="65">
-        <v>1.e-002</v>
-      </c>
-      <c r="D32" s="75">
-        <f>2*PI()/B32</f>
-        <v>1.7073873117335832</v>
-      </c>
-      <c r="E32" s="77">
-        <v>1.7</v>
-      </c>
-      <c r="F32" s="42">
-        <v>1.71</v>
-      </c>
-      <c r="G32" s="43">
-        <v>1.71</v>
-      </c>
-      <c r="H32" s="44">
-        <f>AVERAGE(E32:G32)</f>
-        <v>1.7066666666666668</v>
-      </c>
-      <c r="I32" s="44">
-        <f>2*PI()/H32</f>
-        <v>3.6815538909255388</v>
-      </c>
-      <c r="J32" s="76">
-        <v>1.5800000000000001</v>
-      </c>
-      <c r="K32" s="46">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
-    <row r="33" ht="12.75">
-      <c r="A33" s="8">
-        <v>4.2000000000000002</v>
-      </c>
-      <c r="B33" s="38">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="C33" s="65">
-        <v>1.e-002</v>
-      </c>
-      <c r="D33" s="75">
-        <f>2*PI()/B33</f>
-        <v>1.4312495004964889</v>
-      </c>
-      <c r="E33" s="42">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="F33" s="42">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="G33" s="43">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="H33" s="44">
-        <f>AVERAGE(E33:G33)</f>
-        <v>1.4333333333333333</v>
-      </c>
-      <c r="I33" s="44">
-        <f>2*PI()/H33</f>
-        <v>4.3836176561718041</v>
-      </c>
-      <c r="J33" s="76">
-        <v>0.89300000000000002</v>
-      </c>
-      <c r="K33" s="46">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
-    <row r="34" ht="12.75">
-      <c r="A34" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="B34" s="38">
-        <v>4.75</v>
-      </c>
-      <c r="C34" s="65">
-        <v>1.e-002</v>
-      </c>
-      <c r="D34" s="75">
-        <f>2*PI()/B34</f>
-        <v>1.3227758541430708</v>
-      </c>
-      <c r="E34" s="42">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="F34" s="42">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="G34" s="43">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="H34" s="44">
-        <f>AVERAGE(E34:G34)</f>
-        <v>1.3266666666666669</v>
-      </c>
-      <c r="I34" s="44">
-        <f>2*PI()/H34</f>
-        <v>4.7360693270197878</v>
-      </c>
-      <c r="J34" s="76">
-        <v>0.71399999999999997</v>
-      </c>
-      <c r="K34" s="46">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
-    <row r="35" ht="12.75">
-      <c r="A35" s="11">
-        <v>4.7000000000000002</v>
-      </c>
-      <c r="B35" s="49">
-        <v>4.9500000000000002</v>
-      </c>
-      <c r="C35" s="78">
-        <v>1.e-002</v>
-      </c>
-      <c r="D35" s="79">
-        <f>2*PI()/B35</f>
-        <v>1.2693303650867851</v>
-      </c>
-      <c r="E35" s="52">
-        <v>1.26</v>
-      </c>
-      <c r="F35" s="53">
-        <v>1.28</v>
-      </c>
-      <c r="G35" s="54">
-        <v>1.2669999999999999</v>
-      </c>
-      <c r="H35" s="55">
-        <f>AVERAGE(E35:G35)</f>
-        <v>1.2689999999999999</v>
-      </c>
-      <c r="I35" s="55">
-        <f>2*PI()/H35</f>
-        <v>4.9512886581399425</v>
-      </c>
-      <c r="J35" s="80">
-        <v>0.63400000000000001</v>
-      </c>
-      <c r="K35" s="57">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
-    <row r="36" ht="12.75">
-      <c r="A36" s="58" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="59"/>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
-    </row>
-    <row r="37" ht="12.75">
-      <c r="A37" s="82">
-        <v>2.7000000000000002</v>
-      </c>
-      <c r="B37" s="83">
-        <v>2.54</v>
-      </c>
-      <c r="C37" s="61">
-        <v>1.e-002</v>
-      </c>
-      <c r="D37" s="63">
-        <f>2*PI()/B37</f>
-        <v>2.4736950028266089</v>
-      </c>
-      <c r="E37" s="61">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="F37" s="61">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="G37" s="61">
-        <v>2.46</v>
-      </c>
-      <c r="H37" s="63">
-        <f>AVERAGE(E37:G37)</f>
-        <v>2.4933333333333332</v>
-      </c>
-      <c r="I37" s="64">
-        <f>2*PI()/H37</f>
-        <v>2.5199941071575882</v>
-      </c>
-      <c r="J37" s="61">
-        <v>6.1100000000000003</v>
-      </c>
-      <c r="K37" s="65">
-        <v>2.9999999999999999e-002</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -2675,45 +2160,45 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="85" t="s">
+      <c r="E1" s="63" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="86">
+      <c r="A2" s="64">
         <v>0.25600000000000001</v>
       </c>
-      <c r="B2" s="86">
+      <c r="B2" s="64">
         <v>4.5999999999999999e-003</v>
       </c>
-      <c r="C2" s="86">
+      <c r="C2" s="64">
         <v>2.5699999999999998</v>
       </c>
-      <c r="D2" s="87">
+      <c r="D2" s="65">
         <v>4.4000000000000003e-003</v>
       </c>
-      <c r="E2" s="88">
+      <c r="E2" s="66">
         <f>SQRT(A6^2+C6^2)</f>
         <v>2.6210670338218649</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2725,18 +2210,18 @@
       <c r="C3" s="9">
         <v>2.5899999999999999</v>
       </c>
-      <c r="D3" s="89">
+      <c r="D3" s="67">
         <v>1.9e-003</v>
       </c>
-      <c r="E3" s="90" t="s">
+      <c r="E3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2749,20 +2234,20 @@
       <c r="C4" s="9">
         <v>2.6099999999999999</v>
       </c>
-      <c r="D4" s="89">
+      <c r="D4" s="67">
         <f>7*10^-4</f>
         <v>6.9999999999999988e-004</v>
       </c>
-      <c r="E4" s="88">
+      <c r="E4" s="66">
         <f>E2/2</f>
         <v>1.3105335169109325</v>
       </c>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
     </row>
     <row r="5" ht="13.15">
       <c r="A5" s="14" t="s">
@@ -2777,43 +2262,43 @@
       <c r="D5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="90" t="s">
+      <c r="E5" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
     </row>
     <row r="6" ht="13.15">
-      <c r="A6" s="91">
+      <c r="A6" s="69">
         <f>((A2/B2^2)+(A3/B3^2)+(A4/B4^2))/((1/B2^2)+(1/B3^2)+(1/B4^2))</f>
         <v>0.27320113772034554</v>
       </c>
-      <c r="B6" s="91">
+      <c r="B6" s="69">
         <f>SQRT(1/((1/B2^2)+(1/B3^2)+(1/B4^2)))</f>
         <v>5.724299964622563e-004</v>
       </c>
-      <c r="C6" s="91">
+      <c r="C6" s="69">
         <f>((C2/D2^2)+(C3/D3^2)+(C4/D4^2))/((1/D2^2)+(1/D3^2)+(1/D4^2))</f>
         <v>2.6067898906770486</v>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="70">
         <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)))</f>
         <v>6.4964141370326843e-004</v>
       </c>
-      <c r="E6" s="93">
+      <c r="E6" s="71">
         <f>E2*2</f>
         <v>5.2421340676437298</v>
       </c>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
@@ -2828,13 +2313,13 @@
       <c r="D7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
+      <c r="E7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
     </row>
     <row r="8">
       <c r="A8" s="18">
@@ -2853,435 +2338,435 @@
         <f>_xlfn.STDEV.S(C2:C4)/SQRT(3)</f>
         <v>1.1547005383792526e-002</v>
       </c>
-      <c r="E8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
-      <c r="L8" s="81"/>
+      <c r="E8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
     </row>
     <row r="9" ht="12.75">
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
-      <c r="L9" s="81"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
     </row>
     <row r="10">
-      <c r="A10" s="94" t="s">
+      <c r="A10" s="72" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="95" t="s">
+      <c r="C10" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="D10" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="97" t="s">
+      <c r="E10" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="98"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="96" t="s">
+      <c r="F10" s="76"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="74" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="100" t="s">
+      <c r="J10" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="101" t="s">
+      <c r="K10" s="79" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="102">
+      <c r="A11" s="80">
         <v>1.8</v>
       </c>
-      <c r="B11" s="103">
+      <c r="B11" s="81">
         <v>1.3100000000000001</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="35">
         <v>1.e-002</v>
       </c>
-      <c r="D11" s="40">
-        <f t="shared" ref="D11:D20" si="3">2*PI()/B11</f>
+      <c r="D11" s="82">
+        <f t="shared" ref="D11:D20" si="0">2*PI()/B11</f>
         <v>4.79632466196915</v>
       </c>
-      <c r="E11" s="104">
+      <c r="E11" s="83">
         <v>4.8399999999999999</v>
       </c>
-      <c r="F11" s="104">
+      <c r="F11" s="83">
         <v>4.7400000000000002</v>
       </c>
-      <c r="G11" s="104">
+      <c r="G11" s="83">
         <v>4.8200000000000003</v>
       </c>
-      <c r="H11" s="44">
-        <f t="shared" ref="H11:H16" si="4">AVERAGE(E11:G11)</f>
+      <c r="H11" s="40">
+        <f t="shared" ref="H11:H16" si="1">AVERAGE(E11:G11)</f>
         <v>4.7999999999999998</v>
       </c>
-      <c r="I11" s="44">
-        <f t="shared" ref="I11:I20" si="5">2*PI()/H11</f>
+      <c r="I11" s="40">
+        <f t="shared" ref="I11:I20" si="2">2*PI()/H11</f>
         <v>1.3089969389957472</v>
       </c>
-      <c r="J11" s="103">
+      <c r="J11" s="81">
         <v>2.21</v>
       </c>
-      <c r="K11" s="37">
+      <c r="K11" s="35">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="102">
+      <c r="A12" s="80">
         <v>1.8200000000000001</v>
       </c>
-      <c r="B12" s="89">
+      <c r="B12" s="67">
         <v>1.3600000000000001</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="42">
         <v>1.e-002</v>
       </c>
-      <c r="D12" s="40">
-        <f t="shared" si="3"/>
+      <c r="D12" s="82">
+        <f t="shared" si="0"/>
         <v>4.6199891964555775</v>
       </c>
-      <c r="E12" s="104">
+      <c r="E12" s="83">
         <v>4.6100000000000003</v>
       </c>
-      <c r="F12" s="104">
+      <c r="F12" s="83">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G12" s="104">
+      <c r="G12" s="83">
         <v>4.6500000000000004</v>
       </c>
-      <c r="H12" s="44">
-        <f t="shared" si="4"/>
+      <c r="H12" s="40">
+        <f t="shared" si="1"/>
         <v>4.6200000000000001</v>
       </c>
-      <c r="I12" s="44">
-        <f t="shared" si="5"/>
+      <c r="I12" s="40">
+        <f t="shared" si="2"/>
         <v>1.3599968197358412</v>
       </c>
-      <c r="J12" s="89">
+      <c r="J12" s="67">
         <v>2.2400000000000002</v>
       </c>
-      <c r="K12" s="46">
+      <c r="K12" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="102">
+      <c r="A13" s="80">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B13" s="89">
+      <c r="B13" s="67">
         <v>1.9099999999999999</v>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="42">
         <v>1.e-002</v>
       </c>
-      <c r="D13" s="40">
-        <f t="shared" si="3"/>
+      <c r="D13" s="82">
+        <f t="shared" si="0"/>
         <v>3.2896258152772706</v>
       </c>
-      <c r="E13" s="104">
+      <c r="E13" s="83">
         <v>3.2999999999999998</v>
       </c>
-      <c r="F13" s="104">
+      <c r="F13" s="83">
         <v>3.29</v>
       </c>
-      <c r="G13" s="104">
+      <c r="G13" s="83">
         <v>3.29</v>
       </c>
-      <c r="H13" s="44">
-        <f t="shared" si="4"/>
+      <c r="H13" s="40">
+        <f t="shared" si="1"/>
         <v>3.293333333333333</v>
       </c>
-      <c r="I13" s="44">
-        <f t="shared" si="5"/>
+      <c r="I13" s="40">
+        <f t="shared" si="2"/>
         <v>1.9078497896294293</v>
       </c>
-      <c r="J13" s="89">
+      <c r="J13" s="67">
         <v>3.3799999999999999</v>
       </c>
-      <c r="K13" s="46">
+      <c r="K13" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="102">
+      <c r="A14" s="80">
         <v>3.3999999999999999</v>
       </c>
-      <c r="B14" s="89">
+      <c r="B14" s="67">
         <v>3.3799999999999999</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="42">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="40">
-        <f t="shared" si="3"/>
+      <c r="D14" s="82">
+        <f t="shared" si="0"/>
         <v>1.8589305642543155</v>
       </c>
-      <c r="E14" s="104">
+      <c r="E14" s="83">
         <v>1.8600000000000001</v>
       </c>
-      <c r="F14" s="104">
+      <c r="F14" s="83">
         <v>1.8600000000000001</v>
       </c>
-      <c r="G14" s="104">
+      <c r="G14" s="83">
         <v>1.8500000000000001</v>
       </c>
-      <c r="H14" s="44">
-        <f t="shared" si="4"/>
+      <c r="H14" s="40">
+        <f t="shared" si="1"/>
         <v>1.8566666666666667</v>
       </c>
-      <c r="I14" s="44">
-        <f t="shared" si="5"/>
+      <c r="I14" s="40">
+        <f t="shared" si="2"/>
         <v>3.384121350366025</v>
       </c>
-      <c r="J14" s="89">
+      <c r="J14" s="67">
         <v>2.3599999999999999</v>
       </c>
-      <c r="K14" s="46">
+      <c r="K14" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="102">
+      <c r="A15" s="80">
         <v>3.7999999999999998</v>
       </c>
-      <c r="B15" s="89">
+      <c r="B15" s="67">
         <v>3.8900000000000001</v>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="42">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="40">
-        <f t="shared" si="3"/>
+      <c r="D15" s="82">
+        <f t="shared" si="0"/>
         <v>1.6152147319227728</v>
       </c>
-      <c r="E15" s="104">
+      <c r="E15" s="83">
         <v>1.6200000000000001</v>
       </c>
-      <c r="F15" s="104">
+      <c r="F15" s="83">
         <v>1.6200000000000001</v>
       </c>
-      <c r="G15" s="104">
+      <c r="G15" s="83">
         <v>1.6100000000000001</v>
       </c>
-      <c r="H15" s="44">
-        <f t="shared" si="4"/>
+      <c r="H15" s="40">
+        <f t="shared" si="1"/>
         <v>1.6166666666666669</v>
       </c>
-      <c r="I15" s="44">
-        <f t="shared" si="5"/>
+      <c r="I15" s="40">
+        <f t="shared" si="2"/>
         <v>3.8865063755750011</v>
       </c>
-      <c r="J15" s="89">
+      <c r="J15" s="67">
         <v>1.3600000000000001</v>
       </c>
-      <c r="K15" s="46">
+      <c r="K15" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="16" ht="13.15">
-      <c r="A16" s="102">
+      <c r="A16" s="80">
         <v>4</v>
       </c>
-      <c r="B16" s="89">
+      <c r="B16" s="67">
         <v>4.0599999999999996</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="42">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="40">
-        <f t="shared" si="3"/>
+      <c r="D16" s="82">
+        <f t="shared" si="0"/>
         <v>1.5475825879752676</v>
       </c>
-      <c r="E16" s="104">
+      <c r="E16" s="83">
         <v>1.54</v>
       </c>
-      <c r="F16" s="104">
+      <c r="F16" s="83">
         <v>1.55</v>
       </c>
-      <c r="G16" s="104">
+      <c r="G16" s="83">
         <v>1.55</v>
       </c>
-      <c r="H16" s="44">
-        <f t="shared" si="4"/>
+      <c r="H16" s="40">
+        <f t="shared" si="1"/>
         <v>1.5466666666666666</v>
       </c>
-      <c r="I16" s="44">
-        <f t="shared" si="5"/>
+      <c r="I16" s="40">
+        <f t="shared" si="2"/>
         <v>4.062404293435077</v>
       </c>
-      <c r="J16" s="89">
+      <c r="J16" s="67">
         <v>1.1699999999999999</v>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" s="102">
+      <c r="A17" s="80">
         <v>4.2999999999999998</v>
       </c>
-      <c r="B17" s="45">
+      <c r="B17" s="84">
         <v>4.5</v>
       </c>
-      <c r="C17" s="46">
+      <c r="C17" s="42">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="40">
-        <f t="shared" si="3"/>
+      <c r="D17" s="82">
+        <f t="shared" si="0"/>
         <v>1.3962634015954636</v>
       </c>
-      <c r="E17" s="104">
+      <c r="E17" s="83">
         <v>1.3999999999999999</v>
       </c>
-      <c r="F17" s="104">
+      <c r="F17" s="83">
         <v>1.3999999999999999</v>
       </c>
-      <c r="G17" s="104">
+      <c r="G17" s="83">
         <v>1.3999999999999999</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="40">
         <f>AVERAGE(F17:G17)</f>
         <v>1.3999999999999999</v>
       </c>
-      <c r="I17" s="44">
-        <f t="shared" si="5"/>
+      <c r="I17" s="40">
+        <f t="shared" si="2"/>
         <v>4.4879895051282759</v>
       </c>
-      <c r="J17" s="89">
+      <c r="J17" s="67">
         <v>0.84499999999999997</v>
       </c>
-      <c r="K17" s="46">
+      <c r="K17" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="18" ht="12.75">
-      <c r="A18" s="102">
+      <c r="A18" s="80">
         <v>4.5999999999999996</v>
       </c>
-      <c r="B18" s="89">
+      <c r="B18" s="67">
         <v>4.8799999999999999</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="42">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="82">
+        <f t="shared" si="0"/>
+        <v>1.2875379727827021</v>
+      </c>
+      <c r="E18" s="83">
+        <v>1.3</v>
+      </c>
+      <c r="F18" s="83">
+        <v>1.29</v>
+      </c>
+      <c r="G18" s="83">
+        <v>1.28</v>
+      </c>
+      <c r="H18" s="40">
+        <f t="shared" ref="H18:H20" si="3">AVERAGE(E18:G18)</f>
+        <v>1.29</v>
+      </c>
+      <c r="I18" s="40">
+        <f t="shared" si="2"/>
+        <v>4.8706862846353376</v>
+      </c>
+      <c r="J18" s="67">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="K18" s="42">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="19" ht="12.75">
+      <c r="A19" s="80">
+        <v>4.7999999999999998</v>
+      </c>
+      <c r="B19" s="67">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="C19" s="42">
+        <v>1.e-002</v>
+      </c>
+      <c r="D19" s="82">
+        <f t="shared" si="0"/>
+        <v>1.2295861657885687</v>
+      </c>
+      <c r="E19" s="83">
+        <v>1.22</v>
+      </c>
+      <c r="F19" s="83">
+        <v>1.23</v>
+      </c>
+      <c r="G19" s="83">
+        <v>1.23</v>
+      </c>
+      <c r="H19" s="40">
         <f t="shared" si="3"/>
-        <v>1.2875379727827021</v>
-      </c>
-      <c r="E18" s="104">
-        <v>1.3</v>
-      </c>
-      <c r="F18" s="104">
-        <v>1.29</v>
-      </c>
-      <c r="G18" s="104">
-        <v>1.28</v>
-      </c>
-      <c r="H18" s="44">
-        <f t="shared" ref="H18:H20" si="6">AVERAGE(E18:G18)</f>
-        <v>1.29</v>
-      </c>
-      <c r="I18" s="44">
-        <f t="shared" si="5"/>
-        <v>4.8706862846353376</v>
-      </c>
-      <c r="J18" s="89">
-        <v>0.67300000000000004</v>
-      </c>
-      <c r="K18" s="46">
+        <v>1.2266666666666668</v>
+      </c>
+      <c r="I19" s="40">
+        <f t="shared" si="2"/>
+        <v>5.122161935200749</v>
+      </c>
+      <c r="J19" s="67">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="K19" s="42">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
-    <row r="19" ht="12.75">
-      <c r="A19" s="102">
-        <v>4.7999999999999998</v>
-      </c>
-      <c r="B19" s="89">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="C19" s="46">
+    <row r="20" ht="12.75">
+      <c r="A20" s="85">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="B20" s="86">
+        <v>5.2300000000000004</v>
+      </c>
+      <c r="C20" s="53">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D20" s="87">
+        <f t="shared" si="0"/>
+        <v>1.2013738637054656</v>
+      </c>
+      <c r="E20" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="F20" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="G20" s="88">
+        <v>1.2</v>
+      </c>
+      <c r="H20" s="51">
         <f t="shared" si="3"/>
-        <v>1.2295861657885687</v>
-      </c>
-      <c r="E19" s="104">
-        <v>1.22</v>
-      </c>
-      <c r="F19" s="104">
-        <v>1.23</v>
-      </c>
-      <c r="G19" s="104">
-        <v>1.23</v>
-      </c>
-      <c r="H19" s="44">
-        <f t="shared" si="6"/>
-        <v>1.2266666666666668</v>
-      </c>
-      <c r="I19" s="44">
-        <f t="shared" si="5"/>
-        <v>5.122161935200749</v>
-      </c>
-      <c r="J19" s="89">
-        <v>0.59299999999999997</v>
-      </c>
-      <c r="K19" s="46">
+        <v>1.2</v>
+      </c>
+      <c r="I20" s="51">
+        <f t="shared" si="2"/>
+        <v>5.2359877559829888</v>
+      </c>
+      <c r="J20" s="86">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="K20" s="53">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
-    <row r="20" ht="12.75">
-      <c r="A20" s="105">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="B20" s="106">
-        <v>5.2300000000000004</v>
-      </c>
-      <c r="C20" s="57">
-        <v>1.e-002</v>
-      </c>
-      <c r="D20" s="51">
-        <f t="shared" si="3"/>
-        <v>1.2013738637054656</v>
-      </c>
-      <c r="E20" s="107">
-        <v>1.2</v>
-      </c>
-      <c r="F20" s="107">
-        <v>1.2</v>
-      </c>
-      <c r="G20" s="107">
-        <v>1.2</v>
-      </c>
-      <c r="H20" s="55">
-        <f t="shared" si="6"/>
-        <v>1.2</v>
-      </c>
-      <c r="I20" s="55">
-        <f t="shared" si="5"/>
-        <v>5.2359877559829888</v>
-      </c>
-      <c r="J20" s="106">
-        <v>0.55700000000000005</v>
-      </c>
-      <c r="K20" s="57">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
     <row r="23">
-      <c r="N23" s="108"/>
+      <c r="N23" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Oscillazioni smorzate e forzate.xlsx
+++ b/Oscillazioni smorzate e forzate.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>γ</t>
   </si>
@@ -31,13 +31,13 @@
     <t>sω</t>
   </si>
   <si>
-    <t xml:space="preserve">ω_0 (rad/s)</t>
+    <t xml:space="preserve">ω0 [rad/s]</t>
   </si>
   <si>
-    <t xml:space="preserve">ω_0/2 (rad/s)</t>
+    <t xml:space="preserve">(ω0)/2 [rad/s]</t>
   </si>
   <si>
-    <t xml:space="preserve">2ω_0 (rad/s)</t>
+    <t xml:space="preserve">2(ω0) [rad/s]</t>
   </si>
   <si>
     <t>γ_best</t>
@@ -74,25 +74,25 @@
     <t>ω_medio</t>
   </si>
   <si>
-    <t xml:space="preserve">Tensione (V)</t>
+    <t xml:space="preserve">Tensione [V]</t>
   </si>
   <si>
-    <t xml:space="preserve">ω interp. (rad/s) </t>
+    <t xml:space="preserve">ω interp. [rad/s] </t>
   </si>
   <si>
-    <t xml:space="preserve">sω (int.)</t>
+    <t xml:space="preserve">sω [rad/s]</t>
   </si>
   <si>
-    <t xml:space="preserve">T (s)</t>
+    <t xml:space="preserve">T [s]</t>
   </si>
   <si>
-    <t xml:space="preserve">T_f (s)</t>
+    <t xml:space="preserve">T_f [s]</t>
   </si>
   <si>
-    <t xml:space="preserve">T_f medio (s)</t>
+    <t xml:space="preserve">T_f medio [s]</t>
   </si>
   <si>
-    <t xml:space="preserve">ω forz (rad/s)</t>
+    <t xml:space="preserve">ω_f [rad/s]</t>
   </si>
   <si>
     <t>A</t>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t xml:space="preserve">Valore sul picco di risonanza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ω interp. [rad/s]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ω-f [rad/s]</t>
   </si>
 </sst>
 </file>
@@ -134,18 +140,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="5"/>
+        <fgColor theme="4" tint="0"/>
+        <bgColor theme="4" tint="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4285F4"/>
+        <bgColor rgb="FF4285F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0"/>
-        <bgColor theme="4" tint="0"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,7 +167,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="60">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -877,6 +884,21 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="none"/>
       <right style="medium">
         <color theme="1"/>
@@ -902,11 +924,11 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -917,10 +939,10 @@
     <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -936,6 +958,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -977,10 +1000,10 @@
     <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="38" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="40" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
@@ -1002,6 +1025,7 @@
     <xf fontId="0" fillId="6" borderId="52" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="53" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="54" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="55" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="56" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1013,10 +1037,10 @@
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="56" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="57" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="58" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="58" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="59" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="49" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1588,6 +1612,7 @@
       <c r="E3" s="10" t="s">
         <v>5</v>
       </c>
+      <c r="F3"/>
     </row>
     <row r="4">
       <c r="A4" s="8">
@@ -1673,6 +1698,7 @@
         <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)+(1/D5^2)+(1/D6^2)))</f>
         <v>4.9938375155813399e-003</v>
       </c>
+      <c r="F8"/>
     </row>
     <row r="9" ht="12.75">
       <c r="A9" s="15" t="s">
@@ -1734,45 +1760,45 @@
       <c r="J12" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="27" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27">
+      <c r="A13" s="28">
         <v>1.7</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="29">
         <v>1.27</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>1.e-002</v>
       </c>
-      <c r="D13" s="30">
-        <f>2*PI()/B13</f>
+      <c r="D13" s="31">
+        <f t="shared" ref="D13:D23" si="0">2*PI()/B13</f>
         <v>4.9473900056532178</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <v>5.04</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <v>5.04</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="33">
         <v>4.9500000000000002</v>
       </c>
-      <c r="H13" s="33">
-        <f>AVERAGE(E13:G13)</f>
+      <c r="H13" s="34">
+        <f t="shared" ref="H13:H23" si="1">AVERAGE(E13:G13)</f>
         <v>5.0100000000000007</v>
       </c>
-      <c r="I13" s="33">
-        <f>2*PI()/H13</f>
+      <c r="I13" s="34">
+        <f t="shared" ref="I13:I23" si="2">2*PI()/H13</f>
         <v>1.2541288038282605</v>
       </c>
-      <c r="J13" s="34">
+      <c r="J13" s="35">
         <v>2.1600000000000001</v>
       </c>
-      <c r="K13" s="35">
+      <c r="K13" s="36">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1780,75 +1806,75 @@
       <c r="A14" s="8">
         <v>1.8</v>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="37">
         <v>1.4299999999999999</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="38">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="38">
-        <f>2*PI()/B14</f>
+      <c r="D14" s="39">
+        <f t="shared" si="0"/>
         <v>4.3938358791465637</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <v>4.4100000000000001</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <v>4.5300000000000002</v>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="40">
         <v>4.3700000000000001</v>
       </c>
-      <c r="H14" s="40">
-        <f>AVERAGE(E14:G14)</f>
+      <c r="H14" s="41">
+        <f t="shared" si="1"/>
         <v>4.4366666666666674</v>
       </c>
-      <c r="I14" s="40">
-        <f>2*PI()/H14</f>
+      <c r="I14" s="41">
+        <f t="shared" si="2"/>
         <v>1.4161950354274047</v>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="42">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K14" s="42">
+      <c r="K14" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43">
+      <c r="A15" s="44">
         <v>2</v>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="37">
         <v>1.6100000000000001</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="38">
-        <f>2*PI()/B15</f>
+      <c r="D15" s="39">
+        <f t="shared" si="0"/>
         <v>3.9025995696767612</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <v>3.8599999999999999</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <v>3.8700000000000001</v>
       </c>
-      <c r="G15" s="39">
+      <c r="G15" s="40">
         <v>3.96</v>
       </c>
-      <c r="H15" s="40">
-        <f>AVERAGE(E15:G15)</f>
+      <c r="H15" s="41">
+        <f t="shared" si="1"/>
         <v>3.8966666666666669</v>
       </c>
-      <c r="I15" s="40">
-        <f>2*PI()/H15</f>
+      <c r="I15" s="41">
+        <f t="shared" si="2"/>
         <v>1.6124513192077636</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="42">
         <v>2.6000000000000001</v>
       </c>
-      <c r="K15" s="42">
+      <c r="K15" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1856,37 +1882,37 @@
       <c r="A16" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="37">
         <v>2.0299999999999998</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="38">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="38">
-        <f>2*PI()/B16</f>
+      <c r="D16" s="39">
+        <f t="shared" si="0"/>
         <v>3.0951651759505352</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <v>3.0800000000000001</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <v>3.0800000000000001</v>
       </c>
-      <c r="G16" s="39">
+      <c r="G16" s="40">
         <v>3.1099999999999999</v>
       </c>
-      <c r="H16" s="40">
-        <f>AVERAGE(E16:G16)</f>
+      <c r="H16" s="41">
+        <f t="shared" si="1"/>
         <v>3.0899999999999999</v>
       </c>
-      <c r="I16" s="40">
-        <f>2*PI()/H16</f>
+      <c r="I16" s="41">
+        <f t="shared" si="2"/>
         <v>2.0333933032943645</v>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="42">
         <v>3.6699999999999999</v>
       </c>
-      <c r="K16" s="42">
+      <c r="K16" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1894,37 +1920,37 @@
       <c r="A17" s="8">
         <v>3.2000000000000002</v>
       </c>
-      <c r="B17" s="36">
+      <c r="B17" s="37">
         <v>3.1400000000000001</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="38">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="38">
-        <f>2*PI()/B17</f>
+      <c r="D17" s="39">
+        <f t="shared" si="0"/>
         <v>2.0010144290380847</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="45">
         <v>2</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <v>1.99</v>
       </c>
-      <c r="G17" s="39">
+      <c r="G17" s="40">
         <v>2</v>
       </c>
-      <c r="H17" s="40">
-        <f>AVERAGE(E17:G17)</f>
+      <c r="H17" s="41">
+        <f t="shared" si="1"/>
         <v>1.9966666666666668</v>
       </c>
-      <c r="I17" s="40">
-        <f>2*PI()/H17</f>
+      <c r="I17" s="41">
+        <f t="shared" si="2"/>
         <v>3.1468373825607276</v>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="42">
         <v>2.9900000000000002</v>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1932,37 +1958,37 @@
       <c r="A18" s="8">
         <v>3.6000000000000001</v>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="37">
         <v>3.6800000000000002</v>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="38">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="38">
-        <f>2*PI()/B18</f>
+      <c r="D18" s="39">
+        <f t="shared" si="0"/>
         <v>1.7073873117335832</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="45">
         <v>1.7</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <v>1.71</v>
       </c>
-      <c r="G18" s="39">
+      <c r="G18" s="40">
         <v>1.71</v>
       </c>
-      <c r="H18" s="40">
-        <f>AVERAGE(E18:G18)</f>
+      <c r="H18" s="41">
+        <f t="shared" si="1"/>
         <v>1.7066666666666668</v>
       </c>
-      <c r="I18" s="40">
-        <f>2*PI()/H18</f>
+      <c r="I18" s="41">
+        <f t="shared" si="2"/>
         <v>3.6815538909255388</v>
       </c>
-      <c r="J18" s="41">
+      <c r="J18" s="42">
         <v>1.5800000000000001</v>
       </c>
-      <c r="K18" s="42">
+      <c r="K18" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -1970,37 +1996,37 @@
       <c r="A19" s="8">
         <v>4.2000000000000002</v>
       </c>
-      <c r="B19" s="36">
+      <c r="B19" s="37">
         <v>4.3899999999999997</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="38">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="38">
-        <f>2*PI()/B19</f>
+      <c r="D19" s="39">
+        <f t="shared" si="0"/>
         <v>1.4312495004964889</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="32">
         <v>1.4399999999999999</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="32">
         <v>1.4299999999999999</v>
       </c>
-      <c r="G19" s="39">
+      <c r="G19" s="40">
         <v>1.4299999999999999</v>
       </c>
-      <c r="H19" s="40">
-        <f>AVERAGE(E19:G19)</f>
+      <c r="H19" s="41">
+        <f t="shared" si="1"/>
         <v>1.4333333333333333</v>
       </c>
-      <c r="I19" s="40">
-        <f>2*PI()/H19</f>
+      <c r="I19" s="41">
+        <f t="shared" si="2"/>
         <v>4.3836176561718041</v>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="42">
         <v>0.89300000000000002</v>
       </c>
-      <c r="K19" s="42">
+      <c r="K19" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -2008,37 +2034,37 @@
       <c r="A20" s="8">
         <v>4.5</v>
       </c>
-      <c r="B20" s="36">
+      <c r="B20" s="37">
         <v>4.75</v>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="38">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="38">
-        <f>2*PI()/B20</f>
+      <c r="D20" s="39">
+        <f t="shared" si="0"/>
         <v>1.3227758541430708</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="32">
         <v>1.3300000000000001</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="32">
         <v>1.3300000000000001</v>
       </c>
-      <c r="G20" s="39">
+      <c r="G20" s="40">
         <v>1.3200000000000001</v>
       </c>
-      <c r="H20" s="40">
-        <f>AVERAGE(E20:G20)</f>
+      <c r="H20" s="41">
+        <f t="shared" si="1"/>
         <v>1.3266666666666669</v>
       </c>
-      <c r="I20" s="40">
-        <f>2*PI()/H20</f>
+      <c r="I20" s="41">
+        <f t="shared" si="2"/>
         <v>4.7360693270197878</v>
       </c>
-      <c r="J20" s="41">
+      <c r="J20" s="42">
         <v>0.71399999999999997</v>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -2046,90 +2072,90 @@
       <c r="A21" s="11">
         <v>4.7000000000000002</v>
       </c>
-      <c r="B21" s="45">
+      <c r="B21" s="46">
         <v>4.9500000000000002</v>
       </c>
-      <c r="C21" s="46">
+      <c r="C21" s="47">
         <v>1.e-002</v>
       </c>
-      <c r="D21" s="47">
-        <f>2*PI()/B21</f>
+      <c r="D21" s="48">
+        <f t="shared" si="0"/>
         <v>1.2693303650867851</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="49">
         <v>1.26</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="50">
         <v>1.28</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G21" s="51">
         <v>1.2669999999999999</v>
       </c>
-      <c r="H21" s="51">
-        <f>AVERAGE(E21:G21)</f>
+      <c r="H21" s="52">
+        <f t="shared" si="1"/>
         <v>1.2689999999999999</v>
       </c>
-      <c r="I21" s="51">
-        <f>2*PI()/H21</f>
+      <c r="I21" s="52">
+        <f t="shared" si="2"/>
         <v>4.9512886581399425</v>
       </c>
-      <c r="J21" s="52">
+      <c r="J21" s="53">
         <v>0.63400000000000001</v>
       </c>
-      <c r="K21" s="53">
+      <c r="K21" s="54">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="22" ht="13.5">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="56"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
     </row>
     <row r="23" ht="12.75">
-      <c r="A23" s="57">
+      <c r="A23" s="58">
         <v>2.7000000000000002</v>
       </c>
-      <c r="B23" s="58">
+      <c r="B23" s="59">
         <v>2.54</v>
       </c>
-      <c r="C23" s="58">
+      <c r="C23" s="59">
         <v>1.e-002</v>
       </c>
-      <c r="D23" s="59">
-        <f>2*PI()/B23</f>
+      <c r="D23" s="60">
+        <f t="shared" si="0"/>
         <v>2.4736950028266089</v>
       </c>
-      <c r="E23" s="58">
+      <c r="E23" s="59">
         <v>2.5099999999999998</v>
       </c>
-      <c r="F23" s="58">
+      <c r="F23" s="59">
         <v>2.5099999999999998</v>
       </c>
-      <c r="G23" s="58">
+      <c r="G23" s="59">
         <v>2.46</v>
       </c>
-      <c r="H23" s="59">
-        <f>AVERAGE(E23:G23)</f>
+      <c r="H23" s="60">
+        <f t="shared" si="1"/>
         <v>2.4933333333333332</v>
       </c>
-      <c r="I23" s="60">
-        <f>2*PI()/H23</f>
+      <c r="I23" s="61">
+        <f t="shared" si="2"/>
         <v>2.5199941071575882</v>
       </c>
-      <c r="J23" s="58">
+      <c r="J23" s="59">
         <v>6.1100000000000003</v>
       </c>
-      <c r="K23" s="61">
+      <c r="K23" s="62">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
@@ -2160,45 +2186,45 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="64" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="64">
+      <c r="A2" s="65">
         <v>0.25600000000000001</v>
       </c>
-      <c r="B2" s="64">
+      <c r="B2" s="65">
         <v>4.5999999999999999e-003</v>
       </c>
-      <c r="C2" s="64">
+      <c r="C2" s="65">
         <v>2.5699999999999998</v>
       </c>
-      <c r="D2" s="65">
+      <c r="D2" s="66">
         <v>4.4000000000000003e-003</v>
       </c>
-      <c r="E2" s="66">
+      <c r="E2" s="67">
         <f>SQRT(A6^2+C6^2)</f>
         <v>2.6210670338218649</v>
       </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2210,18 +2236,18 @@
       <c r="C3" s="9">
         <v>2.5899999999999999</v>
       </c>
-      <c r="D3" s="67">
+      <c r="D3" s="68">
         <v>1.9e-003</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2234,20 +2260,20 @@
       <c r="C4" s="9">
         <v>2.6099999999999999</v>
       </c>
-      <c r="D4" s="67">
+      <c r="D4" s="68">
         <f>7*10^-4</f>
         <v>6.9999999999999988e-004</v>
       </c>
-      <c r="E4" s="66">
+      <c r="E4" s="67">
         <f>E2/2</f>
         <v>1.3105335169109325</v>
       </c>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
     </row>
     <row r="5" ht="13.15">
       <c r="A5" s="14" t="s">
@@ -2262,43 +2288,43 @@
       <c r="D5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
     </row>
     <row r="6" ht="13.15">
-      <c r="A6" s="69">
+      <c r="A6" s="70">
         <f>((A2/B2^2)+(A3/B3^2)+(A4/B4^2))/((1/B2^2)+(1/B3^2)+(1/B4^2))</f>
         <v>0.27320113772034554</v>
       </c>
-      <c r="B6" s="69">
+      <c r="B6" s="70">
         <f>SQRT(1/((1/B2^2)+(1/B3^2)+(1/B4^2)))</f>
         <v>5.724299964622563e-004</v>
       </c>
-      <c r="C6" s="69">
+      <c r="C6" s="70">
         <f>((C2/D2^2)+(C3/D3^2)+(C4/D4^2))/((1/D2^2)+(1/D3^2)+(1/D4^2))</f>
         <v>2.6067898906770486</v>
       </c>
-      <c r="D6" s="70">
+      <c r="D6" s="71">
         <f>SQRT(1/((1/D2^2)+(1/D3^2)+(1/D4^2)))</f>
         <v>6.4964141370326843e-004</v>
       </c>
-      <c r="E6" s="71">
+      <c r="E6" s="72">
         <f>E2*2</f>
         <v>5.2421340676437298</v>
       </c>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
@@ -2313,13 +2339,13 @@
       <c r="D7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
+      <c r="E7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
     </row>
     <row r="8">
       <c r="A8" s="18">
@@ -2338,435 +2364,435 @@
         <f>_xlfn.STDEV.S(C2:C4)/SQRT(3)</f>
         <v>1.1547005383792526e-002</v>
       </c>
-      <c r="E8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
+      <c r="E8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
     </row>
     <row r="9" ht="12.75">
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
     </row>
     <row r="10">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="73" t="s">
+      <c r="B10" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="75" t="s">
+      <c r="E10" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="76"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="74" t="s">
+      <c r="F10" s="78"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="78" t="s">
+      <c r="I10" s="74" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="79" t="s">
+      <c r="K10" s="81" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="80">
+      <c r="A11" s="82">
         <v>1.8</v>
       </c>
-      <c r="B11" s="81">
+      <c r="B11" s="83">
         <v>1.3100000000000001</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <v>1.e-002</v>
       </c>
-      <c r="D11" s="82">
-        <f t="shared" ref="D11:D20" si="0">2*PI()/B11</f>
+      <c r="D11" s="84">
+        <f t="shared" ref="D11:D20" si="3">2*PI()/B11</f>
         <v>4.79632466196915</v>
       </c>
-      <c r="E11" s="83">
+      <c r="E11" s="85">
         <v>4.8399999999999999</v>
       </c>
-      <c r="F11" s="83">
+      <c r="F11" s="85">
         <v>4.7400000000000002</v>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="85">
         <v>4.8200000000000003</v>
       </c>
-      <c r="H11" s="40">
-        <f t="shared" ref="H11:H16" si="1">AVERAGE(E11:G11)</f>
+      <c r="H11" s="41">
+        <f t="shared" ref="H11:H16" si="4">AVERAGE(E11:G11)</f>
         <v>4.7999999999999998</v>
       </c>
-      <c r="I11" s="40">
-        <f t="shared" ref="I11:I20" si="2">2*PI()/H11</f>
+      <c r="I11" s="41">
+        <f t="shared" ref="I11:I20" si="5">2*PI()/H11</f>
         <v>1.3089969389957472</v>
       </c>
-      <c r="J11" s="81">
+      <c r="J11" s="68">
         <v>2.21</v>
       </c>
-      <c r="K11" s="35">
+      <c r="K11" s="36">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="80">
+      <c r="A12" s="82">
         <v>1.8200000000000001</v>
       </c>
-      <c r="B12" s="67">
+      <c r="B12" s="68">
         <v>1.3600000000000001</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="43">
         <v>1.e-002</v>
       </c>
-      <c r="D12" s="82">
-        <f t="shared" si="0"/>
+      <c r="D12" s="84">
+        <f t="shared" si="3"/>
         <v>4.6199891964555775</v>
       </c>
-      <c r="E12" s="83">
+      <c r="E12" s="85">
         <v>4.6100000000000003</v>
       </c>
-      <c r="F12" s="83">
+      <c r="F12" s="85">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G12" s="83">
+      <c r="G12" s="85">
         <v>4.6500000000000004</v>
       </c>
-      <c r="H12" s="40">
-        <f t="shared" si="1"/>
+      <c r="H12" s="41">
+        <f t="shared" si="4"/>
         <v>4.6200000000000001</v>
       </c>
-      <c r="I12" s="40">
-        <f t="shared" si="2"/>
+      <c r="I12" s="41">
+        <f t="shared" si="5"/>
         <v>1.3599968197358412</v>
       </c>
-      <c r="J12" s="67">
+      <c r="J12" s="68">
         <v>2.2400000000000002</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="80">
+      <c r="A13" s="82">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B13" s="67">
+      <c r="B13" s="68">
         <v>1.9099999999999999</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="43">
         <v>1.e-002</v>
       </c>
-      <c r="D13" s="82">
-        <f t="shared" si="0"/>
+      <c r="D13" s="84">
+        <f t="shared" si="3"/>
         <v>3.2896258152772706</v>
       </c>
-      <c r="E13" s="83">
+      <c r="E13" s="85">
         <v>3.2999999999999998</v>
       </c>
-      <c r="F13" s="83">
+      <c r="F13" s="85">
         <v>3.29</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="85">
         <v>3.29</v>
       </c>
-      <c r="H13" s="40">
-        <f t="shared" si="1"/>
+      <c r="H13" s="41">
+        <f t="shared" si="4"/>
         <v>3.293333333333333</v>
       </c>
-      <c r="I13" s="40">
-        <f t="shared" si="2"/>
+      <c r="I13" s="41">
+        <f t="shared" si="5"/>
         <v>1.9078497896294293</v>
       </c>
-      <c r="J13" s="67">
+      <c r="J13" s="68">
         <v>3.3799999999999999</v>
       </c>
-      <c r="K13" s="42">
+      <c r="K13" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="80">
+      <c r="A14" s="82">
         <v>3.3999999999999999</v>
       </c>
-      <c r="B14" s="67">
+      <c r="B14" s="68">
         <v>3.3799999999999999</v>
       </c>
-      <c r="C14" s="42">
+      <c r="C14" s="43">
         <v>1.e-002</v>
       </c>
-      <c r="D14" s="82">
-        <f t="shared" si="0"/>
+      <c r="D14" s="84">
+        <f t="shared" si="3"/>
         <v>1.8589305642543155</v>
       </c>
-      <c r="E14" s="83">
+      <c r="E14" s="85">
         <v>1.8600000000000001</v>
       </c>
-      <c r="F14" s="83">
+      <c r="F14" s="85">
         <v>1.8600000000000001</v>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="85">
         <v>1.8500000000000001</v>
       </c>
-      <c r="H14" s="40">
-        <f t="shared" si="1"/>
+      <c r="H14" s="41">
+        <f t="shared" si="4"/>
         <v>1.8566666666666667</v>
       </c>
-      <c r="I14" s="40">
-        <f t="shared" si="2"/>
+      <c r="I14" s="41">
+        <f t="shared" si="5"/>
         <v>3.384121350366025</v>
       </c>
-      <c r="J14" s="67">
+      <c r="J14" s="68">
         <v>2.3599999999999999</v>
       </c>
-      <c r="K14" s="42">
+      <c r="K14" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="80">
+      <c r="A15" s="82">
         <v>3.7999999999999998</v>
       </c>
-      <c r="B15" s="67">
+      <c r="B15" s="68">
         <v>3.8900000000000001</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="43">
         <v>1.e-002</v>
       </c>
-      <c r="D15" s="82">
-        <f t="shared" si="0"/>
+      <c r="D15" s="84">
+        <f t="shared" si="3"/>
         <v>1.6152147319227728</v>
       </c>
-      <c r="E15" s="83">
+      <c r="E15" s="85">
         <v>1.6200000000000001</v>
       </c>
-      <c r="F15" s="83">
+      <c r="F15" s="85">
         <v>1.6200000000000001</v>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="85">
         <v>1.6100000000000001</v>
       </c>
-      <c r="H15" s="40">
-        <f t="shared" si="1"/>
+      <c r="H15" s="41">
+        <f t="shared" si="4"/>
         <v>1.6166666666666669</v>
       </c>
-      <c r="I15" s="40">
-        <f t="shared" si="2"/>
+      <c r="I15" s="41">
+        <f t="shared" si="5"/>
         <v>3.8865063755750011</v>
       </c>
-      <c r="J15" s="67">
+      <c r="J15" s="68">
         <v>1.3600000000000001</v>
       </c>
-      <c r="K15" s="42">
+      <c r="K15" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="16" ht="13.15">
-      <c r="A16" s="80">
+      <c r="A16" s="82">
         <v>4</v>
       </c>
-      <c r="B16" s="67">
+      <c r="B16" s="68">
         <v>4.0599999999999996</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="43">
         <v>1.e-002</v>
       </c>
-      <c r="D16" s="82">
-        <f t="shared" si="0"/>
+      <c r="D16" s="84">
+        <f t="shared" si="3"/>
         <v>1.5475825879752676</v>
       </c>
-      <c r="E16" s="83">
+      <c r="E16" s="85">
         <v>1.54</v>
       </c>
-      <c r="F16" s="83">
+      <c r="F16" s="85">
         <v>1.55</v>
       </c>
-      <c r="G16" s="83">
+      <c r="G16" s="85">
         <v>1.55</v>
       </c>
-      <c r="H16" s="40">
-        <f t="shared" si="1"/>
+      <c r="H16" s="41">
+        <f t="shared" si="4"/>
         <v>1.5466666666666666</v>
       </c>
-      <c r="I16" s="40">
-        <f t="shared" si="2"/>
+      <c r="I16" s="41">
+        <f t="shared" si="5"/>
         <v>4.062404293435077</v>
       </c>
-      <c r="J16" s="67">
+      <c r="J16" s="68">
         <v>1.1699999999999999</v>
       </c>
-      <c r="K16" s="42">
+      <c r="K16" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" s="80">
+      <c r="A17" s="82">
         <v>4.2999999999999998</v>
       </c>
-      <c r="B17" s="84">
+      <c r="B17" s="86">
         <v>4.5</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="43">
         <v>1.e-002</v>
       </c>
-      <c r="D17" s="82">
-        <f t="shared" si="0"/>
+      <c r="D17" s="84">
+        <f t="shared" si="3"/>
         <v>1.3962634015954636</v>
       </c>
-      <c r="E17" s="83">
+      <c r="E17" s="85">
         <v>1.3999999999999999</v>
       </c>
-      <c r="F17" s="83">
+      <c r="F17" s="85">
         <v>1.3999999999999999</v>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="85">
         <v>1.3999999999999999</v>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="41">
         <f>AVERAGE(F17:G17)</f>
         <v>1.3999999999999999</v>
       </c>
-      <c r="I17" s="40">
-        <f t="shared" si="2"/>
+      <c r="I17" s="41">
+        <f t="shared" si="5"/>
         <v>4.4879895051282759</v>
       </c>
-      <c r="J17" s="67">
+      <c r="J17" s="68">
         <v>0.84499999999999997</v>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="18" ht="12.75">
-      <c r="A18" s="80">
+      <c r="A18" s="82">
         <v>4.5999999999999996</v>
       </c>
-      <c r="B18" s="67">
+      <c r="B18" s="68">
         <v>4.8799999999999999</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="43">
         <v>1.e-002</v>
       </c>
-      <c r="D18" s="82">
-        <f t="shared" si="0"/>
+      <c r="D18" s="84">
+        <f t="shared" si="3"/>
         <v>1.2875379727827021</v>
       </c>
-      <c r="E18" s="83">
+      <c r="E18" s="85">
         <v>1.3</v>
       </c>
-      <c r="F18" s="83">
+      <c r="F18" s="85">
         <v>1.29</v>
       </c>
-      <c r="G18" s="83">
+      <c r="G18" s="85">
         <v>1.28</v>
       </c>
-      <c r="H18" s="40">
-        <f t="shared" ref="H18:H20" si="3">AVERAGE(E18:G18)</f>
+      <c r="H18" s="41">
+        <f t="shared" ref="H18:H20" si="6">AVERAGE(E18:G18)</f>
         <v>1.29</v>
       </c>
-      <c r="I18" s="40">
-        <f t="shared" si="2"/>
+      <c r="I18" s="41">
+        <f t="shared" si="5"/>
         <v>4.8706862846353376</v>
       </c>
-      <c r="J18" s="67">
+      <c r="J18" s="68">
         <v>0.67300000000000004</v>
       </c>
-      <c r="K18" s="42">
+      <c r="K18" s="43">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="19" ht="12.75">
-      <c r="A19" s="80">
+      <c r="A19" s="82">
         <v>4.7999999999999998</v>
       </c>
-      <c r="B19" s="67">
+      <c r="B19" s="68">
         <v>5.1100000000000003</v>
       </c>
-      <c r="C19" s="42">
+      <c r="C19" s="43">
         <v>1.e-002</v>
       </c>
-      <c r="D19" s="82">
-        <f t="shared" si="0"/>
+      <c r="D19" s="84">
+        <f t="shared" si="3"/>
         <v>1.2295861657885687</v>
       </c>
-      <c r="E19" s="83">
+      <c r="E19" s="85">
         <v>1.22</v>
       </c>
-      <c r="F19" s="83">
+      <c r="F19" s="85">
         <v>1.23</v>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="85">
         <v>1.23</v>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="41">
+        <f t="shared" si="6"/>
+        <v>1.2266666666666668</v>
+      </c>
+      <c r="I19" s="41">
+        <f t="shared" si="5"/>
+        <v>5.122161935200749</v>
+      </c>
+      <c r="J19" s="68">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="K19" s="43">
+        <v>5.0000000000000003e-002</v>
+      </c>
+    </row>
+    <row r="20" ht="12.75">
+      <c r="A20" s="87">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="B20" s="88">
+        <v>5.2300000000000004</v>
+      </c>
+      <c r="C20" s="54">
+        <v>1.e-002</v>
+      </c>
+      <c r="D20" s="89">
         <f t="shared" si="3"/>
-        <v>1.2266666666666668</v>
-      </c>
-      <c r="I19" s="40">
-        <f t="shared" si="2"/>
-        <v>5.122161935200749</v>
-      </c>
-      <c r="J19" s="67">
-        <v>0.59299999999999997</v>
-      </c>
-      <c r="K19" s="42">
+        <v>1.2013738637054656</v>
+      </c>
+      <c r="E20" s="90">
+        <v>1.2</v>
+      </c>
+      <c r="F20" s="90">
+        <v>1.2</v>
+      </c>
+      <c r="G20" s="90">
+        <v>1.2</v>
+      </c>
+      <c r="H20" s="52">
+        <f t="shared" si="6"/>
+        <v>1.2</v>
+      </c>
+      <c r="I20" s="52">
+        <f t="shared" si="5"/>
+        <v>5.2359877559829888</v>
+      </c>
+      <c r="J20" s="88">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="K20" s="54">
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
-    <row r="20" ht="12.75">
-      <c r="A20" s="85">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="B20" s="86">
-        <v>5.2300000000000004</v>
-      </c>
-      <c r="C20" s="53">
-        <v>1.e-002</v>
-      </c>
-      <c r="D20" s="87">
-        <f t="shared" si="0"/>
-        <v>1.2013738637054656</v>
-      </c>
-      <c r="E20" s="88">
-        <v>1.2</v>
-      </c>
-      <c r="F20" s="88">
-        <v>1.2</v>
-      </c>
-      <c r="G20" s="88">
-        <v>1.2</v>
-      </c>
-      <c r="H20" s="51">
-        <f t="shared" si="3"/>
-        <v>1.2</v>
-      </c>
-      <c r="I20" s="51">
-        <f t="shared" si="2"/>
-        <v>5.2359877559829888</v>
-      </c>
-      <c r="J20" s="86">
-        <v>0.55700000000000005</v>
-      </c>
-      <c r="K20" s="53">
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
     <row r="23">
-      <c r="N23" s="89"/>
+      <c r="N23" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="1">
